--- a/Screener/data/rs_rating.xlsx
+++ b/Screener/data/rs_rating.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t>Symbol</t>
   </si>
@@ -455,6 +455,444 @@
   </si>
   <si>
     <t>CERE</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>PCVX</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>SRRK</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>KROS</t>
+  </si>
+  <si>
+    <t>STNE</t>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>SNAP</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>EOLS</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>PVH</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>PAGS</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>FINW</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>RCKT</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>CELC</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>NRDS</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>PBPB</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>SCS</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>KCLI</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>PRCT</t>
+  </si>
+  <si>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>JBI</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>MBIN</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>BXC</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>GLP</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>CVLT</t>
+  </si>
+  <si>
+    <t>RYAAY</t>
+  </si>
+  <si>
+    <t>JAKK</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>IRWD</t>
+  </si>
+  <si>
+    <t>SILXY</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>AFYA</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>FUNC</t>
+  </si>
+  <si>
+    <t>FSUMF</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>AYI</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>AMAL</t>
+  </si>
+  <si>
+    <t>RBB</t>
   </si>
 </sst>
 </file>
@@ -805,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1109,7 +1547,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>223.7247781429666</v>
+        <v>223.724782057645</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1325,7 +1763,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>187.6240010784819</v>
+        <v>187.6240094908383</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1397,7 +1835,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>184.1952147016001</v>
+        <v>184.195208528382</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1429,7 +1867,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>182.3930432366508</v>
+        <v>182.3930432682599</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1477,7 +1915,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>179.3338571368868</v>
+        <v>179.3338612942247</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1493,7 +1931,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>178.5632080782054</v>
+        <v>178.563213171559</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1557,7 +1995,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>175.6702738677306</v>
+        <v>175.6702689240981</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1693,7 +2131,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>170.8901723872048</v>
+        <v>170.890174351156</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1733,7 +2171,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>169.4919413138123</v>
+        <v>169.4919449301676</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1805,7 +2243,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>165.5654942353676</v>
+        <v>165.5655005693919</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1829,7 +2267,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>164.7507158784572</v>
+        <v>164.7507134098919</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1845,7 +2283,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>164.0718726389723</v>
+        <v>164.0718706184998</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1869,7 +2307,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>163.5737808555782</v>
+        <v>163.5737780719473</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1885,7 +2323,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>162.3958211028741</v>
+        <v>162.3958192067563</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1909,7 +2347,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>161.7993707729368</v>
+        <v>161.7993636686724</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -1925,7 +2363,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>161.0581608512518</v>
+        <v>161.0581606097776</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -1957,7 +2395,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>159.2164543418057</v>
+        <v>159.216452920279</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -1974,6 +2412,1174 @@
       </c>
       <c r="B146" s="1">
         <v>158.6142866269131</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+      <c r="B147" s="1">
+        <v>158.5229664232071</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+      <c r="B148" s="1">
+        <v>157.9682615116059</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="1">
+        <v>157.8103098074713</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+      <c r="B150" s="1">
+        <v>157.4630199428105</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" s="1">
+        <v>157.3258384552559</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" s="1">
+        <v>156.7497806774429</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" s="1">
+        <v>156.744092839885</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" s="1">
+        <v>156.2444974403169</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" s="1">
+        <v>156.1439708066716</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" s="1">
+        <v>156.1125791381686</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="1">
+        <v>155.5015336612318</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" s="1">
+        <v>155.4813823692634</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" s="1">
+        <v>155.473292802959</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" s="1">
+        <v>155.438792739735</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" s="1">
+        <v>155.4176164181508</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162" s="1">
+        <v>155.3610024204277</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" s="1">
+        <v>155.1766287554709</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" s="1">
+        <v>155.1441709923663</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" s="1">
+        <v>155.0301843421754</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" s="1">
+        <v>154.8528317611267</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" s="1">
+        <v>154.7108573796004</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" s="1">
+        <v>154.7017839815732</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" s="1">
+        <v>154.5823232465833</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" s="1">
+        <v>154.5380817432105</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" s="1">
+        <v>153.815539739555</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" s="1">
+        <v>153.5432469339261</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" s="1">
+        <v>153.4190052175755</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" s="1">
+        <v>153.4128954518382</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" s="1">
+        <v>153.3823924487724</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" s="1">
+        <v>152.869624404423</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" s="1">
+        <v>152.7153693194759</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" s="1">
+        <v>152.7142299638126</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" s="1">
+        <v>152.3960608825283</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" s="1">
+        <v>152.354860885453</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" s="1">
+        <v>152.0114632729539</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" s="1">
+        <v>151.8477316946282</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" s="1">
+        <v>151.732417263362</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" s="1">
+        <v>151.3790568249418</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" s="1">
+        <v>151.2489147528634</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="1">
+        <v>151.1952678073417</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" s="1">
+        <v>151.1878747074209</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" s="1">
+        <v>151.1770860233057</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" s="1">
+        <v>151.1756683180012</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" s="1">
+        <v>151.1349865503261</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" s="1">
+        <v>151.1094727448021</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" s="1">
+        <v>151.1001963305359</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" s="1">
+        <v>150.7143891272873</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" s="1">
+        <v>150.5435216383999</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" s="1">
+        <v>150.5412301034025</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" s="1">
+        <v>150.3854371578831</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" s="1">
+        <v>150.2378183644062</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" s="1">
+        <v>150.1337298252177</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" s="1">
+        <v>150.0780593943877</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" s="1">
+        <v>150.0774023608315</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" s="1">
+        <v>149.9348104489818</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" s="1">
+        <v>149.9040441576377</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" s="1">
+        <v>149.8638177500431</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" s="1">
+        <v>149.6171453066953</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" s="1">
+        <v>149.6134814660069</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" s="1">
+        <v>149.4415254148801</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" s="1">
+        <v>149.3789001218165</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" s="1">
+        <v>149.2142530012395</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" s="1">
+        <v>149.1312019734904</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" s="1">
+        <v>148.8495179677401</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" s="1">
+        <v>148.4915615861245</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" s="1">
+        <v>148.4305195509383</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" s="1">
+        <v>148.4169615533222</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" s="1">
+        <v>148.20221511756</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" s="1">
+        <v>148.1423274499962</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="1">
+        <v>147.845792601747</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" s="1">
+        <v>147.7153568588353</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="1">
+        <v>147.6500966579394</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" s="1">
+        <v>147.5857865024387</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" s="1">
+        <v>147.4735643211802</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="1">
+        <v>147.3265730926443</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" s="1">
+        <v>147.2563630947099</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" s="1">
+        <v>147.2259110910508</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="1">
+        <v>147.1635881441495</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" s="1">
+        <v>147.1104464742287</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" s="1">
+        <v>147.0301028020659</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" s="1">
+        <v>146.9559253972292</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>228</v>
+      </c>
+      <c r="B228" s="1">
+        <v>146.8346199831104</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" s="1">
+        <v>146.6856832745011</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" s="1">
+        <v>146.5794559163075</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>231</v>
+      </c>
+      <c r="B231" s="1">
+        <v>146.4919839468865</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>232</v>
+      </c>
+      <c r="B232" s="1">
+        <v>146.3742038147166</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>233</v>
+      </c>
+      <c r="B233" s="1">
+        <v>146.248418422179</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>234</v>
+      </c>
+      <c r="B234" s="1">
+        <v>146.1266409123283</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>235</v>
+      </c>
+      <c r="B235" s="1">
+        <v>146.1034875981094</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+      <c r="B236" s="1">
+        <v>146.0196375506538</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>237</v>
+      </c>
+      <c r="B237" s="1">
+        <v>145.9156537060867</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>238</v>
+      </c>
+      <c r="B238" s="1">
+        <v>145.8253542460312</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" s="1">
+        <v>145.62423069729</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>240</v>
+      </c>
+      <c r="B240" s="1">
+        <v>145.3647920695395</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>241</v>
+      </c>
+      <c r="B241" s="1">
+        <v>145.3600997909536</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>242</v>
+      </c>
+      <c r="B242" s="1">
+        <v>145.2547364261373</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>243</v>
+      </c>
+      <c r="B243" s="1">
+        <v>145.2453109402834</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>244</v>
+      </c>
+      <c r="B244" s="1">
+        <v>145.1075332777627</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>245</v>
+      </c>
+      <c r="B245" s="1">
+        <v>144.9956136454011</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>246</v>
+      </c>
+      <c r="B246" s="1">
+        <v>144.9656811694507</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+      <c r="B247" s="1">
+        <v>144.9355833703768</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>248</v>
+      </c>
+      <c r="B248" s="1">
+        <v>144.9315071075322</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>249</v>
+      </c>
+      <c r="B249" s="1">
+        <v>144.8084077193377</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>250</v>
+      </c>
+      <c r="B250" s="1">
+        <v>144.7415781536561</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" t="s">
+        <v>251</v>
+      </c>
+      <c r="B251" s="1">
+        <v>144.7270368773154</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>252</v>
+      </c>
+      <c r="B252" s="1">
+        <v>144.6542465441192</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>253</v>
+      </c>
+      <c r="B253" s="1">
+        <v>144.6443313300464</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>254</v>
+      </c>
+      <c r="B254" s="1">
+        <v>144.4282316855111</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>255</v>
+      </c>
+      <c r="B255" s="1">
+        <v>144.3476034989698</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" t="s">
+        <v>256</v>
+      </c>
+      <c r="B256" s="1">
+        <v>144.2579118932263</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" t="s">
+        <v>257</v>
+      </c>
+      <c r="B257" s="1">
+        <v>144.1686845146285</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" t="s">
+        <v>258</v>
+      </c>
+      <c r="B258" s="1">
+        <v>143.9257674989048</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" t="s">
+        <v>259</v>
+      </c>
+      <c r="B259" s="1">
+        <v>143.9148912566273</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
+        <v>260</v>
+      </c>
+      <c r="B260" s="1">
+        <v>143.9018810855246</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" t="s">
+        <v>261</v>
+      </c>
+      <c r="B261" s="1">
+        <v>143.8809337249653</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" t="s">
+        <v>262</v>
+      </c>
+      <c r="B262" s="1">
+        <v>143.8129819925551</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" t="s">
+        <v>263</v>
+      </c>
+      <c r="B263" s="1">
+        <v>143.7938493633196</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" t="s">
+        <v>264</v>
+      </c>
+      <c r="B264" s="1">
+        <v>143.7702736155623</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" t="s">
+        <v>265</v>
+      </c>
+      <c r="B265" s="1">
+        <v>143.7512418731264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" t="s">
+        <v>266</v>
+      </c>
+      <c r="B266" s="1">
+        <v>143.6885367189865</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" t="s">
+        <v>267</v>
+      </c>
+      <c r="B267" s="1">
+        <v>143.6868974178292</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" t="s">
+        <v>268</v>
+      </c>
+      <c r="B268" s="1">
+        <v>143.4964930874771</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" t="s">
+        <v>269</v>
+      </c>
+      <c r="B269" s="1">
+        <v>143.4409763861665</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" t="s">
+        <v>270</v>
+      </c>
+      <c r="B270" s="1">
+        <v>143.3775820636508</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" t="s">
+        <v>271</v>
+      </c>
+      <c r="B271" s="1">
+        <v>143.3437857392456</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" t="s">
+        <v>272</v>
+      </c>
+      <c r="B272" s="1">
+        <v>143.1601911281109</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" t="s">
+        <v>273</v>
+      </c>
+      <c r="B273" s="1">
+        <v>142.9776248934738</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" t="s">
+        <v>274</v>
+      </c>
+      <c r="B274" s="1">
+        <v>142.7480580652882</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" t="s">
+        <v>275</v>
+      </c>
+      <c r="B275" s="1">
+        <v>142.6384234026285</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" t="s">
+        <v>276</v>
+      </c>
+      <c r="B276" s="1">
+        <v>142.5078116625839</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" t="s">
+        <v>277</v>
+      </c>
+      <c r="B277" s="1">
+        <v>142.2229274670233</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" t="s">
+        <v>278</v>
+      </c>
+      <c r="B278" s="1">
+        <v>142.0595524747498</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" t="s">
+        <v>279</v>
+      </c>
+      <c r="B279" s="1">
+        <v>142.0432010277314</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" t="s">
+        <v>280</v>
+      </c>
+      <c r="B280" s="1">
+        <v>142.0071328127048</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" t="s">
+        <v>281</v>
+      </c>
+      <c r="B281" s="1">
+        <v>141.8695021685581</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" t="s">
+        <v>282</v>
+      </c>
+      <c r="B282" s="1">
+        <v>141.8597180888004</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" t="s">
+        <v>283</v>
+      </c>
+      <c r="B283" s="1">
+        <v>141.8246090185509</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" t="s">
+        <v>284</v>
+      </c>
+      <c r="B284" s="1">
+        <v>141.5574618431674</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" t="s">
+        <v>285</v>
+      </c>
+      <c r="B285" s="1">
+        <v>141.4653361238993</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" t="s">
+        <v>286</v>
+      </c>
+      <c r="B286" s="1">
+        <v>141.3955067910537</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" t="s">
+        <v>287</v>
+      </c>
+      <c r="B287" s="1">
+        <v>141.3921265007975</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" t="s">
+        <v>288</v>
+      </c>
+      <c r="B288" s="1">
+        <v>141.3812825540914</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" t="s">
+        <v>289</v>
+      </c>
+      <c r="B289" s="1">
+        <v>141.352312466971</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" t="s">
+        <v>290</v>
+      </c>
+      <c r="B290" s="1">
+        <v>141.195647437644</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" t="s">
+        <v>291</v>
+      </c>
+      <c r="B291" s="1">
+        <v>141.1550446090218</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" t="s">
+        <v>292</v>
+      </c>
+      <c r="B292" s="1">
+        <v>141.1249460240842</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating.xlsx
+++ b/Screener/data/rs_rating.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,877 +22,871 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>QDMI</t>
+  </si>
+  <si>
     <t>SLNO</t>
   </si>
   <si>
-    <t>QDMI</t>
-  </si>
-  <si>
     <t>CRBP</t>
   </si>
   <si>
     <t>AAOI</t>
   </si>
   <si>
+    <t>EYPT</t>
+  </si>
+  <si>
+    <t>ABXXF</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>DAVE</t>
+  </si>
+  <si>
+    <t>LBPH</t>
+  </si>
+  <si>
     <t>SSNT</t>
   </si>
   <si>
-    <t>EYPT</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>LBPH</t>
+    <t>IMNM</t>
+  </si>
+  <si>
+    <t>DWACU</t>
+  </si>
+  <si>
+    <t>NPCE</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>ELTK</t>
+  </si>
+  <si>
+    <t>IMGN</t>
   </si>
   <si>
     <t>HARP</t>
   </si>
   <si>
-    <t>ELTK</t>
-  </si>
-  <si>
-    <t>DWACU</t>
-  </si>
-  <si>
-    <t>NPCE</t>
-  </si>
-  <si>
-    <t>DAVE</t>
-  </si>
-  <si>
-    <t>IMGN</t>
+    <t>MGNX</t>
+  </si>
+  <si>
+    <t>AFRM</t>
   </si>
   <si>
     <t>ANF</t>
   </si>
   <si>
-    <t>MGNX</t>
-  </si>
-  <si>
-    <t>NEXI</t>
-  </si>
-  <si>
-    <t>DWAC</t>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>EWTX</t>
+  </si>
+  <si>
+    <t>ALPN</t>
   </si>
   <si>
     <t>SLN</t>
   </si>
   <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>EWTX</t>
+    <t>NERV</t>
   </si>
   <si>
     <t>VRT</t>
   </si>
   <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>PHVS</t>
+  </si>
+  <si>
+    <t>PRAX</t>
+  </si>
+  <si>
     <t>YMAB</t>
   </si>
   <si>
-    <t>PRAX</t>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>ORTX</t>
   </si>
   <si>
     <t>RXST</t>
   </si>
   <si>
+    <t>FDMT</t>
+  </si>
+  <si>
+    <t>HA</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>ALXO</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>CYTK</t>
+  </si>
+  <si>
+    <t>SMID</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>OSCR</t>
+  </si>
+  <si>
+    <t>KAMN</t>
+  </si>
+  <si>
     <t>TNGX</t>
   </si>
   <si>
-    <t>IMNM</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>OSCR</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>ORTX</t>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>ATXS</t>
+  </si>
+  <si>
+    <t>VSTM</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>ORIC</t>
   </si>
   <si>
     <t>DYN</t>
   </si>
   <si>
-    <t>CYTK</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>ALXO</t>
-  </si>
-  <si>
-    <t>HA</t>
-  </si>
-  <si>
-    <t>CVNA</t>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>BVN</t>
+  </si>
+  <si>
+    <t>VKTX</t>
+  </si>
+  <si>
+    <t>KURA</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>GEOS</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>ETHE</t>
   </si>
   <si>
     <t>HOV</t>
   </si>
   <si>
-    <t>ARVN</t>
-  </si>
-  <si>
-    <t>KAMN</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>KURA</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>VKTX</t>
+    <t>SWTX</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>LQDA</t>
+  </si>
+  <si>
+    <t>INBX</t>
+  </si>
+  <si>
+    <t>UTI</t>
+  </si>
+  <si>
+    <t>KDSKF</t>
+  </si>
+  <si>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>ICVX</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>CGEM</t>
+  </si>
+  <si>
+    <t>OLMA</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>TATT</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>WEAV</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>GTBIF</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>KEQU</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>TGI</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>SNAP</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>CRNX</t>
   </si>
   <si>
     <t>XMTR</t>
   </si>
   <si>
-    <t>BVN</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>ICVX</t>
-  </si>
-  <si>
-    <t>RYTM</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>SMID</t>
-  </si>
-  <si>
-    <t>LQDA</t>
-  </si>
-  <si>
-    <t>INBX</t>
-  </si>
-  <si>
-    <t>GEOS</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>GRPN</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>UTI</t>
-  </si>
-  <si>
-    <t>WEAV</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>FFNW</t>
-  </si>
-  <si>
-    <t>ESTC</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>ATXS</t>
+    <t>SRRK</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>KRTX</t>
+  </si>
+  <si>
+    <t>KALV</t>
   </si>
   <si>
     <t>METC</t>
   </si>
   <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>HMST</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>TAL</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>ZS</t>
+  </si>
+  <si>
     <t>KYMR</t>
   </si>
   <si>
-    <t>OLMA</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>HMST</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>MMYT</t>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>EVER</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>TOPS</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>ANET</t>
   </si>
   <si>
     <t>BMA</t>
   </si>
   <si>
-    <t>VSTM</t>
-  </si>
-  <si>
-    <t>TGI</t>
-  </si>
-  <si>
-    <t>CGEM</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>KEQU</t>
-  </si>
-  <si>
-    <t>CMPR</t>
+    <t>HCI</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>STNE</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>CERE</t>
+  </si>
+  <si>
+    <t>SGC</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>PCVX</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>INMB</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>PTVE</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>PRCT</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>CELC</t>
+  </si>
+  <si>
+    <t>PVH</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>PAGS</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>RCKT</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>IRWD</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>APLS</t>
+  </si>
+  <si>
+    <t>IGMS</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>RVIV</t>
+  </si>
+  <si>
+    <t>ELAN</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>UPST</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>NSSC</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>EOLS</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>SILXY</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>GLP</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>AVDL</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>FRD</t>
   </si>
   <si>
     <t>FN</t>
   </si>
   <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>SMLR</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>EVER</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>LWAY</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>SWTX</t>
-  </si>
-  <si>
-    <t>ZS</t>
-  </si>
-  <si>
-    <t>BASE</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>KRTX</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>GTBIF</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>SGC</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>TOPS</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>TREE</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>HCI</t>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>MCAFU</t>
+  </si>
+  <si>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>AXSM</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>BXC</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>DDOG</t>
   </si>
   <si>
     <t>PTGX</t>
   </si>
   <si>
-    <t>PTVE</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>CRNX</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>CERE</t>
-  </si>
-  <si>
-    <t>INFA</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>PCVX</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>GFF</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>SRRK</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>WING</t>
-  </si>
-  <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>KROS</t>
-  </si>
-  <si>
-    <t>STNE</t>
-  </si>
-  <si>
-    <t>RNA</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>SNAP</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>HBB</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>EOLS</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>PVH</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>BPMC</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>PAGS</t>
-  </si>
-  <si>
-    <t>PGTI</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>FINW</t>
-  </si>
-  <si>
-    <t>GIII</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>CYBR</t>
-  </si>
-  <si>
-    <t>RCKT</t>
-  </si>
-  <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>REVG</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>TEAM</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>CELC</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>PAY</t>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>JBI</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>NRDS</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>KCLI</t>
   </si>
   <si>
     <t>NHC</t>
   </si>
   <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>ASND</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>FLXS</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>NRDS</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>PBPB</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>PDD</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>COKE</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>SCS</t>
-  </si>
-  <si>
-    <t>PATH</t>
-  </si>
-  <si>
-    <t>GLOB</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>KCLI</t>
-  </si>
-  <si>
-    <t>MAC</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>PRCT</t>
-  </si>
-  <si>
-    <t>GDDY</t>
-  </si>
-  <si>
-    <t>TNK</t>
-  </si>
-  <si>
-    <t>JBI</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>MBIN</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>BXC</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>GLP</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>CVLT</t>
-  </si>
-  <si>
-    <t>RYAAY</t>
-  </si>
-  <si>
-    <t>JAKK</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>IRWD</t>
-  </si>
-  <si>
-    <t>SILXY</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>PLAY</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>AFYA</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
     <t>DV</t>
   </si>
   <si>
-    <t>FUNC</t>
-  </si>
-  <si>
-    <t>FSUMF</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>AYI</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>AMAL</t>
-  </si>
-  <si>
-    <t>RBB</t>
+    <t>BBU</t>
+  </si>
+  <si>
+    <t>RAPT</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>ASML</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1259,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>912.9364190499157</v>
+        <v>908.7912217663702</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1267,7 +1261,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>908.7912217663702</v>
+        <v>905.2668799999808</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1275,7 +1269,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>482.2593963395864</v>
+        <v>493.0720596181145</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1283,7 +1277,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>416.5679496066904</v>
+        <v>477.6616777867947</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1291,7 +1285,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>416.3534695741623</v>
+        <v>424.856596861924</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1299,7 +1293,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>416.2534147260132</v>
+        <v>420.681525474861</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1307,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>401.0382662044637</v>
+        <v>407.7163546963077</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1315,7 +1309,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>355.7139312259387</v>
+        <v>379.7799497496395</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1323,7 +1317,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>350.8484763217769</v>
+        <v>368.0638924738453</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1331,7 +1325,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>326.1227871873854</v>
+        <v>358.6819966528938</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1339,7 +1333,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>324.1479864325372</v>
+        <v>351.6137868017577</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1347,7 +1341,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>303.5205819163019</v>
+        <v>326.4791048553328</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1355,7 +1349,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>299.1892185698749</v>
+        <v>308.8951733568072</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1363,7 +1357,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>293.91517290177</v>
+        <v>304.3751755625669</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1371,7 +1365,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>283.865435803614</v>
+        <v>298.5059009332023</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1379,7 +1373,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>281.106904299011</v>
+        <v>295.4987702265349</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1387,7 +1381,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>278.8227706418102</v>
+        <v>295.2167500231912</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1395,7 +1389,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>275.2467183067766</v>
+        <v>292.3424326771536</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1403,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>275.0040572252959</v>
+        <v>277.0475960471111</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1411,7 +1405,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>271.9385483634994</v>
+        <v>275.6193837541316</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1419,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>265.7150428570033</v>
+        <v>270.5180171814354</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1427,7 +1421,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>251.9496742098896</v>
+        <v>266.6819893145033</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1435,7 +1429,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>249.7600884963136</v>
+        <v>264.0790129811433</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1443,7 +1437,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>247.0591634837086</v>
+        <v>258.5638091863702</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1451,7 +1445,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>246.1076740807605</v>
+        <v>257.8412114693667</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1459,7 +1453,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>244.9776548236684</v>
+        <v>256.6346285651784</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1467,7 +1461,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>239.7359440662389</v>
+        <v>252.7092844769693</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1475,7 +1469,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>239.2777448796471</v>
+        <v>250.3335096105171</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1483,7 +1477,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>238.6323695559665</v>
+        <v>247.1385204298113</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1491,7 +1485,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>236.9779614679961</v>
+        <v>246.1857370874881</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1499,7 +1493,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>234.4456300361643</v>
+        <v>240.1062860451932</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1507,7 +1501,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>231.0044025771222</v>
+        <v>237.8397637545987</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1515,7 +1509,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>226.3261185797138</v>
+        <v>230.9126927076888</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1523,7 +1517,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>226.0682615296178</v>
+        <v>228.5996114716274</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1531,7 +1525,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>225.3268439380723</v>
+        <v>227.1759440294535</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1539,7 +1533,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>224.09016183629</v>
+        <v>223.7340032827599</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1547,7 +1541,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>223.724782057645</v>
+        <v>222.6266023083127</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1555,7 +1549,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>219.6665731755122</v>
+        <v>221.5528724592597</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1563,7 +1557,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>218.3709412098721</v>
+        <v>220.5531174954706</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1571,7 +1565,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>216.8975600918989</v>
+        <v>219.438068640107</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1579,7 +1573,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>215.6032375991651</v>
+        <v>218.8347601855529</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1587,7 +1581,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>214.9921808441682</v>
+        <v>218.2118222238326</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1595,7 +1589,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>213.2759251113437</v>
+        <v>217.9503332719103</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1603,7 +1597,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>210.6353076315128</v>
+        <v>217.0362125476458</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1611,7 +1605,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>210.5636988798697</v>
+        <v>213.7477036063101</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1619,7 +1613,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>209.7031343061829</v>
+        <v>213.1507441463855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1627,7 +1621,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>209.4014470245964</v>
+        <v>209.9695953210488</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1635,7 +1629,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>206.365256702079</v>
+        <v>208.1451839088261</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1643,7 +1637,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>206.2537098521118</v>
+        <v>206.5330704792872</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1651,7 +1645,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>204.9277176094452</v>
+        <v>204.8617785410724</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1659,7 +1653,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>204.6878795767852</v>
+        <v>203.4819157835435</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1667,7 +1661,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>204.2524668478019</v>
+        <v>202.9374067753691</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1675,7 +1669,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>203.3552978875903</v>
+        <v>201.7296028393139</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1683,7 +1677,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>202.6364611162033</v>
+        <v>201.6445587836949</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1691,7 +1685,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>200.2099217999763</v>
+        <v>201.5034523222189</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1699,7 +1693,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>198.3935393795664</v>
+        <v>200.7447052941775</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1707,7 +1701,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>198.0345395956887</v>
+        <v>200.5296411884413</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1715,7 +1709,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>195.6828759049672</v>
+        <v>199.4324484379049</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1723,7 +1717,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>194.1211710089274</v>
+        <v>198.8728249573693</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1731,7 +1725,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>193.3339342775795</v>
+        <v>198.083321469365</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1739,7 +1733,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>192.731311464978</v>
+        <v>196.848230453552</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1747,7 +1741,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>192.4069506361736</v>
+        <v>195.986621322418</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1755,7 +1749,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>190.9673577644713</v>
+        <v>195.9029087253826</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1763,7 +1757,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>187.6240094908383</v>
+        <v>194.5044310803137</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1771,7 +1765,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>187.0015582442712</v>
+        <v>194.0765726536429</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1779,7 +1773,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>186.8566002162916</v>
+        <v>192.9974349731226</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1787,7 +1781,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>186.8236975510476</v>
+        <v>192.9429731779465</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1795,7 +1789,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>185.8415311740629</v>
+        <v>192.8740395988657</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1803,7 +1797,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>185.6027679796199</v>
+        <v>191.6397347208299</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1811,7 +1805,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>185.006115870232</v>
+        <v>191.5827791466122</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1819,7 +1813,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>184.713372660817</v>
+        <v>190.6870164547751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1827,7 +1821,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>184.6989368092678</v>
+        <v>190.39409402136</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1835,7 +1829,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>184.195208528382</v>
+        <v>189.9683110935702</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1843,7 +1837,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>184.0080649020912</v>
+        <v>188.5520062152269</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1851,7 +1845,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>183.3340331632695</v>
+        <v>188.181798290788</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1859,7 +1853,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>182.713683668921</v>
+        <v>187.0863178393401</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1867,7 +1861,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>182.3930432682599</v>
+        <v>186.7351567085502</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1875,7 +1869,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>181.7852966529517</v>
+        <v>186.165989802147</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1883,7 +1877,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>181.2527485307925</v>
+        <v>183.820804584267</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1891,7 +1885,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>180.7126599086264</v>
+        <v>182.6899127651311</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1899,7 +1893,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>180.053280551346</v>
+        <v>182.4912045860048</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1907,7 +1901,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>179.9162233588072</v>
+        <v>181.7733563393141</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1915,7 +1909,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>179.3338612942247</v>
+        <v>181.7483861389782</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1923,7 +1917,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>179.1121780751212</v>
+        <v>181.5255096507394</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1931,7 +1925,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>178.563213171559</v>
+        <v>181.286022979877</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1939,7 +1933,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>178.2600423730328</v>
+        <v>181.233784960844</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1947,7 +1941,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>177.6030835120482</v>
+        <v>180.7548671398999</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1955,7 +1949,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>176.7234924589982</v>
+        <v>179.3718973222179</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1963,7 +1957,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>176.6978614827513</v>
+        <v>179.3677381151317</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1971,7 +1965,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>176.4616523085841</v>
+        <v>179.3001316562137</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1979,7 +1973,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>176.3611315360475</v>
+        <v>177.4296863123832</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1987,7 +1981,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>175.9627164714499</v>
+        <v>177.0596889951125</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1995,7 +1989,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>175.6702689240981</v>
+        <v>176.9623305501541</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2003,7 +1997,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>175.602277687523</v>
+        <v>174.653737137838</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2011,7 +2005,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>175.3702761316032</v>
+        <v>173.249068460571</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2019,7 +2013,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>175.3601079812664</v>
+        <v>173.2438441412305</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2027,7 +2021,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>174.7544120439586</v>
+        <v>173.234635727267</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2035,7 +2029,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>174.419764557599</v>
+        <v>172.4859751604972</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2043,7 +2037,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>173.531441957839</v>
+        <v>172.0420516397117</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2051,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>173.4903569861426</v>
+        <v>171.867511498237</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2059,7 +2053,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>172.3750640358111</v>
+        <v>171.718531106384</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2067,7 +2061,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>172.329880205743</v>
+        <v>171.6794911716305</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2075,7 +2069,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>172.0811968284416</v>
+        <v>171.1040398619434</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2083,7 +2077,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>171.9920472838667</v>
+        <v>170.6121600424204</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2091,7 +2085,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>171.4709110052199</v>
+        <v>170.4905342225329</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2099,7 +2093,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>171.2503066180379</v>
+        <v>170.4392960635624</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2107,7 +2101,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>171.1811952636542</v>
+        <v>169.4889797263162</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2115,7 +2109,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>171.1413746780079</v>
+        <v>169.2925320937576</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2123,7 +2117,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>171.0151570209438</v>
+        <v>169.0998326218865</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2131,7 +2125,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>170.890174351156</v>
+        <v>168.356583962791</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2139,7 +2133,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>170.5789503395594</v>
+        <v>167.9438339637532</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2147,7 +2141,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>170.363979004502</v>
+        <v>167.5950549636715</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2155,7 +2149,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>169.7467588509923</v>
+        <v>166.9664700147367</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2163,7 +2157,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>169.7346707956275</v>
+        <v>166.6748315727897</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2171,7 +2165,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>169.4919449301676</v>
+        <v>166.0629130157534</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2179,7 +2173,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>167.9930271676182</v>
+        <v>165.8983357299042</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2187,7 +2181,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>167.6438397204554</v>
+        <v>165.8416494511974</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2195,7 +2189,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>167.0633079722796</v>
+        <v>165.7422389680055</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2203,7 +2197,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>166.6162494098352</v>
+        <v>165.6255210818939</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2211,7 +2205,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>166.3649423292429</v>
+        <v>165.4372277498547</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2219,7 +2213,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>166.2554536453833</v>
+        <v>165.3409752398918</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2227,7 +2221,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>165.7074906331672</v>
+        <v>164.6032836744267</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2235,7 +2229,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>165.5936276100514</v>
+        <v>164.5209642648639</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2243,7 +2237,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>165.5655005693919</v>
+        <v>164.299472130041</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2251,7 +2245,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>165.3974926300591</v>
+        <v>164.2845385036366</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2259,7 +2253,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>164.9875256582982</v>
+        <v>164.1897007384462</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2267,7 +2261,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>164.7507134098919</v>
+        <v>163.8943090780857</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2275,7 +2269,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>164.378259070015</v>
+        <v>163.5716640142317</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2283,7 +2277,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>164.0718706184998</v>
+        <v>163.5419853936843</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2291,7 +2285,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>163.9852139631008</v>
+        <v>163.4282725838131</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2299,7 +2293,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>163.7972239147459</v>
+        <v>163.3328044415179</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2307,7 +2301,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>163.5737780719473</v>
+        <v>163.3252659247349</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2315,7 +2309,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>163.0748322096088</v>
+        <v>163.0586782754258</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2323,7 +2317,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>162.3958192067563</v>
+        <v>162.8128236497196</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2331,7 +2325,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>162.2177190435016</v>
+        <v>162.6958960005175</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2339,7 +2333,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>161.8115790705888</v>
+        <v>161.9916128288806</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2347,7 +2341,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>161.7993636686724</v>
+        <v>161.9899667912639</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2355,7 +2349,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>161.7912931735793</v>
+        <v>161.2294979821162</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2363,7 +2357,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>161.0581606097776</v>
+        <v>160.8587239761485</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2371,7 +2365,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>160.4597430174367</v>
+        <v>160.445697519318</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2379,7 +2373,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>159.7286424783622</v>
+        <v>160.2302169270669</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2387,7 +2381,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>159.7119717359229</v>
+        <v>160.1680632069824</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2395,7 +2389,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>159.216452920279</v>
+        <v>158.8736077281749</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2403,7 +2397,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>158.7768034255337</v>
+        <v>158.7165641571219</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2411,7 +2405,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>158.6142866269131</v>
+        <v>158.6798690658427</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2419,7 +2413,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>158.5229664232071</v>
+        <v>158.6521908445361</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2427,7 +2421,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>157.9682615116059</v>
+        <v>158.5638612014836</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2435,7 +2429,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>157.8103098074713</v>
+        <v>158.2823764392229</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2443,7 +2437,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>157.4630199428105</v>
+        <v>157.7581563303898</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2451,7 +2445,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>157.3258384552559</v>
+        <v>157.7514253662565</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2459,7 +2453,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>156.7497806774429</v>
+        <v>157.4605935378798</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2467,7 +2461,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>156.744092839885</v>
+        <v>157.2875451551041</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2475,7 +2469,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>156.2444974403169</v>
+        <v>157.2802431574566</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2483,7 +2477,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>156.1439708066716</v>
+        <v>157.2668606983209</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2491,7 +2485,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>156.1125791381686</v>
+        <v>156.7873745547421</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2499,7 +2493,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>155.5015336612318</v>
+        <v>156.5049878114011</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2507,7 +2501,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>155.4813823692634</v>
+        <v>156.4218136963471</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2515,7 +2509,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>155.473292802959</v>
+        <v>156.2479860819071</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2523,7 +2517,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>155.438792739735</v>
+        <v>156.0008221007946</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2531,7 +2525,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>155.4176164181508</v>
+        <v>155.4590990658935</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2539,7 +2533,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>155.3610024204277</v>
+        <v>155.2101952222008</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2547,7 +2541,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>155.1766287554709</v>
+        <v>155.1354830424837</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2555,7 +2549,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>155.1441709923663</v>
+        <v>155.021270222429</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2563,7 +2557,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>155.0301843421754</v>
+        <v>154.9596976669849</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2571,7 +2565,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>154.8528317611267</v>
+        <v>154.8003579312085</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2579,7 +2573,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>154.7108573796004</v>
+        <v>154.4799850404722</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2587,7 +2581,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>154.7017839815732</v>
+        <v>154.4598167148422</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2595,7 +2589,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>154.5823232465833</v>
+        <v>154.3984895615965</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2603,7 +2597,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>154.5380817432105</v>
+        <v>154.1924220698564</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2611,7 +2605,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>153.815539739555</v>
+        <v>153.9544454479188</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2619,7 +2613,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>153.5432469339261</v>
+        <v>153.8589642083325</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2627,7 +2621,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>153.4190052175755</v>
+        <v>153.7240091063105</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2635,7 +2629,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>153.4128954518382</v>
+        <v>153.6127278972879</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2643,7 +2637,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>153.3823924487724</v>
+        <v>153.5591556202522</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2651,7 +2645,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>152.869624404423</v>
+        <v>153.3853241080314</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2659,7 +2653,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>152.7153693194759</v>
+        <v>153.1836403116247</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2667,7 +2661,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>152.7142299638126</v>
+        <v>152.8896849794769</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2675,7 +2669,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>152.3960608825283</v>
+        <v>152.7840169006321</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2683,7 +2677,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>152.354860885453</v>
+        <v>152.5000038296527</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2691,7 +2685,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>152.0114632729539</v>
+        <v>152.4065744640128</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2699,7 +2693,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>151.8477316946282</v>
+        <v>152.0958307217325</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2707,7 +2701,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>151.732417263362</v>
+        <v>151.9522672973073</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2715,7 +2709,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>151.3790568249418</v>
+        <v>151.8978280933796</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2723,7 +2717,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>151.2489147528634</v>
+        <v>151.7360453933968</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2731,7 +2725,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>151.1952678073417</v>
+        <v>151.5066458366682</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2739,7 +2733,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>151.1878747074209</v>
+        <v>151.4494213981275</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2747,7 +2741,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>151.1770860233057</v>
+        <v>150.7347914333031</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2755,7 +2749,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>151.1756683180012</v>
+        <v>150.7335135869096</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2763,7 +2757,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>151.1349865503261</v>
+        <v>150.6529895448531</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2771,7 +2765,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>151.1094727448021</v>
+        <v>150.4526906271532</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -2779,7 +2773,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>151.1001963305359</v>
+        <v>150.3215905496588</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -2787,7 +2781,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>150.7143891272873</v>
+        <v>150.1617130469193</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -2795,7 +2789,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>150.5435216383999</v>
+        <v>150.0661202942072</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -2803,7 +2797,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>150.5412301034025</v>
+        <v>149.9251124868075</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -2811,7 +2805,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>150.3854371578831</v>
+        <v>149.7431933485869</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -2819,7 +2813,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>150.2378183644062</v>
+        <v>149.6795335767263</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -2827,7 +2821,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>150.1337298252177</v>
+        <v>149.5409923259809</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -2835,7 +2829,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>150.0780593943877</v>
+        <v>149.2996725001151</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -2843,7 +2837,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>150.0774023608315</v>
+        <v>149.1812593158147</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -2851,7 +2845,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>149.9348104489818</v>
+        <v>149.0447669368554</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -2859,7 +2853,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>149.9040441576377</v>
+        <v>149.0175382697626</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -2867,7 +2861,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>149.8638177500431</v>
+        <v>148.8186333992895</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -2875,7 +2869,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>149.6171453066953</v>
+        <v>148.3540700897598</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -2883,7 +2877,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>149.6134814660069</v>
+        <v>148.2548328183105</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -2891,7 +2885,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>149.4415254148801</v>
+        <v>148.2423669444086</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -2899,7 +2893,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>149.3789001218165</v>
+        <v>147.9933362178913</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -2907,7 +2901,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>149.2142530012395</v>
+        <v>147.6156749865324</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -2915,7 +2909,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>149.1312019734904</v>
+        <v>147.603726717502</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -2923,7 +2917,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>148.8495179677401</v>
+        <v>147.4141571078422</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -2931,7 +2925,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>148.4915615861245</v>
+        <v>147.2856644784053</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -2939,7 +2933,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>148.4305195509383</v>
+        <v>147.212924267739</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -2947,7 +2941,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>148.4169615533222</v>
+        <v>147.2094960583713</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -2955,7 +2949,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>148.20221511756</v>
+        <v>146.9600774537036</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -2963,7 +2957,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>148.1423274499962</v>
+        <v>146.9520880562261</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -2971,7 +2965,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>147.845792601747</v>
+        <v>146.9036186674779</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -2979,7 +2973,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>147.7153568588353</v>
+        <v>146.8774997206254</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -2987,7 +2981,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>147.6500966579394</v>
+        <v>146.6987558277348</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -2995,7 +2989,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>147.5857865024387</v>
+        <v>146.6259352483625</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3003,7 +2997,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>147.4735643211802</v>
+        <v>146.6183651325876</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3011,7 +3005,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>147.3265730926443</v>
+        <v>146.4132307226488</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3019,7 +3013,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>147.2563630947099</v>
+        <v>146.3188686891746</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3027,7 +3021,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>147.2259110910508</v>
+        <v>146.3112679119817</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3035,7 +3029,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>147.1635881441495</v>
+        <v>146.2332852774141</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3043,7 +3037,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>147.1104464742287</v>
+        <v>146.0942816152871</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3051,7 +3045,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>147.0301028020659</v>
+        <v>145.971045812894</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3059,7 +3053,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>146.9559253972292</v>
+        <v>145.8590999687898</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3067,7 +3061,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>146.8346199831104</v>
+        <v>145.5774203824675</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3075,7 +3069,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>146.6856832745011</v>
+        <v>145.0865177259149</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3083,7 +3077,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>146.5794559163075</v>
+        <v>144.952068435708</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3091,7 +3085,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>146.4919839468865</v>
+        <v>144.8882599061112</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3099,7 +3093,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>146.3742038147166</v>
+        <v>144.8667847520384</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3107,7 +3101,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>146.248418422179</v>
+        <v>144.8618249031144</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3115,7 +3109,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>146.1266409123283</v>
+        <v>144.4905926773867</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3123,7 +3117,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>146.1034875981094</v>
+        <v>144.0657167193846</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3131,7 +3125,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>146.0196375506538</v>
+        <v>143.9982531754078</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3139,7 +3133,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>145.9156537060867</v>
+        <v>143.7982039199218</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3147,7 +3141,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>145.8253542460312</v>
+        <v>143.7421078393399</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3155,7 +3149,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>145.62423069729</v>
+        <v>143.6973612435422</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3163,7 +3157,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>145.3647920695395</v>
+        <v>143.653457341824</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3171,7 +3165,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>145.3600997909536</v>
+        <v>143.5540661844574</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3179,7 +3173,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>145.2547364261373</v>
+        <v>143.2293761855781</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3187,7 +3181,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>145.2453109402834</v>
+        <v>143.1840990665836</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3195,7 +3189,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>145.1075332777627</v>
+        <v>143.0428322123164</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3203,7 +3197,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>144.9956136454011</v>
+        <v>142.98157191454</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3211,7 +3205,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>144.9656811694507</v>
+        <v>142.9617644221845</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3219,7 +3213,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>144.9355833703768</v>
+        <v>142.6821850632933</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3227,7 +3221,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>144.9315071075322</v>
+        <v>142.4620052165698</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3235,7 +3229,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>144.8084077193377</v>
+        <v>142.264552832483</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3243,7 +3237,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>144.7415781536561</v>
+        <v>142.2536700390305</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3251,7 +3245,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>144.7270368773154</v>
+        <v>142.2354397636507</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3259,7 +3253,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>144.6542465441192</v>
+        <v>142.2198391896674</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3267,7 +3261,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>144.6443313300464</v>
+        <v>142.2140883082893</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3275,7 +3269,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>144.4282316855111</v>
+        <v>142.0806413469289</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3283,7 +3277,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>144.3476034989698</v>
+        <v>142.0068910045252</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3291,7 +3285,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>144.2579118932263</v>
+        <v>141.8640668603788</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3299,7 +3293,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>144.1686845146285</v>
+        <v>141.8530593454739</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3307,7 +3301,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>143.9257674989048</v>
+        <v>141.8353731610912</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3315,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>143.9148912566273</v>
+        <v>141.700408132966</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3323,7 +3317,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>143.9018810855246</v>
+        <v>141.5121359789245</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3331,7 +3325,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>143.8809337249653</v>
+        <v>141.5057186020516</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3339,7 +3333,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>143.8129819925551</v>
+        <v>141.5031613548059</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3347,7 +3341,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>143.7938493633196</v>
+        <v>141.4975196081877</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3355,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>143.7702736155623</v>
+        <v>141.4753882338552</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3363,7 +3357,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>143.7512418731264</v>
+        <v>141.4579332944129</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3371,7 +3365,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>143.6885367189865</v>
+        <v>141.3722306764255</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3379,7 +3373,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>143.6868974178292</v>
+        <v>141.313922352134</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3387,7 +3381,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>143.4964930874771</v>
+        <v>141.3082040535338</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3395,7 +3389,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>143.4409763861665</v>
+        <v>141.2707086017318</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3403,7 +3397,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>143.3775820636508</v>
+        <v>141.177758720168</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3411,7 +3405,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>143.3437857392456</v>
+        <v>141.0801897552028</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3419,7 +3413,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>143.1601911281109</v>
+        <v>140.9414581411094</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3427,7 +3421,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>142.9776248934738</v>
+        <v>140.7440044475105</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3435,7 +3429,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>142.7480580652882</v>
+        <v>140.7338743698861</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3443,7 +3437,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>142.6384234026285</v>
+        <v>140.7223561375927</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3451,7 +3445,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>142.5078116625839</v>
+        <v>140.7202362233414</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3459,7 +3453,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>142.2229274670233</v>
+        <v>140.7027873935847</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3467,7 +3461,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>142.0595524747498</v>
+        <v>140.6242181817155</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3475,7 +3469,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>142.0432010277314</v>
+        <v>140.592600278182</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3483,7 +3477,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>142.0071328127048</v>
+        <v>140.5215377782133</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3491,7 +3485,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>141.8695021685581</v>
+        <v>140.4879428355272</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3499,7 +3493,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>141.8597180888004</v>
+        <v>140.4066472525871</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3507,7 +3501,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>141.8246090185509</v>
+        <v>140.3887243008513</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3515,7 +3509,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>141.5574618431674</v>
+        <v>140.3479337791913</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3523,7 +3517,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>141.4653361238993</v>
+        <v>140.3152397738445</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3531,7 +3525,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>141.3955067910537</v>
+        <v>140.2940623453687</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3539,7 +3533,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>141.3921265007975</v>
+        <v>140.0337893180906</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3547,7 +3541,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>141.3812825540914</v>
+        <v>139.922149336781</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3555,7 +3549,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>141.352312466971</v>
+        <v>139.8912902739061</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3563,23 +3557,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>141.195647437644</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" t="s">
-        <v>291</v>
-      </c>
-      <c r="B291" s="1">
-        <v>141.1550446090218</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2">
-      <c r="A292" t="s">
-        <v>292</v>
-      </c>
-      <c r="B292" s="1">
-        <v>141.1249460240842</v>
+        <v>139.6530957611951</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating.xlsx
+++ b/Screener/data/rs_rating.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
   <si>
     <t>Symbol</t>
   </si>
@@ -22,12 +22,12 @@
     <t>RS Rating</t>
   </si>
   <si>
+    <t>SLNO</t>
+  </si>
+  <si>
     <t>QDMI</t>
   </si>
   <si>
-    <t>SLNO</t>
-  </si>
-  <si>
     <t>CRBP</t>
   </si>
   <si>
@@ -37,856 +37,853 @@
     <t>EYPT</t>
   </si>
   <si>
-    <t>ABXXF</t>
-  </si>
-  <si>
     <t>SMCI</t>
   </si>
   <si>
+    <t>SSNT</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>IMNM</t>
+  </si>
+  <si>
+    <t>LBPH</t>
+  </si>
+  <si>
     <t>DAVE</t>
   </si>
   <si>
-    <t>LBPH</t>
-  </si>
-  <si>
-    <t>SSNT</t>
-  </si>
-  <si>
-    <t>IMNM</t>
+    <t>NPCE</t>
   </si>
   <si>
     <t>DWACU</t>
   </si>
   <si>
-    <t>NPCE</t>
-  </si>
-  <si>
     <t>DWAC</t>
   </si>
   <si>
+    <t>IMGN</t>
+  </si>
+  <si>
+    <t>HARP</t>
+  </si>
+  <si>
+    <t>AFRM</t>
+  </si>
+  <si>
     <t>ELTK</t>
   </si>
   <si>
-    <t>IMGN</t>
-  </si>
-  <si>
-    <t>HARP</t>
+    <t>EWTX</t>
   </si>
   <si>
     <t>MGNX</t>
   </si>
   <si>
-    <t>AFRM</t>
-  </si>
-  <si>
     <t>ANF</t>
   </si>
   <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>SLN</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>ML</t>
   </si>
   <si>
-    <t>EWTX</t>
-  </si>
-  <si>
-    <t>ALPN</t>
-  </si>
-  <si>
-    <t>SLN</t>
-  </si>
-  <si>
-    <t>NERV</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>MOR</t>
+    <t>PRAX</t>
   </si>
   <si>
     <t>PHVS</t>
   </si>
   <si>
-    <t>PRAX</t>
-  </si>
-  <si>
     <t>YMAB</t>
   </si>
   <si>
     <t>BHVN</t>
   </si>
   <si>
-    <t>ORTX</t>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>HA</t>
   </si>
   <si>
     <t>RXST</t>
   </si>
   <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>SMID</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>LQDA</t>
+  </si>
+  <si>
+    <t>CYTK</t>
+  </si>
+  <si>
+    <t>ALXO</t>
+  </si>
+  <si>
+    <t>KAMN</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>ATXS</t>
+  </si>
+  <si>
+    <t>ORIC</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>TNGX</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>OSCR</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
     <t>FDMT</t>
   </si>
   <si>
-    <t>HA</t>
-  </si>
-  <si>
-    <t>ARVN</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>GRPN</t>
-  </si>
-  <si>
-    <t>ALXO</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>CYTK</t>
-  </si>
-  <si>
-    <t>SMID</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>OSCR</t>
-  </si>
-  <si>
-    <t>KAMN</t>
-  </si>
-  <si>
-    <t>TNGX</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>ATXS</t>
+    <t>VKTX</t>
   </si>
   <si>
     <t>VSTM</t>
   </si>
   <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>AMR</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>ORIC</t>
-  </si>
-  <si>
     <t>DYN</t>
   </si>
   <si>
-    <t>RYTM</t>
-  </si>
-  <si>
     <t>BVN</t>
   </si>
   <si>
-    <t>VKTX</t>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>ESTC</t>
   </si>
   <si>
     <t>KURA</t>
   </si>
   <si>
-    <t>MARA</t>
+    <t>INBX</t>
+  </si>
+  <si>
+    <t>SKYW</t>
   </si>
   <si>
     <t>GEOS</t>
   </si>
   <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>ETHE</t>
+    <t>ICVX</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>UTI</t>
+  </si>
+  <si>
+    <t>KDSKF</t>
   </si>
   <si>
     <t>HOV</t>
   </si>
   <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>TATT</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>CGEM</t>
+  </si>
+  <si>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>BBIO</t>
+  </si>
+  <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
     <t>SWTX</t>
   </si>
   <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>LQDA</t>
-  </si>
-  <si>
-    <t>INBX</t>
-  </si>
-  <si>
-    <t>UTI</t>
-  </si>
-  <si>
-    <t>KDSKF</t>
-  </si>
-  <si>
-    <t>ESTC</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>ICVX</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>CGEM</t>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>ELF</t>
   </si>
   <si>
     <t>OLMA</t>
   </si>
   <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>TATT</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>FFNW</t>
+    <t>COHR</t>
   </si>
   <si>
     <t>WEAV</t>
   </si>
   <si>
-    <t>PLTR</t>
-  </si>
-  <si>
-    <t>SMLR</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>BBIO</t>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>SRRK</t>
+  </si>
+  <si>
+    <t>XMTR</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>CRNX</t>
+  </si>
+  <si>
+    <t>TAYD</t>
+  </si>
+  <si>
+    <t>KEQU</t>
+  </si>
+  <si>
+    <t>ZS</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>ACU</t>
   </si>
   <si>
     <t>GTBIF</t>
   </si>
   <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>KEQU</t>
-  </si>
-  <si>
-    <t>XPO</t>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>KRTX</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>HMST</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>METC</t>
+  </si>
+  <si>
+    <t>EVER</t>
+  </si>
+  <si>
+    <t>KYMR</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>TAL</t>
+  </si>
+  <si>
+    <t>KALV</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>UPST</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>STNE</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>INMB</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>TOPS</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>CERE</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>RVIV</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>JSPR</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>PCVX</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>RCKT</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>PRCT</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>SILXY</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>PTVE</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>IRWD</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>PAGS</t>
+  </si>
+  <si>
+    <t>PVH</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>RAMP</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>HCI</t>
+  </si>
+  <si>
+    <t>SGC</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>ISTR</t>
+  </si>
+  <si>
+    <t>ELAN</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>NGMS</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>NSSC</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>SEMR</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>CELC</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>LUNG</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>RAPT</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>AXSM</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>KCLI</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>EOLS</t>
+  </si>
+  <si>
+    <t>BXC</t>
+  </si>
+  <si>
+    <t>UCTT</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>SONO</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>ICHR</t>
   </si>
   <si>
     <t>TGI</t>
   </si>
   <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>BASE</t>
-  </si>
-  <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>SNAP</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>CRNX</t>
-  </si>
-  <si>
-    <t>XMTR</t>
-  </si>
-  <si>
-    <t>SRRK</t>
-  </si>
-  <si>
-    <t>FLXS</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>KRTX</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>METC</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>HMST</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>TAL</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>ZS</t>
-  </si>
-  <si>
-    <t>KYMR</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>HBB</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>EVER</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>TOPS</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>HCI</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>STNE</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>CERE</t>
-  </si>
-  <si>
-    <t>SGC</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>PCVX</t>
-  </si>
-  <si>
-    <t>WING</t>
-  </si>
-  <si>
-    <t>INMB</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>INFA</t>
-  </si>
-  <si>
-    <t>GFF</t>
-  </si>
-  <si>
-    <t>TREE</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>GHM</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>PTVE</t>
-  </si>
-  <si>
-    <t>PGTI</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>REVG</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>PRCT</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>CELC</t>
-  </si>
-  <si>
-    <t>PVH</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>PAGS</t>
-  </si>
-  <si>
-    <t>MAC</t>
-  </si>
-  <si>
-    <t>RCKT</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>IRWD</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>CYBR</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>APLS</t>
-  </si>
-  <si>
-    <t>IGMS</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>GIII</t>
-  </si>
-  <si>
-    <t>RVIV</t>
-  </si>
-  <si>
-    <t>ELAN</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>BPMC</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>UPST</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>NSSC</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>PATH</t>
-  </si>
-  <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>EOLS</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>RNA</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>SILXY</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>GLP</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>ASND</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>HCC</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>CTLT</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>AVDL</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>PLAY</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>NGMS</t>
-  </si>
-  <si>
-    <t>LUNG</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>MCAFU</t>
-  </si>
-  <si>
-    <t>PDD</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>AXSM</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>GLOB</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>BXC</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>DDOG</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
     <t>JBI</t>
   </si>
   <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>AROC</t>
+    <t>PBPB</t>
   </si>
   <si>
     <t>HUBS</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>NRDS</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>KCLI</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>BBU</t>
-  </si>
-  <si>
-    <t>RAPT</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>ASML</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1253,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>908.7912217663702</v>
+        <v>934.8782548859415</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1261,7 +1258,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>905.2668799999808</v>
+        <v>908.7912217663702</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1269,7 +1266,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>493.0720596181145</v>
+        <v>484.8109172676715</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1277,7 +1274,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>477.6616777867947</v>
+        <v>479.8797575430892</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1285,7 +1282,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>424.856596861924</v>
+        <v>453.4736217065869</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1293,7 +1290,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>420.681525474861</v>
+        <v>411.4682431467907</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1301,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>407.7163546963077</v>
+        <v>373.0880561011052</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1309,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>379.7799497496395</v>
+        <v>369.9886341675686</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1317,7 +1314,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>368.0638924738453</v>
+        <v>346.9734958381898</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1325,7 +1322,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>358.6819966528938</v>
+        <v>346.8778488041254</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1333,7 +1330,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>351.6137868017577</v>
+        <v>346.4034278395532</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1341,7 +1338,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>326.4791048553328</v>
+        <v>317.5966150690599</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1349,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>308.8951733568072</v>
+        <v>303.0269338243567</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1357,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>304.3751755625669</v>
+        <v>302.869521417032</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1365,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>298.5059009332023</v>
+        <v>295.2864664072454</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1373,7 +1370,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>295.4987702265349</v>
+        <v>289.5596059955211</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1381,7 +1378,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>295.2167500231912</v>
+        <v>285.0267012315452</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1389,7 +1386,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>292.3424326771536</v>
+        <v>273.2343559846176</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1397,7 +1394,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>277.0475960471111</v>
+        <v>272.0134615455278</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1405,7 +1402,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>275.6193837541316</v>
+        <v>267.8523363533247</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1413,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>270.5180171814354</v>
+        <v>267.6839556170489</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1421,7 +1418,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>266.6819893145033</v>
+        <v>263.4822667343354</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1429,7 +1426,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>264.0790129811433</v>
+        <v>258.8722476973564</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1437,7 +1434,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>258.5638091863702</v>
+        <v>258.799322756697</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1445,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>257.8412114693667</v>
+        <v>257.1521244203529</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1453,7 +1450,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>256.6346285651784</v>
+        <v>255.3993910210998</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1461,7 +1458,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>252.7092844769693</v>
+        <v>252.8957894665716</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1469,7 +1466,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>250.3335096105171</v>
+        <v>243.527956973175</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1477,7 +1474,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>247.1385204298113</v>
+        <v>239.9427649652455</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1485,7 +1482,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>246.1857370874881</v>
+        <v>234.3270545628249</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1493,7 +1490,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>240.1062860451932</v>
+        <v>231.4271624157234</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1501,7 +1498,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>237.8397637545987</v>
+        <v>227.7233528522736</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1509,7 +1506,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>230.9126927076888</v>
+        <v>223.604981748346</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1517,7 +1514,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>228.5996114716274</v>
+        <v>222.9255021378353</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1525,7 +1522,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>227.1759440294535</v>
+        <v>221.9204784635743</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1533,7 +1530,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>223.7340032827599</v>
+        <v>221.525131023993</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1541,7 +1538,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>222.6266023083127</v>
+        <v>221.4477906112913</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1549,7 +1546,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>221.5528724592597</v>
+        <v>217.7590170770551</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1557,7 +1554,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>220.5531174954706</v>
+        <v>213.9219332308575</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1565,7 +1562,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>219.438068640107</v>
+        <v>213.2051849462182</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1573,7 +1570,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>218.8347601855529</v>
+        <v>212.0900190663449</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1581,7 +1578,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>218.2118222238326</v>
+        <v>211.9779871842872</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1589,7 +1586,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>217.9503332719103</v>
+        <v>209.4647289862687</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1597,7 +1594,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>217.0362125476458</v>
+        <v>208.4083230256585</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1605,7 +1602,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>213.7477036063101</v>
+        <v>208.3368367788274</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1613,7 +1610,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>213.1507441463855</v>
+        <v>206.6095097880959</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1621,7 +1618,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>209.9695953210488</v>
+        <v>204.9269239010539</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1629,7 +1626,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>208.1451839088261</v>
+        <v>204.7111038757216</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1637,7 +1634,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>206.5330704792872</v>
+        <v>204.0869926100391</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1645,7 +1642,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>204.8617785410724</v>
+        <v>203.5356009403062</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1653,7 +1650,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>203.4819157835435</v>
+        <v>203.3955798012686</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1661,7 +1658,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>202.9374067753691</v>
+        <v>202.7496482339283</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1669,7 +1666,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>201.7296028393139</v>
+        <v>202.5160570697104</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1677,7 +1674,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>201.6445587836949</v>
+        <v>200.7496636070472</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1685,7 +1682,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>201.5034523222189</v>
+        <v>199.986186316974</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1693,7 +1690,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>200.7447052941775</v>
+        <v>199.4696867247688</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1701,7 +1698,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>200.5296411884413</v>
+        <v>198.6577364790614</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1709,7 +1706,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>199.4324484379049</v>
+        <v>197.9623433623224</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1717,7 +1714,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>198.8728249573693</v>
+        <v>197.9022318023913</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1725,7 +1722,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>198.083321469365</v>
+        <v>197.2597654925958</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1733,7 +1730,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>196.848230453552</v>
+        <v>195.1408495305553</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1741,7 +1738,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>195.986621322418</v>
+        <v>194.8599259489743</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1749,7 +1746,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>195.9029087253826</v>
+        <v>194.5429852590242</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1757,7 +1754,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>194.5044310803137</v>
+        <v>193.4899556246448</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1765,7 +1762,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>194.0765726536429</v>
+        <v>193.3919520972929</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1773,7 +1770,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>192.9974349731226</v>
+        <v>193.2620312938286</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1781,7 +1778,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>192.9429731779465</v>
+        <v>190.4560379797102</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1789,7 +1786,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>192.8740395988657</v>
+        <v>189.5206810219656</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1797,7 +1794,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>191.6397347208299</v>
+        <v>189.1928275008968</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1805,7 +1802,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>191.5827791466122</v>
+        <v>188.6169341793273</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1813,7 +1810,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>190.6870164547751</v>
+        <v>188.502933770453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1821,7 +1818,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>190.39409402136</v>
+        <v>187.846637105031</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1829,7 +1826,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>189.9683110935702</v>
+        <v>187.4966372690067</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1837,7 +1834,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>188.5520062152269</v>
+        <v>186.7072711899011</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1845,7 +1842,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>188.181798290788</v>
+        <v>185.6552170098175</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1853,7 +1850,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>187.0863178393401</v>
+        <v>184.9049256728647</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1861,7 +1858,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>186.7351567085502</v>
+        <v>184.701264163496</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1869,7 +1866,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>186.165989802147</v>
+        <v>182.5973955474412</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1877,7 +1874,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>183.820804584267</v>
+        <v>182.4089105241668</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1885,7 +1882,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>182.6899127651311</v>
+        <v>181.2181988979145</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1893,7 +1890,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>182.4912045860048</v>
+        <v>180.3569519124598</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1901,7 +1898,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>181.7733563393141</v>
+        <v>180.0358809490808</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1909,7 +1906,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>181.7483861389782</v>
+        <v>179.4991702974295</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1917,7 +1914,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>181.5255096507394</v>
+        <v>178.6253678430774</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1925,7 +1922,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>181.286022979877</v>
+        <v>178.4632289635751</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1933,7 +1930,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>181.233784960844</v>
+        <v>178.0935820151557</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1941,7 +1938,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>180.7548671398999</v>
+        <v>177.4402189446547</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1949,7 +1946,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>179.3718973222179</v>
+        <v>177.1618729452253</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1957,7 +1954,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>179.3677381151317</v>
+        <v>176.5538204856765</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1965,7 +1962,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>179.3001316562137</v>
+        <v>176.016281847991</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1973,7 +1970,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>177.4296863123832</v>
+        <v>175.8370174391085</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1981,7 +1978,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>177.0596889951125</v>
+        <v>175.4787516333829</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1989,7 +1986,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>176.9623305501541</v>
+        <v>175.3142541678004</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1997,7 +1994,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>174.653737137838</v>
+        <v>174.9485683731108</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2005,7 +2002,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>173.249068460571</v>
+        <v>174.6741798174269</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2013,7 +2010,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>173.2438441412305</v>
+        <v>174.5821541344844</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2021,7 +2018,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>173.234635727267</v>
+        <v>174.3361796379824</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2029,7 +2026,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>172.4859751604972</v>
+        <v>173.4581572376241</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2037,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>172.0420516397117</v>
+        <v>173.3671690905132</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2045,7 +2042,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>171.867511498237</v>
+        <v>172.1779439419554</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2053,7 +2050,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>171.718531106384</v>
+        <v>172.0584293511174</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2061,7 +2058,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>171.6794911716305</v>
+        <v>171.2871851891295</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2069,7 +2066,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>171.1040398619434</v>
+        <v>171.0603663953062</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2077,7 +2074,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>170.6121600424204</v>
+        <v>170.9659253934831</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2085,7 +2082,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>170.4905342225329</v>
+        <v>170.766045039202</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2093,7 +2090,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>170.4392960635624</v>
+        <v>170.607252188801</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2101,7 +2098,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>169.4889797263162</v>
+        <v>169.8968677930725</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2109,7 +2106,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>169.2925320937576</v>
+        <v>169.8613809676836</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2117,7 +2114,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>169.0998326218865</v>
+        <v>169.8375569753863</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2125,7 +2122,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>168.356583962791</v>
+        <v>169.270335927613</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2133,7 +2130,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>167.9438339637532</v>
+        <v>168.9926329255467</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2141,7 +2138,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>167.5950549636715</v>
+        <v>168.8941902229274</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2149,7 +2146,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>166.9664700147367</v>
+        <v>168.4214225039869</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2157,7 +2154,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>166.6748315727897</v>
+        <v>168.3562195607036</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2165,7 +2162,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>166.0629130157534</v>
+        <v>167.5936904765755</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2173,7 +2170,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>165.8983357299042</v>
+        <v>167.4910172351528</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2181,7 +2178,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>165.8416494511974</v>
+        <v>167.4675951206975</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2189,7 +2186,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>165.7422389680055</v>
+        <v>167.1796227903264</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2197,7 +2194,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>165.6255210818939</v>
+        <v>166.652457595364</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2205,7 +2202,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>165.4372277498547</v>
+        <v>166.0930245040968</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2213,7 +2210,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>165.3409752398918</v>
+        <v>165.2674445894488</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2221,7 +2218,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>164.6032836744267</v>
+        <v>164.5782747420864</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2229,7 +2226,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>164.5209642648639</v>
+        <v>164.2012881450587</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2237,7 +2234,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>164.299472130041</v>
+        <v>164.1982499827802</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2245,7 +2242,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>164.2845385036366</v>
+        <v>163.6188994323068</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2253,7 +2250,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>164.1897007384462</v>
+        <v>163.0319753604669</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2261,7 +2258,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>163.8943090780857</v>
+        <v>162.980507994866</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2269,7 +2266,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>163.5716640142317</v>
+        <v>162.780717602906</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2277,7 +2274,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>163.5419853936843</v>
+        <v>162.6086718438089</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2285,7 +2282,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>163.4282725838131</v>
+        <v>162.574022189175</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2293,7 +2290,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>163.3328044415179</v>
+        <v>162.5498681534556</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2301,7 +2298,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>163.3252659247349</v>
+        <v>162.4466252169987</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2309,7 +2306,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>163.0586782754258</v>
+        <v>162.2004934887105</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2317,7 +2314,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>162.8128236497196</v>
+        <v>161.9353965753859</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2325,7 +2322,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>162.6958960005175</v>
+        <v>161.2394527382269</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2333,7 +2330,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>161.9916128288806</v>
+        <v>161.1917936512429</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2341,7 +2338,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>161.9899667912639</v>
+        <v>160.9919069898439</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2349,7 +2346,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>161.2294979821162</v>
+        <v>159.8690655975161</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2357,7 +2354,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>160.8587239761485</v>
+        <v>159.479437203264</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2365,7 +2362,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>160.445697519318</v>
+        <v>159.2932706766657</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2373,7 +2370,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>160.2302169270669</v>
+        <v>159.0485726235478</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2381,7 +2378,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>160.1680632069824</v>
+        <v>158.9779962345624</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2389,7 +2386,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>158.8736077281749</v>
+        <v>158.835736162088</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2397,7 +2394,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>158.7165641571219</v>
+        <v>158.7515049411051</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2405,7 +2402,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>158.6798690658427</v>
+        <v>158.4518109165045</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2413,7 +2410,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>158.6521908445361</v>
+        <v>158.076884107914</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2421,7 +2418,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>158.5638612014836</v>
+        <v>158.0246130163858</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2429,7 +2426,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>158.2823764392229</v>
+        <v>157.6411580304059</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2437,7 +2434,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>157.7581563303898</v>
+        <v>157.5819790571595</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2445,7 +2442,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>157.7514253662565</v>
+        <v>157.579409200929</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2453,7 +2450,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>157.4605935378798</v>
+        <v>157.4571763231282</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2461,7 +2458,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>157.2875451551041</v>
+        <v>156.9959857367188</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2469,7 +2466,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>157.2802431574566</v>
+        <v>156.8680274775821</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2477,7 +2474,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>157.2668606983209</v>
+        <v>156.7681885130417</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2485,7 +2482,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>156.7873745547421</v>
+        <v>156.5528982495269</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2493,7 +2490,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>156.5049878114011</v>
+        <v>156.4472037290332</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2501,7 +2498,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>156.4218136963471</v>
+        <v>156.325945408044</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2509,7 +2506,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>156.2479860819071</v>
+        <v>156.050235804983</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2517,7 +2514,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>156.0008221007946</v>
+        <v>155.5527992580489</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2525,7 +2522,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>155.4590990658935</v>
+        <v>155.5509132931111</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2533,7 +2530,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>155.2101952222008</v>
+        <v>155.030831829664</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2541,7 +2538,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>155.1354830424837</v>
+        <v>154.9578093084084</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2549,7 +2546,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>155.021270222429</v>
+        <v>154.708556549184</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2557,7 +2554,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>154.9596976669849</v>
+        <v>154.7061182974564</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2565,7 +2562,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>154.8003579312085</v>
+        <v>154.6582857190961</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2573,7 +2570,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>154.4799850404722</v>
+        <v>154.6159922814782</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2581,7 +2578,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>154.4598167148422</v>
+        <v>154.5339377643868</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2589,7 +2586,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>154.3984895615965</v>
+        <v>154.3187756622949</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2597,7 +2594,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>154.1924220698564</v>
+        <v>153.8803250943895</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2605,7 +2602,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>153.9544454479188</v>
+        <v>153.8025706256185</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2613,7 +2610,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>153.8589642083325</v>
+        <v>153.719325224501</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2621,7 +2618,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>153.7240091063105</v>
+        <v>153.1882174078707</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2629,7 +2626,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>153.6127278972879</v>
+        <v>153.0892743973388</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2637,7 +2634,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>153.5591556202522</v>
+        <v>153.0245009972395</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2645,7 +2642,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>153.3853241080314</v>
+        <v>153.0201644598322</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2653,7 +2650,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>153.1836403116247</v>
+        <v>152.9557200419964</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2661,7 +2658,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>152.8896849794769</v>
+        <v>152.8200729782021</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2669,7 +2666,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>152.7840169006321</v>
+        <v>152.7325189487613</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2677,7 +2674,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>152.5000038296527</v>
+        <v>152.6470998497351</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2685,7 +2682,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>152.4065744640128</v>
+        <v>152.5433366420013</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2693,7 +2690,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>152.0958307217325</v>
+        <v>152.4769468693942</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2701,7 +2698,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>151.9522672973073</v>
+        <v>152.447642425329</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2709,7 +2706,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>151.8978280933796</v>
+        <v>151.985482495454</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2717,7 +2714,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>151.7360453933968</v>
+        <v>151.9233217012739</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2725,7 +2722,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>151.5066458366682</v>
+        <v>151.8078812527567</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2733,7 +2730,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>151.4494213981275</v>
+        <v>151.6909749333479</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2741,7 +2738,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>150.7347914333031</v>
+        <v>151.6864860281966</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2749,7 +2746,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>150.7335135869096</v>
+        <v>151.3621726051368</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -2757,7 +2754,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>150.6529895448531</v>
+        <v>151.2796321509528</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -2765,7 +2762,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>150.4526906271532</v>
+        <v>151.0350609826563</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -2773,7 +2770,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>150.3215905496588</v>
+        <v>150.91273972094</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -2781,7 +2778,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>150.1617130469193</v>
+        <v>150.795588681398</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -2789,7 +2786,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>150.0661202942072</v>
+        <v>150.1793738858038</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -2797,7 +2794,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>149.9251124868075</v>
+        <v>149.9088082548701</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -2805,7 +2802,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>149.7431933485869</v>
+        <v>149.8872200128124</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -2813,7 +2810,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>149.6795335767263</v>
+        <v>149.7748413973676</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -2821,7 +2818,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>149.5409923259809</v>
+        <v>149.6541160109738</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -2829,7 +2826,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>149.2996725001151</v>
+        <v>149.4003472650797</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -2837,7 +2834,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>149.1812593158147</v>
+        <v>149.1664677181303</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -2845,7 +2842,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>149.0447669368554</v>
+        <v>149.1268164827431</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -2853,7 +2850,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>149.0175382697626</v>
+        <v>149.1239545304081</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -2861,7 +2858,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>148.8186333992895</v>
+        <v>148.8551933661014</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -2869,7 +2866,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>148.3540700897598</v>
+        <v>148.750483869228</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -2877,7 +2874,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>148.2548328183105</v>
+        <v>148.6827515530919</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -2885,7 +2882,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>148.2423669444086</v>
+        <v>148.6238509362301</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -2893,7 +2890,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>147.9933362178913</v>
+        <v>148.5663376754773</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -2901,7 +2898,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>147.6156749865324</v>
+        <v>148.5168092526375</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -2909,7 +2906,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>147.603726717502</v>
+        <v>148.4733652455437</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -2917,7 +2914,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>147.4141571078422</v>
+        <v>148.3694488540571</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -2925,7 +2922,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>147.2856644784053</v>
+        <v>147.930531554941</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -2933,7 +2930,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>147.212924267739</v>
+        <v>147.871641736685</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -2941,7 +2938,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>147.2094960583713</v>
+        <v>147.8504369768162</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -2949,7 +2946,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>146.9600774537036</v>
+        <v>147.7960642641501</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -2957,7 +2954,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>146.9520880562261</v>
+        <v>147.6871287442297</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -2965,7 +2962,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>146.9036186674779</v>
+        <v>147.5343231512931</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -2973,7 +2970,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>146.8774997206254</v>
+        <v>147.5169848530857</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -2981,7 +2978,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>146.6987558277348</v>
+        <v>147.0523503049426</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -2989,7 +2986,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>146.6259352483625</v>
+        <v>146.8168534347756</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -2997,7 +2994,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>146.6183651325876</v>
+        <v>146.4680089625342</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3005,7 +3002,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>146.4132307226488</v>
+        <v>146.2917563733228</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3013,7 +3010,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>146.3188686891746</v>
+        <v>146.1318147927895</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3021,7 +3018,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>146.3112679119817</v>
+        <v>146.1251380339361</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3029,7 +3026,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>146.2332852774141</v>
+        <v>146.0388239138205</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3037,7 +3034,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>146.0942816152871</v>
+        <v>146.0266673451217</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3045,7 +3042,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>145.971045812894</v>
+        <v>145.6346895884372</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3053,7 +3050,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>145.8590999687898</v>
+        <v>145.443152886625</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3061,7 +3058,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>145.5774203824675</v>
+        <v>145.3374456687508</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3069,7 +3066,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>145.0865177259149</v>
+        <v>145.2382009319672</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3077,7 +3074,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>144.952068435708</v>
+        <v>145.1363248026461</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3085,7 +3082,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>144.8882599061112</v>
+        <v>144.9636868688467</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3093,7 +3090,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>144.8667847520384</v>
+        <v>144.7886807360162</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3101,7 +3098,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>144.8618249031144</v>
+        <v>144.7062246594947</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3109,7 +3106,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>144.4905926773867</v>
+        <v>144.3267483970436</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3117,7 +3114,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>144.0657167193846</v>
+        <v>144.280360366322</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3125,7 +3122,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>143.9982531754078</v>
+        <v>144.223848067249</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3133,7 +3130,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>143.7982039199218</v>
+        <v>144.0857984905842</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3141,7 +3138,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>143.7421078393399</v>
+        <v>143.8967274131594</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3149,7 +3146,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>143.6973612435422</v>
+        <v>143.6394382908269</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3157,7 +3154,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>143.653457341824</v>
+        <v>143.4036457148802</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3165,7 +3162,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>143.5540661844574</v>
+        <v>143.3463264956307</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3173,7 +3170,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>143.2293761855781</v>
+        <v>143.250320339498</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3181,7 +3178,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>143.1840990665836</v>
+        <v>143.1687404662949</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3189,7 +3186,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>143.0428322123164</v>
+        <v>143.1115390138919</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3197,7 +3194,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>142.98157191454</v>
+        <v>143.1047247674147</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3205,7 +3202,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>142.9617644221845</v>
+        <v>143.0656284460898</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3213,7 +3210,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>142.6821850632933</v>
+        <v>143.0493121489616</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3221,7 +3218,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>142.4620052165698</v>
+        <v>143.0406118072495</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3229,7 +3226,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>142.264552832483</v>
+        <v>142.9066703025737</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3237,7 +3234,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>142.2536700390305</v>
+        <v>142.9043505252912</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3245,7 +3242,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>142.2354397636507</v>
+        <v>142.7287065106385</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3253,7 +3250,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>142.2198391896674</v>
+        <v>142.6530834550017</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3261,7 +3258,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>142.2140883082893</v>
+        <v>142.4489648686566</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3269,7 +3266,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>142.0806413469289</v>
+        <v>142.4065938471842</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3277,7 +3274,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>142.0068910045252</v>
+        <v>142.3712256566654</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3285,7 +3282,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>141.8640668603788</v>
+        <v>142.3130553113594</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3293,7 +3290,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>141.8530593454739</v>
+        <v>142.3048770110966</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3301,7 +3298,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>141.8353731610912</v>
+        <v>142.2877876875739</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3309,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>141.700408132966</v>
+        <v>142.2338235167947</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3317,7 +3314,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>141.5121359789245</v>
+        <v>142.1797408581503</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3325,7 +3322,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>141.5057186020516</v>
+        <v>142.1496068472844</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3333,7 +3330,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>141.5031613548059</v>
+        <v>142.1236756040729</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3341,7 +3338,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>141.4975196081877</v>
+        <v>142.0117869507092</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3349,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>141.4753882338552</v>
+        <v>141.9881215783784</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3357,7 +3354,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>141.4579332944129</v>
+        <v>141.9848036476675</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3365,7 +3362,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>141.3722306764255</v>
+        <v>141.9484793331816</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3373,7 +3370,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>141.313922352134</v>
+        <v>141.8708091249966</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3381,7 +3378,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>141.3082040535338</v>
+        <v>141.8018865832952</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3389,7 +3386,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>141.2707086017318</v>
+        <v>141.6745245593798</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3397,7 +3394,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>141.177758720168</v>
+        <v>141.6206105667051</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3405,7 +3402,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>141.0801897552028</v>
+        <v>141.5884957304038</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3413,7 +3410,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>140.9414581411094</v>
+        <v>141.588341114136</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3421,7 +3418,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>140.7440044475105</v>
+        <v>141.4568967138333</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3429,7 +3426,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>140.7338743698861</v>
+        <v>141.4266602874378</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3437,7 +3434,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>140.7223561375927</v>
+        <v>141.399142495002</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3445,7 +3442,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>140.7202362233414</v>
+        <v>141.3586118341758</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3453,7 +3450,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>140.7027873935847</v>
+        <v>141.3350482919594</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3461,7 +3458,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>140.6242181817155</v>
+        <v>141.2709807677481</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3469,7 +3466,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>140.592600278182</v>
+        <v>140.9831002662939</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3477,7 +3474,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>140.5215377782133</v>
+        <v>140.9394143024886</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3485,7 +3482,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>140.4879428355272</v>
+        <v>140.8921677028563</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3493,7 +3490,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>140.4066472525871</v>
+        <v>140.8839384824993</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3501,7 +3498,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>140.3887243008513</v>
+        <v>140.8679289132309</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3509,7 +3506,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>140.3479337791913</v>
+        <v>140.5923165255903</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3517,7 +3514,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>140.3152397738445</v>
+        <v>140.424816028242</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3525,7 +3522,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>140.2940623453687</v>
+        <v>140.4052480689024</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3533,7 +3530,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>140.0337893180906</v>
+        <v>140.2930427554761</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3541,7 +3538,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>139.922149336781</v>
+        <v>140.2008691236458</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3549,15 +3546,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>139.8912902739061</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290" t="s">
-        <v>290</v>
-      </c>
-      <c r="B290" s="1">
-        <v>139.6530957611951</v>
+        <v>140.0346396560749</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating.xlsx
+++ b/Screener/data/rs_rating.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
   <si>
     <t>Symbol</t>
   </si>
@@ -34,12 +34,12 @@
     <t>AAOI</t>
   </si>
   <si>
+    <t>CRBP</t>
+  </si>
+  <si>
     <t>EYPT</t>
   </si>
   <si>
-    <t>CRBP</t>
-  </si>
-  <si>
     <t>SSNT</t>
   </si>
   <si>
@@ -49,138 +49,138 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>DAVE</t>
+  </si>
+  <si>
     <t>LBPH</t>
   </si>
   <si>
-    <t>DAVE</t>
-  </si>
-  <si>
     <t>IMNM</t>
   </si>
   <si>
     <t>IMGN</t>
   </si>
   <si>
+    <t>MARA</t>
+  </si>
+  <si>
     <t>ANF</t>
   </si>
   <si>
-    <t>MARA</t>
-  </si>
-  <si>
     <t>DWACU</t>
   </si>
   <si>
     <t>CVNA</t>
   </si>
   <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>MGNX</t>
+  </si>
+  <si>
     <t>YMAB</t>
   </si>
   <si>
-    <t>DWAC</t>
-  </si>
-  <si>
-    <t>MGNX</t>
-  </si>
-  <si>
-    <t>MOR</t>
+    <t>CBAY</t>
   </si>
   <si>
     <t>HARP</t>
   </si>
   <si>
-    <t>CBAY</t>
+    <t>ML</t>
   </si>
   <si>
     <t>ALPN</t>
   </si>
   <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>NPCE</t>
+  </si>
+  <si>
     <t>SLN</t>
   </si>
   <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>NPCE</t>
-  </si>
-  <si>
-    <t>VRT</t>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>OSCR</t>
   </si>
   <si>
     <t>VKTX</t>
   </si>
   <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>OSCR</t>
+    <t>AFRM</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>MOD</t>
   </si>
   <si>
     <t>EWTX</t>
   </si>
   <si>
-    <t>BHVN</t>
-  </si>
-  <si>
-    <t>AFRM</t>
-  </si>
-  <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>MOD</t>
+    <t>ALXO</t>
+  </si>
+  <si>
+    <t>ELTK</t>
+  </si>
+  <si>
+    <t>RXST</t>
   </si>
   <si>
     <t>PRAX</t>
   </si>
   <si>
-    <t>ELTK</t>
-  </si>
-  <si>
     <t>GRPN</t>
   </si>
   <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>ALXO</t>
-  </si>
-  <si>
     <t>CLS</t>
   </si>
   <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>CYTK</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
     <t>PHVS</t>
   </si>
   <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>CYTK</t>
-  </si>
-  <si>
-    <t>TWST</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
     <t>CAMT</t>
   </si>
   <si>
-    <t>NVDA</t>
+    <t>DYN</t>
   </si>
   <si>
     <t>XPO</t>
   </si>
   <si>
-    <t>DYN</t>
-  </si>
-  <si>
     <t>ARVN</t>
   </si>
   <si>
@@ -193,6 +193,9 @@
     <t>TAL</t>
   </si>
   <si>
+    <t>ASPN</t>
+  </si>
+  <si>
     <t>SMID</t>
   </si>
   <si>
@@ -211,511 +214,559 @@
     <t>NUVL</t>
   </si>
   <si>
+    <t>IDYA</t>
+  </si>
+  <si>
     <t>BVN</t>
   </si>
   <si>
+    <t>FDMT</t>
+  </si>
+  <si>
+    <t>HOV</t>
+  </si>
+  <si>
     <t>MCAFU</t>
   </si>
   <si>
-    <t>FDMT</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>IGMS</t>
-  </si>
-  <si>
-    <t>HOV</t>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>TAYD</t>
   </si>
   <si>
     <t>OLMA</t>
   </si>
   <si>
-    <t>ESTC</t>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>LMB</t>
   </si>
   <si>
     <t>KURA</t>
   </si>
   <si>
-    <t>ASPN</t>
-  </si>
-  <si>
-    <t>PLTR</t>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>JSPR</t>
   </si>
   <si>
     <t>CGEM</t>
   </si>
   <si>
-    <t>JSPR</t>
-  </si>
-  <si>
-    <t>TAYD</t>
-  </si>
-  <si>
-    <t>LMB</t>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>ICVX</t>
   </si>
   <si>
     <t>S</t>
   </si>
   <si>
-    <t>ICVX</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>RIOT</t>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>SWTX</t>
   </si>
   <si>
     <t>INBX</t>
   </si>
   <si>
-    <t>INBK</t>
+    <t>FLXS</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>DFH</t>
   </si>
   <si>
     <t>BBIO</t>
   </si>
   <si>
-    <t>FFNW</t>
+    <t>EVER</t>
   </si>
   <si>
     <t>TREE</t>
   </si>
   <si>
-    <t>FLXS</t>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>CVRX</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>KRTX</t>
+  </si>
+  <si>
+    <t>COHR</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>IESC</t>
   </si>
   <si>
     <t>KEQU</t>
   </si>
   <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>SWTX</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>CVRX</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>EVER</t>
-  </si>
-  <si>
-    <t>KRTX</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>KALV</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
     <t>GTLB</t>
   </si>
   <si>
-    <t>APP</t>
+    <t>ZS</t>
   </si>
   <si>
     <t>GFF</t>
   </si>
   <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>ZS</t>
+    <t>SRRK</t>
+  </si>
+  <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>METC</t>
   </si>
   <si>
     <t>KYMR</t>
   </si>
   <si>
-    <t>IESC</t>
+    <t>XMTR</t>
+  </si>
+  <si>
+    <t>CERE</t>
   </si>
   <si>
     <t>ARCT</t>
   </si>
   <si>
-    <t>SRRK</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>CERE</t>
-  </si>
-  <si>
-    <t>XMTR</t>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>BMA</t>
   </si>
   <si>
     <t>CMPR</t>
   </si>
   <si>
-    <t>SPOT</t>
-  </si>
-  <si>
     <t>BASE</t>
   </si>
   <si>
-    <t>MAX</t>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>GHM</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>CRNX</t>
   </si>
   <si>
     <t>FTAI</t>
   </si>
   <si>
-    <t>CRNX</t>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>VRNS</t>
   </si>
   <si>
     <t>SAIA</t>
   </si>
   <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>SMLR</t>
-  </si>
-  <si>
-    <t>DECK</t>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>MEDP</t>
   </si>
   <si>
     <t>KKR</t>
   </si>
   <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>METC</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
     <t>CYBR</t>
   </si>
   <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
     <t>AZEK</t>
   </si>
   <si>
-    <t>NET</t>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>ONTO</t>
   </si>
   <si>
     <t>URGN</t>
   </si>
   <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>HBB</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>GHM</t>
+    <t>BLD</t>
   </si>
   <si>
     <t>PATH</t>
   </si>
   <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
     <t>IMVT</t>
   </si>
   <si>
     <t>USAP</t>
   </si>
   <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>WING</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>BLD</t>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>GGAL</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>LYFT</t>
+    <t>PVH</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>PDD</t>
   </si>
   <si>
     <t>STRL</t>
   </si>
   <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>RCMT</t>
+    <t>KROS</t>
+  </si>
+  <si>
+    <t>HCI</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>RAPT</t>
   </si>
   <si>
     <t>GKOS</t>
   </si>
   <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>PVH</t>
-  </si>
-  <si>
     <t>ASND</t>
   </si>
   <si>
-    <t>PDD</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>RAPT</t>
+    <t>PRCT</t>
   </si>
   <si>
     <t>PGTI</t>
   </si>
   <si>
-    <t>PRCT</t>
-  </si>
-  <si>
-    <t>FICO</t>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>PCVX</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>MAC</t>
   </si>
   <si>
     <t>INFA</t>
   </si>
   <si>
-    <t>ESEA</t>
-  </si>
-  <si>
-    <t>PCVX</t>
-  </si>
-  <si>
-    <t>WOR</t>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>FIX</t>
   </si>
   <si>
     <t>IRWD</t>
   </si>
   <si>
-    <t>GIII</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>PLAY</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>KROS</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>BRZE</t>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>JAKK</t>
+  </si>
+  <si>
+    <t>ARES</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>ELAN</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>OWL</t>
+  </si>
+  <si>
+    <t>ICHR</t>
+  </si>
+  <si>
+    <t>AXR</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>CRSP</t>
+  </si>
+  <si>
+    <t>FSLY</t>
+  </si>
+  <si>
+    <t>RCKT</t>
   </si>
   <si>
     <t>QEPC</t>
   </si>
   <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>HCI</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>RCKT</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>CRSP</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>OWL</t>
-  </si>
-  <si>
-    <t>MAC</t>
-  </si>
-  <si>
-    <t>WIX</t>
-  </si>
-  <si>
-    <t>JAKK</t>
-  </si>
-  <si>
-    <t>ELAN</t>
-  </si>
-  <si>
-    <t>AXR</t>
-  </si>
-  <si>
-    <t>ICHR</t>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>ACMR</t>
   </si>
   <si>
     <t>TYRA</t>
   </si>
   <si>
-    <t>APO</t>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>NRDS</t>
   </si>
   <si>
     <t>MDC</t>
   </si>
   <si>
-    <t>ARES</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>NRDS</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>FROG</t>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>CG</t>
   </si>
   <si>
     <t>NVMI</t>
   </si>
   <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>MKSI</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
     <t>JBI</t>
   </si>
   <si>
-    <t>NOW</t>
-  </si>
-  <si>
     <t>STNE</t>
   </si>
   <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>OPRX</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>NSSC</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
     <t>XENE</t>
   </si>
   <si>
-    <t>ACMR</t>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>APPF</t>
   </si>
   <si>
     <t>NRP</t>
@@ -724,562 +775,583 @@
     <t>GLP</t>
   </si>
   <si>
-    <t>MKSI</t>
-  </si>
-  <si>
     <t>DDOG</t>
   </si>
   <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>EVR</t>
+  </si>
+  <si>
+    <t>DOOR</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>CELC</t>
+  </si>
+  <si>
     <t>AXSM</t>
   </si>
   <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>OPRX</t>
-  </si>
-  <si>
-    <t>DOOR</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>CELC</t>
-  </si>
-  <si>
-    <t>ESP</t>
-  </si>
-  <si>
-    <t>BPMC</t>
-  </si>
-  <si>
-    <t>TOL</t>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>FRD</t>
   </si>
   <si>
     <t>UCTT</t>
   </si>
   <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>HCC</t>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>PATK</t>
   </si>
   <si>
     <t>CELH</t>
   </si>
   <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>BXC</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>GWRE</t>
+  </si>
+  <si>
+    <t>KLAC</t>
+  </si>
+  <si>
+    <t>SILXY</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
     <t>TRIP</t>
   </si>
   <si>
-    <t>SILXY</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>EVR</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>NSSC</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>GWRE</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>BXC</t>
-  </si>
-  <si>
-    <t>KLAC</t>
-  </si>
-  <si>
     <t>TM</t>
   </si>
   <si>
-    <t>NVO</t>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>AYI</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>CVLT</t>
+  </si>
+  <si>
+    <t>PPBN</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>KAI</t>
+  </si>
+  <si>
+    <t>NS</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>AMZN</t>
   </si>
   <si>
     <t>CSWI</t>
   </si>
   <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>FRD</t>
+    <t>AWI</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>SIG</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>AFYA</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>ISTR</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>MNDY</t>
   </si>
   <si>
     <t>APLS</t>
   </si>
   <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>KAI</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>AGO</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>CVLT</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>AYI</t>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>PSN</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>KCLI</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>HIBB</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>TDG</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>AAON</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>SONO</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>NGVC</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>SCSC</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>MELI</t>
   </si>
   <si>
     <t>DLHC</t>
   </si>
   <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>AFYA</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>GDDY</t>
-  </si>
-  <si>
-    <t>AWI</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>TT</t>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>ISRG</t>
+  </si>
+  <si>
+    <t>MBIN</t>
+  </si>
+  <si>
+    <t>NSIT</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>PUBGY</t>
+  </si>
+  <si>
+    <t>CSL</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>BBU</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>ALTR</t>
+  </si>
+  <si>
+    <t>CMG</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>LEN</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>KTB</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>KDSKF</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>RYAAY</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>SPXC</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>BAH</t>
   </si>
   <si>
     <t>IMCR</t>
   </si>
   <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>PSN</t>
-  </si>
-  <si>
-    <t>SIG</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>PPBN</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>KCLI</t>
-  </si>
-  <si>
-    <t>SONO</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>ERIE</t>
-  </si>
-  <si>
-    <t>ISTR</t>
-  </si>
-  <si>
-    <t>HOLI</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>SFM</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>MLKN</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>HIBB</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>SCSC</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
-    <t>SPLK</t>
-  </si>
-  <si>
-    <t>ISRG</t>
-  </si>
-  <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>MBIN</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>CSL</t>
-  </si>
-  <si>
-    <t>KDSKF</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>AAON</t>
-  </si>
-  <si>
-    <t>ALTR</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>SPXC</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>BBU</t>
-  </si>
-  <si>
-    <t>FWRG</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>RYAAY</t>
+    <t>COLL</t>
   </si>
   <si>
     <t>EDRY</t>
   </si>
   <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>NWS</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>PUBGY</t>
-  </si>
-  <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>QTWO</t>
+    <t>REVG</t>
   </si>
   <si>
     <t>IHG</t>
   </si>
   <si>
+    <t>DFIN</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>NMM</t>
+  </si>
+  <si>
+    <t>HWM</t>
+  </si>
+  <si>
+    <t>STLA</t>
+  </si>
+  <si>
+    <t>PGPEF</t>
+  </si>
+  <si>
     <t>GLBE</t>
   </si>
   <si>
-    <t>LEN</t>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>HNI</t>
   </si>
   <si>
     <t>GLOB</t>
   </si>
   <si>
-    <t>BAH</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>DFIN</t>
-  </si>
-  <si>
-    <t>STLA</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>NMM</t>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>ALLY</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>QNST</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>QTRX</t>
   </si>
   <si>
     <t>URBN</t>
   </si>
   <si>
-    <t>NS</t>
-  </si>
-  <si>
-    <t>QNST</t>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>AZTA</t>
+  </si>
+  <si>
+    <t>AXP</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>CVCO</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>MCY</t>
   </si>
   <si>
     <t>TDW</t>
   </si>
   <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>HWM</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>DMRC</t>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>STN</t>
   </si>
   <si>
     <t>COKE</t>
   </si>
   <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>DKS</t>
+  </si>
+  <si>
     <t>CDNS</t>
   </si>
   <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>REVG</t>
-  </si>
-  <si>
-    <t>DKS</t>
-  </si>
-  <si>
-    <t>PGPEF</t>
-  </si>
-  <si>
-    <t>JXN</t>
-  </si>
-  <si>
-    <t>KTB</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>AXON</t>
-  </si>
-  <si>
-    <t>TDG</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>SAP</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>QTRX</t>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>EML</t>
+  </si>
+  <si>
+    <t>MAS</t>
+  </si>
+  <si>
+    <t>WRK</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
+    <t>MYGN</t>
+  </si>
+  <si>
+    <t>FSS</t>
+  </si>
+  <si>
+    <t>RCL</t>
   </si>
   <si>
     <t>PCAR</t>
@@ -1288,283 +1360,214 @@
     <t>GWW</t>
   </si>
   <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>FSS</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>CWCO</t>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>PJT</t>
+  </si>
+  <si>
+    <t>PIPR</t>
+  </si>
+  <si>
+    <t>JNPR</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>CTLT</t>
   </si>
   <si>
     <t>ITCI</t>
   </si>
   <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>AXP</t>
-  </si>
-  <si>
-    <t>NATR</t>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>DBX</t>
+  </si>
+  <si>
+    <t>BKNG</t>
   </si>
   <si>
     <t>SWDAF</t>
   </si>
   <si>
-    <t>CVCO</t>
-  </si>
-  <si>
-    <t>MAS</t>
-  </si>
-  <si>
-    <t>WIRE</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>M</t>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>GHLD</t>
+  </si>
+  <si>
+    <t>WDFC</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>PGR</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>ALOT</t>
+  </si>
+  <si>
+    <t>RRR</t>
+  </si>
+  <si>
+    <t>ITT</t>
   </si>
   <si>
     <t>FONR</t>
   </si>
   <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>CTLT</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>MCY</t>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>CENT</t>
+  </si>
+  <si>
+    <t>LZB</t>
+  </si>
+  <si>
+    <t>PRIM</t>
   </si>
   <si>
     <t>LRN</t>
   </si>
   <si>
-    <t>PGR</t>
-  </si>
-  <si>
-    <t>PJT</t>
-  </si>
-  <si>
-    <t>CCS</t>
-  </si>
-  <si>
-    <t>DBX</t>
-  </si>
-  <si>
-    <t>TNK</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>WDFC</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>ALLY</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>HNI</t>
-  </si>
-  <si>
-    <t>RRR</t>
-  </si>
-  <si>
-    <t>GOLF</t>
-  </si>
-  <si>
-    <t>QCOM</t>
+    <t>RCKY</t>
+  </si>
+  <si>
+    <t>GBOOY</t>
+  </si>
+  <si>
+    <t>MLM</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>RELX</t>
+  </si>
+  <si>
+    <t>UPWK</t>
+  </si>
+  <si>
+    <t>LAKE</t>
+  </si>
+  <si>
+    <t>RHP</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>DY</t>
+  </si>
+  <si>
+    <t>FMX</t>
+  </si>
+  <si>
+    <t>MGRC</t>
+  </si>
+  <si>
+    <t>SNPS</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>NX</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>FORM</t>
   </si>
   <si>
     <t>CPLP</t>
   </si>
   <si>
-    <t>JNPR</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>MYGN</t>
-  </si>
-  <si>
-    <t>MGRC</t>
-  </si>
-  <si>
-    <t>WRK</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>RAMP</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>FRPT</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>PIPR</t>
-  </si>
-  <si>
-    <t>ITT</t>
-  </si>
-  <si>
-    <t>FMX</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>MLM</t>
-  </si>
-  <si>
-    <t>CNXN</t>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>PFSI</t>
+  </si>
+  <si>
+    <t>LECO</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>RGEN</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>FOUR</t>
+  </si>
+  <si>
+    <t>NVR</t>
+  </si>
+  <si>
+    <t>FSUMF</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>LOB</t>
   </si>
   <si>
     <t>TW</t>
   </si>
   <si>
-    <t>LECO</t>
-  </si>
-  <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>CENT</t>
-  </si>
-  <si>
-    <t>ALOT</t>
-  </si>
-  <si>
-    <t>RGEN</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>BSX</t>
-  </si>
-  <si>
-    <t>WRB</t>
-  </si>
-  <si>
-    <t>FOUR</t>
-  </si>
-  <si>
-    <t>RELX</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
     <t>PTC</t>
   </si>
   <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>NBIX</t>
-  </si>
-  <si>
-    <t>STX</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>ASO</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>EML</t>
-  </si>
-  <si>
-    <t>DY</t>
-  </si>
-  <si>
-    <t>ITGR</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>PFSI</t>
-  </si>
-  <si>
-    <t>TNC</t>
-  </si>
-  <si>
-    <t>FRO</t>
-  </si>
-  <si>
-    <t>LZB</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
     <t>BWMN</t>
   </si>
   <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>KB</t>
+    <t>TRMD</t>
   </si>
 </sst>
 </file>
@@ -1915,7 +1918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1931,7 +1934,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>988.6925624573811</v>
+        <v>993.0118760204987</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1947,7 +1950,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>485.1681858483266</v>
+        <v>501.9502149887406</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1955,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>477.8565944840053</v>
+        <v>496.0769481609699</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1963,7 +1966,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>475.7214864722076</v>
+        <v>467.8637430884435</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1971,7 +1974,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>453.3079663278382</v>
+        <v>465.7367975178112</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1979,7 +1982,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>446.8893637416734</v>
+        <v>447.8968668729</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1987,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>421.2317619401599</v>
+        <v>439.7222886108577</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1995,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>407.8769852425587</v>
+        <v>405.5656454918984</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2003,7 +2006,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>362.8617270593015</v>
+        <v>357.4438141193338</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2011,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>354.0005629109638</v>
+        <v>356.5019199808208</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2019,7 +2022,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>352.7871087120664</v>
+        <v>333.605556285777</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2035,7 +2038,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>305.1971748167461</v>
+        <v>313.5987690546785</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2043,7 +2046,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>301.6348880836634</v>
+        <v>310.4030967752407</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2059,7 +2062,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>297.2245746742462</v>
+        <v>299.5753742655253</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2067,7 +2070,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>296.2165425873237</v>
+        <v>290.6358455925627</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2075,7 +2078,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>287.2316522077479</v>
+        <v>278.1506883820032</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2083,7 +2086,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>280.6052999213745</v>
+        <v>278.0890132827783</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2091,7 +2094,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>278.7889988504318</v>
+        <v>276.7357875936636</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2099,7 +2102,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>276.3822812746571</v>
+        <v>276.5832119839652</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2107,7 +2110,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>276.1104910106478</v>
+        <v>275.9520683589604</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2115,7 +2118,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>272.4570715316671</v>
+        <v>271.4837988434024</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2123,7 +2126,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>270.8570088057771</v>
+        <v>269.3136901929224</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2131,7 +2134,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>270.3646416079081</v>
+        <v>266.6536454026689</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2139,7 +2142,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>266.5859306841722</v>
+        <v>266.55833921498</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2147,7 +2150,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>265.7507036389117</v>
+        <v>264.8245589260223</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2155,7 +2158,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>258.085813537634</v>
+        <v>257.1335801553731</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2163,7 +2166,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>256.5212426209907</v>
+        <v>251.4455606825062</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2171,7 +2174,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>253.008742998519</v>
+        <v>249.4932697692256</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2179,7 +2182,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>243.4894830198728</v>
+        <v>243.2233895107867</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2187,7 +2190,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>240.3250100304624</v>
+        <v>242.4604169142983</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2195,7 +2198,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>240.1598062014093</v>
+        <v>238.2534730035777</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2203,7 +2206,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>236.6935695687039</v>
+        <v>236.9789021125949</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2211,7 +2214,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>232.0955514092255</v>
+        <v>234.4084465662514</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2219,7 +2222,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>230.7041609018078</v>
+        <v>233.6418656296866</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2227,7 +2230,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>227.4705951587198</v>
+        <v>227.9615872059833</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2235,7 +2238,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>226.5960424940856</v>
+        <v>227.0826569836406</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2243,7 +2246,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>225.2516881584424</v>
+        <v>226.8948645524051</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2251,7 +2254,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>224.2017852775953</v>
+        <v>225.9208302783726</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2259,7 +2262,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>222.7463889243043</v>
+        <v>224.5255910451171</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2267,7 +2270,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>221.6001756645421</v>
+        <v>221.0440802197559</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2275,7 +2278,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>216.5605354502228</v>
+        <v>218.1784368952755</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2283,7 +2286,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>216.5386175202743</v>
+        <v>217.3557078674006</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2291,7 +2294,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>216.2737613247429</v>
+        <v>216.8306241432174</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2299,7 +2302,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>215.1843977463423</v>
+        <v>216.7968484493946</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2307,7 +2310,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>214.9534256448916</v>
+        <v>216.0162322186133</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2315,7 +2318,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>214.4961202486153</v>
+        <v>213.4866432393798</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2323,7 +2326,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>211.8414683784935</v>
+        <v>212.8528011224376</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2331,7 +2334,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>210.4582404473535</v>
+        <v>210.9807257945843</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2339,7 +2342,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>210.1968670704278</v>
+        <v>210.9415739068598</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2347,7 +2350,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>209.1975278222959</v>
+        <v>210.9070191002552</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2355,7 +2358,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>207.2266692749721</v>
+        <v>208.1965927520661</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2363,7 +2366,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>207.1325502297678</v>
+        <v>206.9273917538011</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2371,7 +2374,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>205.0543133187482</v>
+        <v>206.7698828412172</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2379,7 +2382,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>203.2142246681316</v>
+        <v>203.7489984402841</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2387,7 +2390,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>201.4435701218528</v>
+        <v>203.5986282707769</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2395,7 +2398,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>200.7920382853256</v>
+        <v>202.6096650581405</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2403,7 +2406,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>198.7913869226044</v>
+        <v>202.1653902248305</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2411,7 +2414,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>198.7835481264903</v>
+        <v>198.7913869226044</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2419,7 +2422,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>194.501292131003</v>
+        <v>195.3466461734932</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2427,7 +2430,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>194.1100365895765</v>
+        <v>194.9099176565227</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2435,7 +2438,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>193.7255313231917</v>
+        <v>194.7807394147801</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2443,7 +2446,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>193.0507495175515</v>
+        <v>194.5602738381466</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2451,7 +2454,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>192.3698892393178</v>
+        <v>194.0961880894919</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2459,7 +2462,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>191.970580849449</v>
+        <v>193.6581544618578</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2467,7 +2470,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>190.8945057238524</v>
+        <v>193.5639206213303</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2475,7 +2478,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>190.4390244953603</v>
+        <v>193.0507495175515</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2483,7 +2486,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>189.7682261101496</v>
+        <v>191.0566652101926</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2491,7 +2494,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>188.6797799947564</v>
+        <v>187.9959544375448</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2499,7 +2502,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>188.2790759398406</v>
+        <v>187.0326268094843</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2507,7 +2510,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>187.9225951957599</v>
+        <v>186.6064542440639</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2515,7 +2518,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>186.4794391382877</v>
+        <v>186.2873070672412</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2523,7 +2526,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>185.351195696004</v>
+        <v>185.8805639487153</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2531,7 +2534,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>185.3015515254904</v>
+        <v>185.7382252009164</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2539,7 +2542,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>184.6657564714015</v>
+        <v>184.9179526679937</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2547,7 +2550,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>184.4689173224145</v>
+        <v>184.7730124910265</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2555,7 +2558,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>183.9867736832817</v>
+        <v>184.5176693170979</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2563,7 +2566,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>183.0317036414434</v>
+        <v>183.8592073261414</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2571,7 +2574,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>182.6728868515121</v>
+        <v>183.4098685618668</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2579,7 +2582,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>182.1560583177106</v>
+        <v>183.3867120389398</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2587,7 +2590,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>181.7584865029122</v>
+        <v>183.3397013248745</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2595,7 +2598,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>181.4064963671314</v>
+        <v>183.0671825424205</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2603,7 +2606,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>180.8078871130414</v>
+        <v>182.8219132933098</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2611,7 +2614,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>180.5771034380162</v>
+        <v>181.8470391845812</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2619,7 +2622,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>179.7670467701272</v>
+        <v>181.8051086802839</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2627,7 +2630,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>179.6612793064502</v>
+        <v>181.0029853824078</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2635,7 +2638,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>179.209831421821</v>
+        <v>180.2942159653385</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2643,7 +2646,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>179.0966752023361</v>
+        <v>179.8149000360741</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2651,7 +2654,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>178.8235492452122</v>
+        <v>179.6776311116332</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2659,7 +2662,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>178.6468053711486</v>
+        <v>179.0537438625254</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2667,7 +2670,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>178.2087830289996</v>
+        <v>178.3000332019203</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2675,7 +2678,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>176.7949830936809</v>
+        <v>178.2761751248962</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2683,7 +2686,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>176.0319471568773</v>
+        <v>178.1352526580611</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2691,7 +2694,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>175.8919079976162</v>
+        <v>177.3291868992648</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2699,7 +2702,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>175.8492581992975</v>
+        <v>175.8294413339237</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2707,7 +2710,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>175.686236360211</v>
+        <v>175.6194993449164</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2715,7 +2718,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>175.5289424955571</v>
+        <v>175.3450533442745</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2723,7 +2726,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>174.2980817865591</v>
+        <v>174.7980890393005</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2731,7 +2734,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>173.7323793513044</v>
+        <v>174.5292743560361</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2739,7 +2742,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>173.4516033776147</v>
+        <v>174.2665816847922</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2747,7 +2750,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>173.4460671029815</v>
+        <v>174.1995475324639</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2755,7 +2758,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>173.1288376249391</v>
+        <v>173.2192721323784</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2763,7 +2766,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>173.0384233428713</v>
+        <v>172.9227369891877</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2771,7 +2774,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>172.5270506030904</v>
+        <v>172.9087698639939</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2779,7 +2782,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>172.3463639545486</v>
+        <v>172.7060855337455</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2787,7 +2790,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>172.1695463418022</v>
+        <v>172.1386282587162</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2795,7 +2798,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>171.6783372092922</v>
+        <v>172.1173390655148</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2803,7 +2806,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>171.2448677951715</v>
+        <v>171.3112139345328</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2811,7 +2814,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>169.7956946582657</v>
+        <v>170.2580240358326</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2819,7 +2822,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>169.7670232999203</v>
+        <v>170.030228098906</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2827,7 +2830,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>169.7392513818101</v>
+        <v>169.9010348832895</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2835,7 +2838,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>169.5428417997257</v>
+        <v>169.7360061252195</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2843,7 +2846,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>168.7295205856985</v>
+        <v>169.0407875714442</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2851,7 +2854,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>168.6112432430901</v>
+        <v>167.7932685676735</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2859,7 +2862,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>167.1659479035141</v>
+        <v>167.6243860507081</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2867,7 +2870,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>167.1071805299456</v>
+        <v>167.5136713694659</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2875,7 +2878,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>165.8719430868564</v>
+        <v>167.1318797548075</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2883,7 +2886,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>165.7766193321717</v>
+        <v>166.6631694584948</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2891,7 +2894,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>165.7711134670694</v>
+        <v>166.4973290679817</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2899,7 +2902,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>165.3288170731475</v>
+        <v>166.4703427474792</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2907,7 +2910,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>165.246149762174</v>
+        <v>166.3961327747301</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2915,7 +2918,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>164.9406874658164</v>
+        <v>165.9932655528489</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2923,7 +2926,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>164.531182912196</v>
+        <v>165.9675511334461</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2931,7 +2934,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>164.2553391441961</v>
+        <v>165.6009984308646</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2939,7 +2942,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>164.0835204535442</v>
+        <v>165.5051101307496</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2947,7 +2950,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>163.9514618528974</v>
+        <v>165.1212143168495</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2955,7 +2958,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>163.5444308573669</v>
+        <v>164.847054124522</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2963,7 +2966,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>163.5003713200947</v>
+        <v>164.7126386019181</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2971,7 +2974,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>163.376476437285</v>
+        <v>164.6360362420815</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2979,7 +2982,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>163.2235954567205</v>
+        <v>164.1222674798733</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2987,7 +2990,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>163.1447459987118</v>
+        <v>164.0456553824763</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2995,7 +2998,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>162.4738096592656</v>
+        <v>163.8423051585371</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3003,7 +3006,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>162.0678690947854</v>
+        <v>163.7571677461654</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3011,7 +3014,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>161.6021677305594</v>
+        <v>163.3961473383027</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3019,7 +3022,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>161.5366298773818</v>
+        <v>163.3940173409482</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3027,7 +3030,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>160.8130031343495</v>
+        <v>162.76289294951</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3035,7 +3038,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>160.8078007090854</v>
+        <v>162.6087197992098</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3043,7 +3046,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>160.6815075932903</v>
+        <v>162.4789787535335</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3051,7 +3054,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>160.647433128752</v>
+        <v>162.4250962681461</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3059,7 +3062,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>160.5638697610584</v>
+        <v>162.0007375049034</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3067,7 +3070,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>160.540408333309</v>
+        <v>161.8057276185583</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3075,7 +3078,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>159.9746486648873</v>
+        <v>161.3276023918729</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3083,7 +3086,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>159.7652474983634</v>
+        <v>160.9174722483266</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3091,7 +3094,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>159.3579679776051</v>
+        <v>160.9036620049415</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3099,7 +3102,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>158.9750674572935</v>
+        <v>160.7637484060138</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3107,7 +3110,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>158.8072577999088</v>
+        <v>160.6397089379776</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3115,7 +3118,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>158.4962592131099</v>
+        <v>159.8370759511383</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3123,7 +3126,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>158.4494529235904</v>
+        <v>159.7736350478393</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3131,7 +3134,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>158.3052897632006</v>
+        <v>159.6733940919481</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3139,7 +3142,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>157.67024447918</v>
+        <v>159.0531376526341</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3147,7 +3150,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>157.6645286338</v>
+        <v>158.86482706354</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3155,7 +3158,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>157.4423410867657</v>
+        <v>158.5192756147213</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3163,7 +3166,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>157.0915843770556</v>
+        <v>158.4631051451589</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3171,7 +3174,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>156.8449965385727</v>
+        <v>158.3464586609861</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3179,7 +3182,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>156.7766789220792</v>
+        <v>158.2882074408374</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3187,7 +3190,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>156.7729745098877</v>
+        <v>158.2635046526287</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3195,7 +3198,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>156.6252669964713</v>
+        <v>158.130916238728</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3203,7 +3206,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>156.4567446799173</v>
+        <v>157.8416653006802</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3211,7 +3214,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>156.1030645821303</v>
+        <v>157.7112852777196</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3219,7 +3222,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>156.0237275961915</v>
+        <v>157.5148235622562</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3227,7 +3230,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>155.9489183753631</v>
+        <v>156.9072048425875</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3235,7 +3238,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>155.7610948454907</v>
+        <v>156.7832386076331</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3243,7 +3246,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>155.6975686187738</v>
+        <v>156.6282812909215</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3251,7 +3254,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>155.4348531570136</v>
+        <v>155.7895396300546</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3259,7 +3262,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>155.1046542634938</v>
+        <v>155.5666639498032</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3267,7 +3270,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>155.0126108705607</v>
+        <v>155.4913257852101</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3275,7 +3278,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>154.7881696616389</v>
+        <v>155.3058013928895</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3283,7 +3286,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>154.7339804868152</v>
+        <v>155.2579830547822</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3291,7 +3294,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>154.5653374917106</v>
+        <v>155.040388683078</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3299,7 +3302,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>154.564282972295</v>
+        <v>154.5908340443499</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3307,7 +3310,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>154.4543335781487</v>
+        <v>154.4377640074869</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3315,7 +3318,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>154.0581611956794</v>
+        <v>154.4242077025185</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3323,7 +3326,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>153.9761888441862</v>
+        <v>154.2997203330521</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3331,7 +3334,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>153.3810052760373</v>
+        <v>154.095301282314</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3339,7 +3342,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>153.3751011645017</v>
+        <v>154.0355158500684</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3347,7 +3350,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>153.3217689748085</v>
+        <v>153.9769851186637</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3355,7 +3358,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>153.0534134787899</v>
+        <v>153.9016945468901</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3363,7 +3366,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>152.711807013138</v>
+        <v>153.8678701343113</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3371,7 +3374,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>152.5106112838233</v>
+        <v>153.79373494229</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3379,7 +3382,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>152.1066455427305</v>
+        <v>153.7301979762256</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3387,7 +3390,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>151.9152553473238</v>
+        <v>153.4730926774123</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3395,7 +3398,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>151.8761220108989</v>
+        <v>153.4266012259737</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3403,7 +3406,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>151.7958762300233</v>
+        <v>153.0055261148817</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3411,7 +3414,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>151.5037620321995</v>
+        <v>152.9481155682125</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3419,7 +3422,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>151.3604005852097</v>
+        <v>152.9051326626987</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3427,7 +3430,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>151.345051982465</v>
+        <v>152.8927196107902</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3435,7 +3438,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>151.26343270182</v>
+        <v>152.7252304472475</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3443,7 +3446,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>151.2508608407211</v>
+        <v>152.30799203296</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3451,7 +3454,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>151.2464452683975</v>
+        <v>152.227924477125</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3459,7 +3462,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>151.0791241699526</v>
+        <v>151.6673765246762</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3467,7 +3470,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>151.0763945679294</v>
+        <v>151.6138198421972</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3475,7 +3478,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>151.004694681902</v>
+        <v>151.4017703936251</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3483,7 +3486,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>150.9205304393336</v>
+        <v>151.3992675431089</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3491,7 +3494,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>150.7628005474613</v>
+        <v>151.3530072150283</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3499,7 +3502,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>150.6384879855002</v>
+        <v>151.332847032617</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3507,7 +3510,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>150.6258779825288</v>
+        <v>151.0995752802726</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3515,7 +3518,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>150.5519937649477</v>
+        <v>151.0566802759085</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3523,7 +3526,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>150.3048621400661</v>
+        <v>151.0494711920319</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3531,7 +3534,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>149.7973006981011</v>
+        <v>150.9596325127919</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3539,7 +3542,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>149.5459561332339</v>
+        <v>150.6872561811326</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3547,7 +3550,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>149.5043480546047</v>
+        <v>150.5043919249341</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3555,7 +3558,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>149.3894989318619</v>
+        <v>150.4859768991003</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3563,7 +3566,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>149.2337446984517</v>
+        <v>150.4030492558813</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3571,7 +3574,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>149.1725862105282</v>
+        <v>150.1584299458016</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3579,7 +3582,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>148.966273220595</v>
+        <v>149.8756807576229</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3587,7 +3590,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>148.9605791815459</v>
+        <v>149.7020620080436</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3595,7 +3598,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>148.9338544659671</v>
+        <v>149.5126865731177</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3603,7 +3606,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>148.6882959325816</v>
+        <v>149.4644877044751</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3611,7 +3614,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>148.4612907660027</v>
+        <v>149.3293091402235</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3619,7 +3622,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>148.2953597991072</v>
+        <v>149.2981109241952</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3627,7 +3630,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>148.0792398991555</v>
+        <v>149.080876421635</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3635,7 +3638,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>147.7314017234328</v>
+        <v>149.0311079770999</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3643,7 +3646,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>147.70892704457</v>
+        <v>148.5863051336133</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3651,7 +3654,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>147.702128813989</v>
+        <v>148.5605142748601</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3659,7 +3662,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>147.1516849936945</v>
+        <v>148.4081194986588</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3667,7 +3670,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>146.718965730432</v>
+        <v>148.3343361039399</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3675,7 +3678,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>146.7180677962821</v>
+        <v>148.3002315045435</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3683,7 +3686,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>146.4939699411789</v>
+        <v>148.2912780905471</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3691,7 +3694,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>146.4732984613225</v>
+        <v>147.7736355779643</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3699,7 +3702,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>146.0289396213739</v>
+        <v>147.6763285357554</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3707,7 +3710,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>145.9765609484821</v>
+        <v>147.1095565593818</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3715,7 +3718,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>145.9704741745516</v>
+        <v>146.8705056413796</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3723,7 +3726,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>145.908305894511</v>
+        <v>146.866626496892</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3731,7 +3734,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>145.3272032725775</v>
+        <v>146.5901157019858</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3739,7 +3742,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>145.0327210820973</v>
+        <v>146.5204046373005</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3747,7 +3750,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>144.9884804970023</v>
+        <v>146.0381306677117</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3755,7 +3758,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>144.7356811755487</v>
+        <v>145.8202837004987</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3763,7 +3766,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>144.4868499408539</v>
+        <v>145.7083641504138</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3771,7 +3774,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>144.3401534224905</v>
+        <v>145.6422661571636</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3779,7 +3782,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>144.1718244984523</v>
+        <v>145.6389299657713</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3787,7 +3790,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>144.073413366543</v>
+        <v>145.6195937103561</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3795,7 +3798,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>144.0385981314907</v>
+        <v>145.3429103151014</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3803,7 +3806,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>143.8039901458687</v>
+        <v>145.0364433819561</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3811,7 +3814,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>143.5855502770592</v>
+        <v>144.9833797159702</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3819,7 +3822,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>143.3818875383448</v>
+        <v>144.8505876020079</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3827,7 +3830,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>143.3694043231024</v>
+        <v>144.5495647205423</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3835,7 +3838,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>143.2645589117148</v>
+        <v>144.4280502958692</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3843,7 +3846,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>143.2180342164943</v>
+        <v>144.2951731517515</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3851,7 +3854,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>143.0615084340875</v>
+        <v>144.2172921360329</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3859,7 +3862,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>143.0553330466256</v>
+        <v>144.0055322160865</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3867,7 +3870,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>143.0543653710425</v>
+        <v>143.8860731970635</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3875,7 +3878,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>143.0149144689084</v>
+        <v>143.79641013781</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3883,7 +3886,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>142.9901836964648</v>
+        <v>143.7518447743103</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3891,7 +3894,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>142.8375734572354</v>
+        <v>143.6720189399621</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3899,7 +3902,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>142.6823636609907</v>
+        <v>143.350006598375</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3907,7 +3910,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>142.6814804229871</v>
+        <v>143.270153486762</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3915,7 +3918,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>142.5813352207838</v>
+        <v>143.1989858525894</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3923,7 +3926,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>142.4826033862092</v>
+        <v>143.167402405357</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3931,7 +3934,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>142.3878933788753</v>
+        <v>143.153612439664</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3939,7 +3942,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>142.3458634192968</v>
+        <v>143.0929445445091</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3947,7 +3950,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>142.3083201451481</v>
+        <v>142.9853168152086</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3955,7 +3958,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>142.2634238613319</v>
+        <v>142.8257246063277</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3963,7 +3966,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>142.2522262019659</v>
+        <v>142.7734463703551</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3971,7 +3974,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>142.1477853541822</v>
+        <v>142.7475267902678</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3979,7 +3982,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>141.8458919540657</v>
+        <v>142.6578558301345</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3987,7 +3990,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>141.7228753058066</v>
+        <v>142.6314331034537</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3995,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>141.41835395281</v>
+        <v>142.5325023314945</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4003,7 +4006,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>141.281393701315</v>
+        <v>142.3904987565423</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4011,7 +4014,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>141.2109761876562</v>
+        <v>142.3822072827061</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4019,7 +4022,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>140.8473026276901</v>
+        <v>142.3292676753946</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4027,7 +4030,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>140.7795951981164</v>
+        <v>142.2790251814566</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4035,7 +4038,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>140.73687094401</v>
+        <v>142.2355648174488</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4043,7 +4046,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>140.6742151421692</v>
+        <v>142.2189115550009</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4051,7 +4054,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>140.6418274795667</v>
+        <v>142.1307114684748</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4059,7 +4062,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>140.504288025095</v>
+        <v>142.1014729476676</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4067,7 +4070,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>140.4173259280775</v>
+        <v>141.9286902497569</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4075,7 +4078,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>140.2519178629403</v>
+        <v>141.8356896648192</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4083,7 +4086,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>140.1345350808549</v>
+        <v>141.6775809258328</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4091,7 +4094,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>140.0788632742544</v>
+        <v>141.6573320586146</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4099,7 +4102,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>139.9903782378738</v>
+        <v>141.6009192508177</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4107,7 +4110,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>139.9450478874842</v>
+        <v>141.469055414031</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4115,7 +4118,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>139.8941167662134</v>
+        <v>141.3233236090321</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4123,7 +4126,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>139.8609642671719</v>
+        <v>141.2952558456391</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4131,7 +4134,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>139.8005741457096</v>
+        <v>141.281393701315</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4139,7 +4142,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>139.7924500986329</v>
+        <v>141.0687392909593</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4147,7 +4150,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>139.4850371582545</v>
+        <v>140.837043568145</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4155,7 +4158,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>139.2408445305366</v>
+        <v>140.7831771618348</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4163,7 +4166,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>139.2208480981058</v>
+        <v>140.7236282913396</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4171,7 +4174,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>139.1640361176752</v>
+        <v>140.622167925837</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4179,7 +4182,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>139.1299174543795</v>
+        <v>140.4954127429718</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4187,7 +4190,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>139.1130493425313</v>
+        <v>140.4667836254618</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4195,7 +4198,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>138.6970933094404</v>
+        <v>140.3183747117703</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4203,7 +4206,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>138.5198318341186</v>
+        <v>140.2812781175905</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4211,7 +4214,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>138.5054007272457</v>
+        <v>140.2709857312056</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4219,7 +4222,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>138.4756195378544</v>
+        <v>140.1426510915536</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4227,7 +4230,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>138.3452269060959</v>
+        <v>140.0032423823479</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4235,7 +4238,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>138.2999409224641</v>
+        <v>139.8758848999815</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4243,7 +4246,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>138.276285070385</v>
+        <v>139.8700118011949</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4251,7 +4254,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>138.1860450979784</v>
+        <v>139.8260445616984</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4259,7 +4262,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>138.1382335272167</v>
+        <v>139.7526485789137</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4267,7 +4270,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>138.1357423624858</v>
+        <v>139.712898807347</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4275,7 +4278,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>138.1223767002803</v>
+        <v>139.5285521240404</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4283,7 +4286,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>138.0370712653395</v>
+        <v>139.4232606319929</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4291,7 +4294,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>137.9813402395752</v>
+        <v>139.4152053670403</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4299,7 +4302,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>137.9372098590875</v>
+        <v>139.07276009247</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4307,7 +4310,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>137.8877898429012</v>
+        <v>139.0717528399503</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4315,7 +4318,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>137.8375253428996</v>
+        <v>139.000141060723</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4323,7 +4326,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>137.744363386329</v>
+        <v>138.8876838597598</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4331,7 +4334,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>137.6933821463758</v>
+        <v>138.757530956834</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4339,7 +4342,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>137.6509498010443</v>
+        <v>138.4585106980577</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4347,7 +4350,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>137.647458557392</v>
+        <v>138.3757021251016</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4355,7 +4358,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>137.6062567984847</v>
+        <v>138.3134976692729</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4363,7 +4366,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>137.5904632869181</v>
+        <v>138.3004934457557</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4371,7 +4374,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>137.4537922423122</v>
+        <v>138.2247667539818</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4379,7 +4382,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>137.3897039613701</v>
+        <v>138.1946189360682</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4387,7 +4390,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>137.3327048914867</v>
+        <v>138.1649788922283</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4395,7 +4398,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>137.2692197736505</v>
+        <v>138.1421840395282</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4403,7 +4406,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>137.264815080596</v>
+        <v>138.0678853327856</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4411,7 +4414,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>136.9803683242971</v>
+        <v>137.9319397796686</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4419,7 +4422,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>136.8855697991591</v>
+        <v>137.9089933130399</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4427,7 +4430,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>136.8169889237313</v>
+        <v>137.8751069078024</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4435,7 +4438,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>136.6340560601046</v>
+        <v>137.8233476928218</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4443,7 +4446,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>136.5588552686513</v>
+        <v>137.7289479185786</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4451,7 +4454,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>136.4102888186026</v>
+        <v>137.5998302442785</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4459,7 +4462,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>136.3509509438343</v>
+        <v>137.5620665023833</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4467,7 +4470,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>136.2712048877005</v>
+        <v>137.5492988083257</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4475,7 +4478,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>136.2678478481354</v>
+        <v>137.5225269094026</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4483,7 +4486,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>136.2554461908692</v>
+        <v>137.4917762612925</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4491,7 +4494,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>136.17885493576</v>
+        <v>137.3091374238749</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4499,7 +4502,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>136.1607489479903</v>
+        <v>137.1305287063741</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4507,7 +4510,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>136.1246010414806</v>
+        <v>137.0777665358281</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4515,7 +4518,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>136.0800848199438</v>
+        <v>137.0736211891701</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4523,7 +4526,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>135.9492908783246</v>
+        <v>137.0475751390173</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4531,7 +4534,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>135.9151329141101</v>
+        <v>136.8932059297087</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4539,7 +4542,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>135.881856529892</v>
+        <v>136.8830822531503</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4547,7 +4550,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>135.8349986865929</v>
+        <v>136.8762115340304</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4555,7 +4558,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>135.8087644903276</v>
+        <v>136.8272427162115</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4563,7 +4566,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>135.7443522713542</v>
+        <v>136.7870332700534</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4571,7 +4574,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>135.7354702691932</v>
+        <v>136.5896591056988</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4579,7 +4582,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>135.6639168157129</v>
+        <v>136.5888155444449</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4587,7 +4590,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>135.6568557443776</v>
+        <v>136.5820695450764</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4595,7 +4598,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>135.6465331214706</v>
+        <v>136.5664519846778</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4603,7 +4606,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>135.4387898231419</v>
+        <v>136.5588552686513</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4611,7 +4614,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>135.4117286928039</v>
+        <v>136.5134546717367</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4619,7 +4622,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>135.3037071553671</v>
+        <v>136.510856857912</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4627,7 +4630,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>135.2591883682406</v>
+        <v>136.4946885430332</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4635,7 +4638,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>135.218675846875</v>
+        <v>136.3425062120198</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4643,7 +4646,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>135.1726625672705</v>
+        <v>136.240501535632</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4651,7 +4654,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>135.1712629134285</v>
+        <v>136.149696433469</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4659,7 +4662,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>135.127181190445</v>
+        <v>136.1343000627213</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4667,7 +4670,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>135.0982972549286</v>
+        <v>136.1167688559052</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4675,7 +4678,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>135.0053981644405</v>
+        <v>136.0283612725839</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4683,7 +4686,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>134.9985590227004</v>
+        <v>135.9898367487228</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4691,7 +4694,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>134.9902615021602</v>
+        <v>135.9564132216049</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4699,7 +4702,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>134.9823904760325</v>
+        <v>135.8944043923146</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4707,7 +4710,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>134.9335943338178</v>
+        <v>135.8659213812735</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4715,7 +4718,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>134.874848367183</v>
+        <v>135.8204251442773</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4723,7 +4726,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>134.8415500380249</v>
+        <v>135.8133700575665</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4731,7 +4734,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>134.7758008461508</v>
+        <v>135.8010516678593</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4739,7 +4742,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>134.7675143339929</v>
+        <v>135.7845847834069</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4747,7 +4750,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>134.664162211485</v>
+        <v>135.7775327278687</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4755,7 +4758,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>134.6576321469574</v>
+        <v>135.777217425524</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4763,7 +4766,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>134.5615065657816</v>
+        <v>135.696341430034</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4771,7 +4774,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>134.5030138410121</v>
+        <v>135.6785385298174</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4779,7 +4782,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>134.434398564467</v>
+        <v>135.6714865845233</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4787,7 +4790,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>134.4095200739912</v>
+        <v>135.6437489798742</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4795,7 +4798,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>134.4047917336708</v>
+        <v>135.6228382269661</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4803,7 +4806,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>134.3765992904932</v>
+        <v>135.4493073430927</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4811,7 +4814,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>134.3629590593991</v>
+        <v>135.4233809437227</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4819,7 +4822,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>134.2468691654297</v>
+        <v>135.3660302608396</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4827,7 +4830,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>134.2312354114259</v>
+        <v>135.2723893503697</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4835,7 +4838,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>134.0113513612873</v>
+        <v>135.2609209140926</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4843,7 +4846,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>133.9940390316504</v>
+        <v>135.2294264056247</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -4851,7 +4854,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>133.9317467605561</v>
+        <v>135.1369064179616</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -4859,7 +4862,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>133.8827182358481</v>
+        <v>135.1184404643811</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -4867,7 +4870,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>133.7379571249518</v>
+        <v>135.0663314383268</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -4875,7 +4878,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>133.6753535786762</v>
+        <v>135.05611330084</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -4883,7 +4886,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>133.5471508080951</v>
+        <v>135.0307576311058</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -4891,7 +4894,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>133.5102196011165</v>
+        <v>135.0162056260318</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -4899,7 +4902,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>133.4704096654048</v>
+        <v>134.9205196922295</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -4907,7 +4910,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>133.42426094988</v>
+        <v>134.9120315388282</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -4915,7 +4918,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>133.3943646596023</v>
+        <v>134.7675143339929</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -4923,7 +4926,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>133.2611118636476</v>
+        <v>134.7369521197146</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -4931,7 +4934,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>133.2519231882565</v>
+        <v>134.6134762322478</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -4939,7 +4942,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>133.177611779643</v>
+        <v>134.6131570464181</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -4947,7 +4950,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>133.1749380472845</v>
+        <v>134.5480889998557</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -4955,7 +4958,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>133.0228999647857</v>
+        <v>134.5077423355252</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -4963,7 +4966,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>132.9930752276908</v>
+        <v>134.4816530498618</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -4971,7 +4974,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>132.8746984834535</v>
+        <v>134.3423768536229</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -4979,7 +4982,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>132.8528752470305</v>
+        <v>134.3185113309643</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -4987,7 +4990,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>132.8283589196511</v>
+        <v>134.2330568107842</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -4995,7 +4998,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>132.6892347450174</v>
+        <v>134.2311972295556</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5003,7 +5006,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>132.668831970362</v>
+        <v>134.1972802944035</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5011,7 +5014,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>132.6591201274924</v>
+        <v>134.1218000012914</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5019,7 +5022,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>132.6288290535528</v>
+        <v>134.0887356560289</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5027,7 +5030,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>132.5682061923399</v>
+        <v>134.0706978202651</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5035,7 +5038,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>132.5512263449019</v>
+        <v>134.0648806703029</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5043,7 +5046,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>132.5113448461767</v>
+        <v>133.8666702648151</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5051,7 +5054,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>132.5104617988036</v>
+        <v>133.8331580648533</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5059,7 +5062,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>132.3742520407793</v>
+        <v>133.8288463997068</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5067,7 +5070,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>132.3693266298455</v>
+        <v>133.7814363366115</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5075,7 +5078,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>132.2728987720686</v>
+        <v>133.6733717616019</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5083,7 +5086,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>132.2042383231628</v>
+        <v>133.578471733086</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5091,7 +5094,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>132.0543223000497</v>
+        <v>133.5517455804628</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5099,7 +5102,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>132.0218349929716</v>
+        <v>133.5316917758043</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5107,7 +5110,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>131.9806297025372</v>
+        <v>133.5122898801307</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5115,7 +5118,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>131.9686915178323</v>
+        <v>133.4758687716442</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5123,7 +5126,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>131.9117304217967</v>
+        <v>133.4303669656856</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5131,7 +5134,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>131.8970974180505</v>
+        <v>133.4287969044585</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5139,7 +5142,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>131.8808820577207</v>
+        <v>133.3496372350919</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5147,7 +5150,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>131.8697284244274</v>
+        <v>133.2009906876031</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5155,7 +5158,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>131.7963527910497</v>
+        <v>133.1526995673106</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5163,7 +5166,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>131.6479896514303</v>
+        <v>133.0951091735079</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5171,7 +5174,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>131.6385283799808</v>
+        <v>133.0345319386588</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5179,7 +5182,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>131.5587596561698</v>
+        <v>132.8606974725568</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5187,7 +5190,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>131.4779865507568</v>
+        <v>132.7867263234683</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5195,7 +5198,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>131.2906822880004</v>
+        <v>132.6685312417383</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5203,7 +5206,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>131.2787950238559</v>
+        <v>132.3597795865131</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5211,7 +5214,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>131.2262615842498</v>
+        <v>132.3017531819189</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5219,7 +5222,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>131.1932307659093</v>
+        <v>132.2645678691204</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5227,7 +5230,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>131.1090439226632</v>
+        <v>132.247949881012</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5235,7 +5238,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>131.0091610384851</v>
+        <v>132.2105418897723</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5243,7 +5246,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>130.9795778903521</v>
+        <v>132.1791428249641</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5251,7 +5254,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>130.9691570507906</v>
+        <v>132.1461889816248</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5259,7 +5262,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>130.9680400452467</v>
+        <v>132.1335650303092</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5267,7 +5270,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>130.9065934825076</v>
+        <v>132.107613301763</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5275,7 +5278,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>130.8806184738569</v>
+        <v>132.0922967519471</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5283,7 +5286,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>130.8711798021147</v>
+        <v>132.0055047455213</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5291,7 +5294,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>130.8434634862676</v>
+        <v>131.9862732497961</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5299,7 +5302,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>130.7724849471469</v>
+        <v>131.9716528205148</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5307,7 +5310,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>130.7578852562786</v>
+        <v>131.9506770923455</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5315,7 +5318,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>130.7536615252871</v>
+        <v>131.9334877013236</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5323,7 +5326,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>130.5636090423448</v>
+        <v>131.8892335357851</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5331,7 +5334,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>130.4949176725231</v>
+        <v>131.8828113013893</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5339,7 +5342,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>130.48444560534</v>
+        <v>131.8141385415728</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5347,7 +5350,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>130.4481120838515</v>
+        <v>131.7293820784066</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5355,7 +5358,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>130.3241566202772</v>
+        <v>131.7218314513688</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5363,7 +5366,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>130.2041753273829</v>
+        <v>131.635055785486</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5371,7 +5374,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>130.1878740708109</v>
+        <v>131.5528423215511</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5379,7 +5382,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>130.1872951329721</v>
+        <v>131.5080563449507</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5387,7 +5390,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>130.154216649341</v>
+        <v>131.371738915307</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5395,7 +5398,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>130.1416911557495</v>
+        <v>131.3689553832469</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5403,7 +5406,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>130.1327898618999</v>
+        <v>131.3168470501039</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5411,7 +5414,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>130.0753312061518</v>
+        <v>131.2583293614723</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5419,7 +5422,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>130.0669409212317</v>
+        <v>131.2418158996013</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5427,7 +5430,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>129.9933499210113</v>
+        <v>131.2281651718217</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5435,7 +5438,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>129.8374301410808</v>
+        <v>131.1847081728993</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5443,7 +5446,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>129.7720167976253</v>
+        <v>131.1636131856755</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5451,7 +5454,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>129.7691603239647</v>
+        <v>131.1550718727375</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -5459,7 +5462,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>129.7277297922156</v>
+        <v>131.0718791149157</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -5467,7 +5470,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>129.7126282720566</v>
+        <v>131.0688545601615</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -5475,7 +5478,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>129.6801187179357</v>
+        <v>131.0161634288398</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -5483,7 +5486,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>129.6765754068652</v>
+        <v>130.9908175574508</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -5491,7 +5494,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>129.6617692440564</v>
+        <v>130.863944788545</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -5499,7 +5502,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>129.647700420486</v>
+        <v>130.8588862090086</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -5507,7 +5510,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>129.6280612343079</v>
+        <v>130.8115438109213</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -5515,7 +5518,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>129.5551231167595</v>
+        <v>130.7781202492414</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -5523,7 +5526,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>129.5238024386716</v>
+        <v>130.6295161894465</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -5531,7 +5534,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>129.480858445772</v>
+        <v>130.6074131791358</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5539,7 +5542,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>129.4569043044106</v>
+        <v>130.5369201784649</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -5547,7 +5550,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>129.4473643234843</v>
+        <v>130.5273717485854</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -5555,7 +5558,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>129.3895546161135</v>
+        <v>130.5269369481896</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -5563,7 +5566,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>129.3153440926911</v>
+        <v>130.468765165976</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -5571,7 +5574,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>129.307561530571</v>
+        <v>130.4663188942164</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -5579,7 +5582,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>129.2816133978601</v>
+        <v>130.3890215026617</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -5587,7 +5590,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>129.0183620272533</v>
+        <v>130.3409533201896</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -5595,7 +5598,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>128.8316219085347</v>
+        <v>130.328051430999</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -5603,7 +5606,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>128.7662482552271</v>
+        <v>130.2232698255305</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -5611,7 +5614,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>128.7559372337961</v>
+        <v>130.2144633368873</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -5619,7 +5622,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>128.6892175044889</v>
+        <v>130.1573207532953</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -5627,7 +5630,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>128.6481318295633</v>
+        <v>130.0523698271155</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -5635,7 +5638,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>128.6405277305258</v>
+        <v>130.0353570197399</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -5643,7 +5646,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>128.6083294700458</v>
+        <v>129.957473993423</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -5651,7 +5654,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>128.4739202266124</v>
+        <v>129.9449890315277</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -5659,7 +5662,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>128.4150161232045</v>
+        <v>129.8224217422613</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -5667,7 +5670,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>128.3547650806118</v>
+        <v>129.7965216854572</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -5675,7 +5678,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>128.2120808430969</v>
+        <v>129.72166837428</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -5683,7 +5686,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>128.2078683625028</v>
+        <v>129.699570358383</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -5691,7 +5694,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>128.1574708752902</v>
+        <v>129.5938102747621</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -5699,7 +5702,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>128.1315823177906</v>
+        <v>129.5914271114432</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -5707,7 +5710,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>128.0372359275025</v>
+        <v>129.5533230881431</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -5715,7 +5718,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>128.0159288068061</v>
+        <v>129.427110473218</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -5723,7 +5726,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>127.7893747588866</v>
+        <v>129.3942498504892</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -5731,7 +5734,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>127.7529042765712</v>
+        <v>129.3699124862285</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -5739,7 +5742,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>127.715213778496</v>
+        <v>129.2365240642166</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -5747,7 +5750,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>127.701985366705</v>
+        <v>129.1715695365264</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -5755,7 +5758,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>127.6755440249751</v>
+        <v>129.0360905156825</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -5763,7 +5766,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>127.5855011342489</v>
+        <v>129.0003355394946</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -5771,7 +5774,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>127.576836950069</v>
+        <v>128.9772195775112</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -5779,7 +5782,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>127.5534396233952</v>
+        <v>128.9145340736237</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -5787,7 +5790,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>127.5506596331911</v>
+        <v>128.8738592974142</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -5795,7 +5798,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>127.5046524337664</v>
+        <v>128.8335380088422</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -5803,7 +5806,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>127.4078918415257</v>
+        <v>128.7038881705562</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -5811,7 +5814,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>127.3665544631783</v>
+        <v>128.6758480505154</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -5819,7 +5822,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>127.3476649191804</v>
+        <v>128.6441440817489</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -5827,7 +5830,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>127.3227494605722</v>
+        <v>128.6135092122462</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -5835,7 +5838,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>127.3126966863034</v>
+        <v>128.4878467360042</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -5843,7 +5846,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>127.1729073336666</v>
+        <v>128.4625038683571</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -5851,7 +5854,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>127.1557785896076</v>
+        <v>128.4580555714589</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -5859,7 +5862,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>127.0960083258662</v>
+        <v>128.4439111866835</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -5867,7 +5870,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>126.9811208986773</v>
+        <v>128.435328157059</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -5875,7 +5878,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>126.9713535303955</v>
+        <v>128.4200921017961</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -5883,7 +5886,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>126.9548100174484</v>
+        <v>128.3891767215763</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -5891,7 +5894,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>126.908299335357</v>
+        <v>128.3281056227393</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -5899,7 +5902,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>126.8948323022164</v>
+        <v>128.3260938096832</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -5907,7 +5910,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>126.7922572370206</v>
+        <v>128.323204087398</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -5915,7 +5918,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>126.7613186557812</v>
+        <v>128.1895807288587</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -5923,7 +5926,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>126.744337671979</v>
+        <v>128.1511122907845</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -5931,7 +5934,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>126.7386057992682</v>
+        <v>128.1016985033609</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -5939,7 +5942,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>126.6795382089595</v>
+        <v>128.0722391793587</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -5947,7 +5950,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>126.6089481883313</v>
+        <v>128.0421016796318</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -5955,7 +5958,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>126.6083610710793</v>
+        <v>128.0273627501318</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -5963,7 +5966,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>126.5568302947528</v>
+        <v>128.0050406490876</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -5971,7 +5974,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>126.4909126472755</v>
+        <v>127.9954091664016</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -5979,7 +5982,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>126.48311872936</v>
+        <v>127.9653612193474</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -5987,7 +5990,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>126.413288082866</v>
+        <v>127.9502987701212</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -5995,7 +5998,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>126.4001742262731</v>
+        <v>127.9303864554428</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6003,7 +6006,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>126.3932742683299</v>
+        <v>127.9193447919005</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6011,7 +6014,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>126.3150179118371</v>
+        <v>127.7782149490504</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6019,7 +6022,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>126.2775269556842</v>
+        <v>127.7654179919931</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6027,7 +6030,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>126.2287905449198</v>
+        <v>127.6837691403796</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6035,7 +6038,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>126.1989532146311</v>
+        <v>127.4394049117574</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6043,7 +6046,15 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>126.0509902619897</v>
+        <v>127.4144714814237</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" t="s">
+        <v>517</v>
+      </c>
+      <c r="B517" s="1">
+        <v>127.4127621386592</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/data/rs_rating.xlsx
+++ b/Screener/data/rs_rating.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
   <si>
     <t>Symbol</t>
   </si>
@@ -40,12 +40,12 @@
     <t>EYPT</t>
   </si>
   <si>
+    <t>CLSK</t>
+  </si>
+  <si>
     <t>SSNT</t>
   </si>
   <si>
-    <t>CLSK</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -58,1516 +58,1519 @@
     <t>IMNM</t>
   </si>
   <si>
+    <t>DWACU</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
     <t>IMGN</t>
   </si>
   <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>MARA</t>
   </si>
   <si>
-    <t>ANF</t>
-  </si>
-  <si>
-    <t>DWACU</t>
-  </si>
-  <si>
-    <t>CVNA</t>
-  </si>
-  <si>
-    <t>DWAC</t>
-  </si>
-  <si>
-    <t>MOR</t>
+    <t>YMAB</t>
   </si>
   <si>
     <t>MGNX</t>
   </si>
   <si>
-    <t>YMAB</t>
+    <t>NPCE</t>
   </si>
   <si>
     <t>CBAY</t>
   </si>
   <si>
+    <t>OSCR</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
     <t>HARP</t>
   </si>
   <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>ALPN</t>
+    <t>SLN</t>
+  </si>
+  <si>
+    <t>GBTC</t>
   </si>
   <si>
     <t>VRT</t>
   </si>
   <si>
-    <t>NPCE</t>
-  </si>
-  <si>
-    <t>SLN</t>
-  </si>
-  <si>
-    <t>GBTC</t>
-  </si>
-  <si>
-    <t>OSCR</t>
-  </si>
-  <si>
     <t>VKTX</t>
   </si>
   <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>ALXO</t>
+  </si>
+  <si>
     <t>AFRM</t>
   </si>
   <si>
     <t>BHVN</t>
   </si>
   <si>
-    <t>POWL</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
     <t>EWTX</t>
   </si>
   <si>
-    <t>ALXO</t>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>TWST</t>
+  </si>
+  <si>
+    <t>CYTK</t>
+  </si>
+  <si>
+    <t>PRAX</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>PHVS</t>
   </si>
   <si>
     <t>ELTK</t>
   </si>
   <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>PRAX</t>
-  </si>
-  <si>
-    <t>GRPN</t>
-  </si>
-  <si>
-    <t>CLS</t>
-  </si>
-  <si>
-    <t>TWST</t>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>DYN</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>SMID</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>CSPI</t>
+  </si>
+  <si>
+    <t>KAMN</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>ASPN</t>
+  </si>
+  <si>
+    <t>NVDA</t>
   </si>
   <si>
     <t>MSTR</t>
   </si>
   <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>ETHE</t>
-  </si>
-  <si>
-    <t>CYTK</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>PHVS</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>DYN</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>ARVN</t>
-  </si>
-  <si>
-    <t>KAMN</t>
+    <t>HOV</t>
+  </si>
+  <si>
+    <t>BBIO</t>
   </si>
   <si>
     <t>AMR</t>
   </si>
   <si>
-    <t>TAL</t>
-  </si>
-  <si>
-    <t>ASPN</t>
-  </si>
-  <si>
-    <t>SMID</t>
+    <t>MRUS</t>
   </si>
   <si>
     <t>RYTM</t>
   </si>
   <si>
-    <t>UTI</t>
-  </si>
-  <si>
-    <t>MRUS</t>
+    <t>ESTC</t>
+  </si>
+  <si>
+    <t>BVN</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>KURA</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>FDMT</t>
+  </si>
+  <si>
+    <t>CGEM</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>INBK</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>SWTX</t>
   </si>
   <si>
     <t>CABA</t>
   </si>
   <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>BVN</t>
-  </si>
-  <si>
-    <t>FDMT</t>
-  </si>
-  <si>
-    <t>HOV</t>
-  </si>
-  <si>
-    <t>MCAFU</t>
-  </si>
-  <si>
-    <t>ESTC</t>
-  </si>
-  <si>
-    <t>PLTR</t>
+    <t>TARS</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>ICVX</t>
+  </si>
+  <si>
+    <t>IGMS</t>
+  </si>
+  <si>
+    <t>JSPR</t>
+  </si>
+  <si>
+    <t>EDN</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>DFH</t>
   </si>
   <si>
     <t>TAYD</t>
   </si>
   <si>
-    <t>OLMA</t>
+    <t>EVER</t>
+  </si>
+  <si>
+    <t>IESC</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>EDU</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>FFNW</t>
+  </si>
+  <si>
+    <t>SRRK</t>
   </si>
   <si>
     <t>RIOT</t>
   </si>
   <si>
-    <t>LMB</t>
-  </si>
-  <si>
-    <t>KURA</t>
-  </si>
-  <si>
-    <t>TARS</t>
-  </si>
-  <si>
-    <t>JSPR</t>
-  </si>
-  <si>
-    <t>CGEM</t>
-  </si>
-  <si>
-    <t>EDU</t>
-  </si>
-  <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>SKYW</t>
-  </si>
-  <si>
-    <t>NTNX</t>
-  </si>
-  <si>
-    <t>INBK</t>
-  </si>
-  <si>
-    <t>CSPI</t>
-  </si>
-  <si>
-    <t>ICVX</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>SWTX</t>
+    <t>GFF</t>
   </si>
   <si>
     <t>INBX</t>
   </si>
   <si>
+    <t>SMLR</t>
+  </si>
+  <si>
+    <t>KRTX</t>
+  </si>
+  <si>
     <t>FLXS</t>
   </si>
   <si>
-    <t>FFNW</t>
-  </si>
-  <si>
-    <t>DFH</t>
-  </si>
-  <si>
-    <t>BBIO</t>
-  </si>
-  <si>
-    <t>EVER</t>
-  </si>
-  <si>
-    <t>TREE</t>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>METC</t>
+  </si>
+  <si>
+    <t>XMTR</t>
+  </si>
+  <si>
+    <t>USAP</t>
+  </si>
+  <si>
+    <t>PLAB</t>
+  </si>
+  <si>
+    <t>GTLB</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>KEQU</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>KYMR</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>CRNX</t>
+  </si>
+  <si>
+    <t>COHR</t>
   </si>
   <si>
     <t>PANW</t>
   </si>
   <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>ZS</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>CERE</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>ACU</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>BELFA</t>
+  </si>
+  <si>
+    <t>ARCT</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>VRNS</t>
+  </si>
+  <si>
+    <t>BPMC</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>GSHD</t>
+  </si>
+  <si>
+    <t>DKNG</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>CUBI</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>QEPC</t>
+  </si>
+  <si>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
     <t>CVRX</t>
   </si>
   <si>
-    <t>EDN</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>KRTX</t>
-  </si>
-  <si>
-    <t>COHR</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>IESC</t>
-  </si>
-  <si>
-    <t>KEQU</t>
-  </si>
-  <si>
-    <t>GTLB</t>
-  </si>
-  <si>
-    <t>ZS</t>
-  </si>
-  <si>
-    <t>GFF</t>
-  </si>
-  <si>
-    <t>SRRK</t>
-  </si>
-  <si>
-    <t>SMLR</t>
-  </si>
-  <si>
-    <t>IBP</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>PLAB</t>
-  </si>
-  <si>
-    <t>METC</t>
-  </si>
-  <si>
-    <t>KYMR</t>
-  </si>
-  <si>
-    <t>XMTR</t>
-  </si>
-  <si>
-    <t>CERE</t>
-  </si>
-  <si>
-    <t>ARCT</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>SPOT</t>
-  </si>
-  <si>
-    <t>BMA</t>
-  </si>
-  <si>
-    <t>CMPR</t>
-  </si>
-  <si>
-    <t>BASE</t>
-  </si>
-  <si>
-    <t>ACU</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
     <t>GHM</t>
   </si>
   <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>CRNX</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>VRNS</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>AZZ</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>CYBR</t>
-  </si>
-  <si>
-    <t>AZEK</t>
-  </si>
-  <si>
-    <t>BELFA</t>
-  </si>
-  <si>
-    <t>DKNG</t>
-  </si>
-  <si>
-    <t>HBB</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>ONTO</t>
+    <t>NSSC</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>HCI</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>PDD</t>
+  </si>
+  <si>
+    <t>RCMT</t>
+  </si>
+  <si>
+    <t>SHAK</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>GIII</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>PTGX</t>
+  </si>
+  <si>
+    <t>ESEA</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>BELFB</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>PATH</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>PVH</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>PCVX</t>
+  </si>
+  <si>
+    <t>RCKT</t>
+  </si>
+  <si>
+    <t>IMVT</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>NVMI</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>TRIP</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>KROS</t>
+  </si>
+  <si>
+    <t>KRUS</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>ICHR</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>WMS</t>
   </si>
   <si>
     <t>URGN</t>
   </si>
   <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>PATH</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>WING</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>IMVT</t>
-  </si>
-  <si>
-    <t>USAP</t>
-  </si>
-  <si>
-    <t>CUBI</t>
-  </si>
-  <si>
-    <t>ESEA</t>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>BRZE</t>
+  </si>
+  <si>
+    <t>CRSP</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>JAKK</t>
+  </si>
+  <si>
+    <t>KAI</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>TYRA</t>
+  </si>
+  <si>
+    <t>MLKN</t>
+  </si>
+  <si>
+    <t>JBI</t>
   </si>
   <si>
     <t>DELL</t>
   </si>
   <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>GSHD</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>GGAL</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>PVH</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>RCMT</t>
-  </si>
-  <si>
-    <t>PDD</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>KROS</t>
-  </si>
-  <si>
-    <t>HCI</t>
-  </si>
-  <si>
-    <t>PTGX</t>
-  </si>
-  <si>
-    <t>FICO</t>
+    <t>ALKT</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>OWL</t>
+  </si>
+  <si>
+    <t>MBIN</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>ELAN</t>
+  </si>
+  <si>
+    <t>KRT</t>
+  </si>
+  <si>
+    <t>FSTR</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>OPRX</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>ARES</t>
+  </si>
+  <si>
+    <t>GBX</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>RCEL</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>PRCT</t>
+  </si>
+  <si>
+    <t>GIC</t>
+  </si>
+  <si>
+    <t>SLG</t>
+  </si>
+  <si>
+    <t>GLP</t>
+  </si>
+  <si>
+    <t>HIBB</t>
+  </si>
+  <si>
+    <t>BXC</t>
+  </si>
+  <si>
+    <t>NRDS</t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>MKSI</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>PATK</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>APPF</t>
   </si>
   <si>
     <t>RAPT</t>
   </si>
   <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>ASND</t>
-  </si>
-  <si>
-    <t>PRCT</t>
-  </si>
-  <si>
-    <t>PGTI</t>
-  </si>
-  <si>
-    <t>ALKT</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>GIII</t>
-  </si>
-  <si>
-    <t>PCVX</t>
-  </si>
-  <si>
-    <t>BELFB</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>BRZE</t>
-  </si>
-  <si>
-    <t>KRUS</t>
-  </si>
-  <si>
-    <t>USM</t>
-  </si>
-  <si>
-    <t>MLP</t>
-  </si>
-  <si>
-    <t>MAC</t>
-  </si>
-  <si>
-    <t>INFA</t>
-  </si>
-  <si>
-    <t>PLAY</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>WMS</t>
-  </si>
-  <si>
-    <t>ESP</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>IRWD</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>TREX</t>
-  </si>
-  <si>
-    <t>JAKK</t>
-  </si>
-  <si>
-    <t>ARES</t>
-  </si>
-  <si>
-    <t>FSTR</t>
-  </si>
-  <si>
-    <t>ELAN</t>
+    <t>PEGA</t>
+  </si>
+  <si>
+    <t>ZEUS</t>
+  </si>
+  <si>
+    <t>UCTT</t>
+  </si>
+  <si>
+    <t>AMWD</t>
   </si>
   <si>
     <t>WIX</t>
   </si>
   <si>
-    <t>OWL</t>
-  </si>
-  <si>
-    <t>ICHR</t>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>VEL</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>NRP</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>AXSM</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>GWRE</t>
+  </si>
+  <si>
+    <t>ODC</t>
+  </si>
+  <si>
+    <t>PKOH</t>
+  </si>
+  <si>
+    <t>DOOR</t>
+  </si>
+  <si>
+    <t>DBRG</t>
+  </si>
+  <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>EVR</t>
+  </si>
+  <si>
+    <t>CFLT</t>
+  </si>
+  <si>
+    <t>XENE</t>
+  </si>
+  <si>
+    <t>SIG</t>
   </si>
   <si>
     <t>AXR</t>
   </si>
   <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>CRSP</t>
-  </si>
-  <si>
-    <t>FSLY</t>
-  </si>
-  <si>
-    <t>RCKT</t>
-  </si>
-  <si>
-    <t>QEPC</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>FROG</t>
-  </si>
-  <si>
-    <t>ACMR</t>
-  </si>
-  <si>
-    <t>TYRA</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>NRDS</t>
-  </si>
-  <si>
-    <t>MDC</t>
+    <t>AAON</t>
+  </si>
+  <si>
+    <t>STLA</t>
+  </si>
+  <si>
+    <t>ASMIY</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>NPO</t>
+  </si>
+  <si>
+    <t>THC</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>HLNE</t>
+  </si>
+  <si>
+    <t>CVLT</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>MCY</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>QTRX</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>NHC</t>
+  </si>
+  <si>
+    <t>STNE</t>
+  </si>
+  <si>
+    <t>KLAC</t>
+  </si>
+  <si>
+    <t>CELC</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>KOP</t>
+  </si>
+  <si>
+    <t>SILXY</t>
+  </si>
+  <si>
+    <t>JXN</t>
+  </si>
+  <si>
+    <t>VECO</t>
+  </si>
+  <si>
+    <t>SCSC</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>PSN</t>
   </si>
   <si>
     <t>HCC</t>
   </si>
   <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>NVMI</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>SLG</t>
-  </si>
-  <si>
-    <t>MKSI</t>
-  </si>
-  <si>
-    <t>GIC</t>
-  </si>
-  <si>
-    <t>JBI</t>
-  </si>
-  <si>
-    <t>STNE</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>AROC</t>
-  </si>
-  <si>
-    <t>VCEL</t>
-  </si>
-  <si>
-    <t>OPRX</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>RCEL</t>
-  </si>
-  <si>
-    <t>NSSC</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>XENE</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>NRP</t>
-  </si>
-  <si>
-    <t>GLP</t>
+    <t>AWI</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>ALTR</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>NEU</t>
+  </si>
+  <si>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>AYI</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>PSX</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>JHX</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>TDG</t>
+  </si>
+  <si>
+    <t>ISTR</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>FRD</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>NS</t>
+  </si>
+  <si>
+    <t>PCAR</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>TGI</t>
+  </si>
+  <si>
+    <t>MNDY</t>
+  </si>
+  <si>
+    <t>BBU</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>LECO</t>
+  </si>
+  <si>
+    <t>AFYA</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>PPBN</t>
+  </si>
+  <si>
+    <t>DKS</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>EDRY</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>BMEA</t>
+  </si>
+  <si>
+    <t>ITCI</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>SPXC</t>
   </si>
   <si>
     <t>DDOG</t>
   </si>
   <si>
-    <t>GBX</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>BPMC</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t>EVR</t>
-  </si>
-  <si>
-    <t>DOOR</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>CELC</t>
-  </si>
-  <si>
-    <t>AXSM</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>UCTT</t>
-  </si>
-  <si>
-    <t>FOR</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>ASMIY</t>
-  </si>
-  <si>
-    <t>PATK</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>CFLT</t>
-  </si>
-  <si>
-    <t>BXC</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>GWRE</t>
-  </si>
-  <si>
-    <t>KLAC</t>
-  </si>
-  <si>
-    <t>SILXY</t>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>COKE</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>HOFT</t>
+  </si>
+  <si>
+    <t>CDRE</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>HNI</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>QNST</t>
+  </si>
+  <si>
+    <t>KCLI</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>RYAAY</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>USLM</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>JELD</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ALLY</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>LEN</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>HOLI</t>
+  </si>
+  <si>
+    <t>GLOB</t>
+  </si>
+  <si>
+    <t>CNXN</t>
+  </si>
+  <si>
+    <t>IHG</t>
+  </si>
+  <si>
+    <t>AX</t>
+  </si>
+  <si>
+    <t>CSL</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>APLS</t>
+  </si>
+  <si>
+    <t>KNSA</t>
+  </si>
+  <si>
+    <t>GPOR</t>
+  </si>
+  <si>
+    <t>NMM</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>CWCO</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>CVLG</t>
+  </si>
+  <si>
+    <t>RCKY</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>CMG</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>EML</t>
+  </si>
+  <si>
+    <t>ENVA</t>
+  </si>
+  <si>
+    <t>SPLK</t>
+  </si>
+  <si>
+    <t>CAAP</t>
+  </si>
+  <si>
+    <t>UFPT</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>PJT</t>
+  </si>
+  <si>
+    <t>DMRC</t>
+  </si>
+  <si>
+    <t>FSS</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>BWMN</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>BAH</t>
+  </si>
+  <si>
+    <t>HWM</t>
+  </si>
+  <si>
+    <t>PFSI</t>
+  </si>
+  <si>
+    <t>NGVC</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>KTB</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>WIRE</t>
+  </si>
+  <si>
+    <t>XRX</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>ISRG</t>
+  </si>
+  <si>
+    <t>PIPR</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>CVCO</t>
+  </si>
+  <si>
+    <t>AVTE</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>RRR</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>DBX</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>IMCR</t>
+  </si>
+  <si>
+    <t>DDS</t>
+  </si>
+  <si>
+    <t>AMNB</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>PUBGY</t>
+  </si>
+  <si>
+    <t>VNO</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>MAS</t>
+  </si>
+  <si>
+    <t>RHP</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>AXP</t>
+  </si>
+  <si>
+    <t>CPLP</t>
+  </si>
+  <si>
+    <t>BZH</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>FRO</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>JNPR</t>
+  </si>
+  <si>
+    <t>SPG</t>
+  </si>
+  <si>
+    <t>PGPEF</t>
+  </si>
+  <si>
+    <t>STNG</t>
+  </si>
+  <si>
+    <t>ZG</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>WRK</t>
+  </si>
+  <si>
+    <t>CBZ</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>CENT</t>
+  </si>
+  <si>
+    <t>GWW</t>
+  </si>
+  <si>
+    <t>BBWI</t>
+  </si>
+  <si>
+    <t>XOMA</t>
+  </si>
+  <si>
+    <t>PLMR</t>
+  </si>
+  <si>
+    <t>REZI</t>
+  </si>
+  <si>
+    <t>FSUMF</t>
+  </si>
+  <si>
+    <t>MYRG</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>ASO</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>SAP</t>
   </si>
   <si>
     <t>PBR</t>
   </si>
   <si>
-    <t>GDDY</t>
-  </si>
-  <si>
-    <t>KRT</t>
-  </si>
-  <si>
-    <t>TRIP</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>HLNE</t>
-  </si>
-  <si>
-    <t>AGO</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>MLKN</t>
-  </si>
-  <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>AYI</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>CVLT</t>
-  </si>
-  <si>
-    <t>PPBN</t>
-  </si>
-  <si>
-    <t>VECO</t>
-  </si>
-  <si>
-    <t>AMWD</t>
-  </si>
-  <si>
-    <t>KAI</t>
-  </si>
-  <si>
-    <t>NS</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>KTOS</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>CSWI</t>
-  </si>
-  <si>
-    <t>AWI</t>
-  </si>
-  <si>
-    <t>THC</t>
-  </si>
-  <si>
-    <t>SIG</t>
-  </si>
-  <si>
-    <t>ENTG</t>
-  </si>
-  <si>
-    <t>BMEA</t>
-  </si>
-  <si>
-    <t>AFYA</t>
-  </si>
-  <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>ISTR</t>
-  </si>
-  <si>
-    <t>FRO</t>
-  </si>
-  <si>
-    <t>MNDY</t>
-  </si>
-  <si>
-    <t>APLS</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>JXN</t>
-  </si>
-  <si>
-    <t>NHC</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>PSN</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>KCLI</t>
-  </si>
-  <si>
-    <t>NPO</t>
-  </si>
-  <si>
-    <t>SBS</t>
-  </si>
-  <si>
-    <t>SFM</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>HIBB</t>
-  </si>
-  <si>
-    <t>DBRG</t>
-  </si>
-  <si>
-    <t>TDG</t>
-  </si>
-  <si>
-    <t>KOP</t>
-  </si>
-  <si>
-    <t>AAON</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>PKOH</t>
+    <t>PGR</t>
   </si>
   <si>
     <t>SONO</t>
   </si>
   <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <t>NGVC</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>SCSC</t>
-  </si>
-  <si>
-    <t>KD</t>
-  </si>
-  <si>
-    <t>HOLI</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>NTRA</t>
-  </si>
-  <si>
-    <t>MELI</t>
+    <t>DY</t>
   </si>
   <si>
     <t>DLHC</t>
   </si>
   <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>VEL</t>
-  </si>
-  <si>
-    <t>ISRG</t>
-  </si>
-  <si>
-    <t>MBIN</t>
-  </si>
-  <si>
-    <t>NSIT</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>ERIE</t>
-  </si>
-  <si>
-    <t>NEU</t>
-  </si>
-  <si>
-    <t>PUBGY</t>
-  </si>
-  <si>
-    <t>CSL</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>BBU</t>
-  </si>
-  <si>
-    <t>PSX</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>CDRE</t>
-  </si>
-  <si>
-    <t>ALTR</t>
-  </si>
-  <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>SPLK</t>
-  </si>
-  <si>
-    <t>FWRG</t>
-  </si>
-  <si>
-    <t>LEN</t>
-  </si>
-  <si>
-    <t>QTWO</t>
+    <t>SCVL</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>VSEC</t>
+  </si>
+  <si>
+    <t>MFC</t>
+  </si>
+  <si>
+    <t>FONR</t>
+  </si>
+  <si>
+    <t>BPOP</t>
   </si>
   <si>
     <t>INTC</t>
   </si>
   <si>
-    <t>KTB</t>
-  </si>
-  <si>
-    <t>MRVL</t>
-  </si>
-  <si>
-    <t>KDSKF</t>
-  </si>
-  <si>
-    <t>USLM</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>RYAAY</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>SPXC</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>KNSA</t>
-  </si>
-  <si>
-    <t>WDC</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>ZEUS</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>JHX</t>
-  </si>
-  <si>
-    <t>NWS</t>
-  </si>
-  <si>
-    <t>BAH</t>
-  </si>
-  <si>
-    <t>IMCR</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>EDRY</t>
-  </si>
-  <si>
-    <t>REVG</t>
-  </si>
-  <si>
-    <t>IHG</t>
+    <t>SPH</t>
+  </si>
+  <si>
+    <t>NATR</t>
+  </si>
+  <si>
+    <t>MGRC</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>MYGN</t>
+  </si>
+  <si>
+    <t>LAZ</t>
   </si>
   <si>
     <t>DFIN</t>
   </si>
   <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>NMM</t>
-  </si>
-  <si>
-    <t>HWM</t>
-  </si>
-  <si>
-    <t>STLA</t>
-  </si>
-  <si>
-    <t>PGPEF</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>HNI</t>
-  </si>
-  <si>
-    <t>GLOB</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>ALLY</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>QNST</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>CWCO</t>
-  </si>
-  <si>
-    <t>QTRX</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>AZTA</t>
-  </si>
-  <si>
-    <t>AXP</t>
-  </si>
-  <si>
-    <t>AXON</t>
-  </si>
-  <si>
-    <t>JELD</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>DMRC</t>
-  </si>
-  <si>
-    <t>CVCO</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>MCY</t>
-  </si>
-  <si>
-    <t>TDW</t>
-  </si>
-  <si>
-    <t>SAP</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>PSTG</t>
-  </si>
-  <si>
-    <t>STN</t>
-  </si>
-  <si>
-    <t>COKE</t>
-  </si>
-  <si>
-    <t>NATR</t>
-  </si>
-  <si>
-    <t>DKS</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>ZG</t>
-  </si>
-  <si>
-    <t>EML</t>
-  </si>
-  <si>
-    <t>MAS</t>
-  </si>
-  <si>
-    <t>WRK</t>
-  </si>
-  <si>
-    <t>CCS</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>TNK</t>
-  </si>
-  <si>
-    <t>SUN</t>
-  </si>
-  <si>
-    <t>MYGN</t>
-  </si>
-  <si>
-    <t>FSS</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>PCAR</t>
-  </si>
-  <si>
-    <t>GWW</t>
-  </si>
-  <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>PJT</t>
-  </si>
-  <si>
-    <t>PIPR</t>
-  </si>
-  <si>
-    <t>JNPR</t>
-  </si>
-  <si>
-    <t>AX</t>
-  </si>
-  <si>
-    <t>CAAP</t>
-  </si>
-  <si>
-    <t>CTLT</t>
-  </si>
-  <si>
-    <t>ITCI</t>
-  </si>
-  <si>
-    <t>GOLF</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>DBX</t>
-  </si>
-  <si>
-    <t>BKNG</t>
+    <t>SLVM</t>
+  </si>
+  <si>
+    <t>FSUGY</t>
+  </si>
+  <si>
+    <t>ITT</t>
   </si>
   <si>
     <t>SWDAF</t>
   </si>
   <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>GHLD</t>
+    <t>GCBC</t>
+  </si>
+  <si>
+    <t>SYF</t>
+  </si>
+  <si>
+    <t>WAL</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>PHR</t>
+  </si>
+  <si>
+    <t>TPR</t>
+  </si>
+  <si>
+    <t>BAP</t>
   </si>
   <si>
     <t>WDFC</t>
   </si>
   <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>PGR</t>
-  </si>
-  <si>
-    <t>FRPT</t>
-  </si>
-  <si>
-    <t>XP</t>
-  </si>
-  <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>ALOT</t>
-  </si>
-  <si>
-    <t>RRR</t>
-  </si>
-  <si>
-    <t>ITT</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>GPOR</t>
-  </si>
-  <si>
-    <t>CENT</t>
-  </si>
-  <si>
-    <t>LZB</t>
-  </si>
-  <si>
-    <t>PRIM</t>
-  </si>
-  <si>
-    <t>LRN</t>
-  </si>
-  <si>
-    <t>RCKY</t>
-  </si>
-  <si>
-    <t>GBOOY</t>
-  </si>
-  <si>
-    <t>MLM</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>RELX</t>
-  </si>
-  <si>
-    <t>UPWK</t>
-  </si>
-  <si>
-    <t>LAKE</t>
-  </si>
-  <si>
-    <t>RHP</t>
-  </si>
-  <si>
-    <t>CNXN</t>
-  </si>
-  <si>
-    <t>DY</t>
-  </si>
-  <si>
-    <t>FMX</t>
-  </si>
-  <si>
-    <t>MGRC</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>VNO</t>
-  </si>
-  <si>
-    <t>BSX</t>
-  </si>
-  <si>
     <t>NX</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>CPLP</t>
-  </si>
-  <si>
-    <t>ARCH</t>
-  </si>
-  <si>
-    <t>PFSI</t>
-  </si>
-  <si>
-    <t>LECO</t>
-  </si>
-  <si>
-    <t>MPC</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>BZH</t>
-  </si>
-  <si>
-    <t>RGEN</t>
-  </si>
-  <si>
-    <t>LDOS</t>
-  </si>
-  <si>
-    <t>FOUR</t>
-  </si>
-  <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>FSUMF</t>
-  </si>
-  <si>
-    <t>MYRG</t>
-  </si>
-  <si>
-    <t>LOB</t>
-  </si>
-  <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>BWMN</t>
-  </si>
-  <si>
-    <t>TRMD</t>
   </si>
 </sst>
 </file>
@@ -1918,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1934,7 +1937,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>993.0118760204987</v>
+        <v>952.1610406842551</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1950,7 +1953,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>501.9502149887406</v>
+        <v>574.4674227957686</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1958,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>496.0769481609699</v>
+        <v>512.4912594398529</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1966,7 +1969,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>467.8637430884435</v>
+        <v>472.4602006389215</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1974,7 +1977,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>465.7367975178112</v>
+        <v>467.2623431650007</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1982,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>447.8968668729</v>
+        <v>442.7697131394341</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1990,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>439.7222886108577</v>
+        <v>434.9129104283135</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1998,7 +2001,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>405.5656454918984</v>
+        <v>416.4295589029501</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2006,7 +2009,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>357.4438141193338</v>
+        <v>384.311712216596</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2014,7 +2017,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>356.5019199808208</v>
+        <v>380.3374586383059</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2022,7 +2025,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>333.605556285777</v>
+        <v>352.9798127668435</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2030,7 +2033,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>313.964862765867</v>
+        <v>344.129702496924</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2038,7 +2041,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>313.5987690546785</v>
+        <v>332.3168489099905</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2046,7 +2049,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>310.4030967752407</v>
+        <v>314.7006267078487</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2054,7 +2057,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>300.0448570886946</v>
+        <v>313.964862765867</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2062,7 +2065,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>299.5753742655253</v>
+        <v>313.864149515699</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2070,7 +2073,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>290.6358455925627</v>
+        <v>291.20795686529</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2078,7 +2081,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>278.1506883820032</v>
+        <v>290.6868049750683</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2086,7 +2089,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>278.0890132827783</v>
+        <v>289.4867241549439</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2094,7 +2097,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>276.7357875936636</v>
+        <v>280.0531083227832</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2102,7 +2105,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>276.5832119839652</v>
+        <v>278.6522457523411</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2110,7 +2113,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>275.9520683589604</v>
+        <v>274.8920887172121</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2118,7 +2121,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>271.4837988434024</v>
+        <v>272.619655556782</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2126,7 +2129,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>269.3136901929224</v>
+        <v>269.79462210015</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2134,7 +2137,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>266.6536454026689</v>
+        <v>268.0806618935715</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2142,7 +2145,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>266.55833921498</v>
+        <v>267.4482583065148</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2150,7 +2153,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>264.8245589260223</v>
+        <v>265.0275309793848</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2158,7 +2161,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>257.1335801553731</v>
+        <v>262.2422879475207</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2166,7 +2169,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>251.4455606825062</v>
+        <v>251.6139741457112</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2174,7 +2177,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>249.4932697692256</v>
+        <v>249.9056699335496</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2182,7 +2185,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>243.2233895107867</v>
+        <v>246.1851932814934</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2190,7 +2193,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>242.4604169142983</v>
+        <v>244.653547272267</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2198,7 +2201,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>238.2534730035777</v>
+        <v>244.2320735334746</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2206,7 +2209,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>236.9789021125949</v>
+        <v>243.4387949050277</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2214,7 +2217,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>234.4084465662514</v>
+        <v>242.9829182047355</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2222,7 +2225,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>233.6418656296866</v>
+        <v>240.7728960866883</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2230,7 +2233,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>227.9615872059833</v>
+        <v>240.1087380834998</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2238,7 +2241,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>227.0826569836406</v>
+        <v>231.9304566977752</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2246,7 +2249,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>226.8948645524051</v>
+        <v>227.6678962820738</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2254,7 +2257,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>225.9208302783726</v>
+        <v>225.7669087874366</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2262,7 +2265,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>224.5255910451171</v>
+        <v>225.3145202287657</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2270,7 +2273,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>221.0440802197559</v>
+        <v>223.0903624939791</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2278,7 +2281,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>218.1784368952755</v>
+        <v>221.0837185537965</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2286,7 +2289,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>217.3557078674006</v>
+        <v>220.8022563441733</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2294,7 +2297,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>216.8306241432174</v>
+        <v>220.2418723124757</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2302,7 +2305,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>216.7968484493946</v>
+        <v>219.991673147452</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2310,7 +2313,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>216.0162322186133</v>
+        <v>213.8582265076487</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2318,7 +2321,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>213.4866432393798</v>
+        <v>213.7555898380171</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2326,7 +2329,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>212.8528011224376</v>
+        <v>212.8266568434063</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2334,7 +2337,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>210.9807257945843</v>
+        <v>212.0648711547115</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2342,7 +2345,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>210.9415739068598</v>
+        <v>211.4823372216812</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2350,7 +2353,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>210.9070191002552</v>
+        <v>211.4422246416734</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2358,7 +2361,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>208.1965927520661</v>
+        <v>210.0468454967792</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2366,7 +2369,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>206.9273917538011</v>
+        <v>209.6557334192852</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2374,7 +2377,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>206.7698828412172</v>
+        <v>209.2580015770911</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2382,7 +2385,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>203.7489984402841</v>
+        <v>207.92422543072</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2390,7 +2393,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>203.5986282707769</v>
+        <v>206.3071012683102</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2398,7 +2401,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>202.6096650581405</v>
+        <v>203.846198815573</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2406,7 +2409,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>202.1653902248305</v>
+        <v>203.5734217182534</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2414,7 +2417,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>198.7913869226044</v>
+        <v>203.1884200319871</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2422,7 +2425,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>195.3466461734932</v>
+        <v>201.3414338221835</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2430,7 +2433,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>194.9099176565227</v>
+        <v>200.6996334186361</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2438,7 +2441,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>194.7807394147801</v>
+        <v>200.2073334951956</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2446,7 +2449,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>194.5602738381466</v>
+        <v>200.0604999830715</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2454,7 +2457,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>194.0961880894919</v>
+        <v>194.6015157800755</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2462,7 +2465,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>193.6581544618578</v>
+        <v>193.8139692606766</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2470,7 +2473,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>193.5639206213303</v>
+        <v>192.7495882992732</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2478,7 +2481,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>193.0507495175515</v>
+        <v>191.5164890637168</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2486,7 +2489,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>191.0566652101926</v>
+        <v>191.1396399049035</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2494,7 +2497,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>187.9959544375448</v>
+        <v>190.9027770663977</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2502,7 +2505,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>187.0326268094843</v>
+        <v>190.5055036575044</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2510,7 +2513,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>186.6064542440639</v>
+        <v>190.4681617412137</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2518,7 +2521,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>186.2873070672412</v>
+        <v>190.1712755895458</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2526,7 +2529,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>185.8805639487153</v>
+        <v>189.8729076088386</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2534,7 +2537,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>185.7382252009164</v>
+        <v>189.4763822300184</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2542,7 +2545,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>184.9179526679937</v>
+        <v>188.1309921473546</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2550,7 +2553,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>184.7730124910265</v>
+        <v>187.8383826158005</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2558,7 +2561,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>184.5176693170979</v>
+        <v>187.1128184811197</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2566,7 +2569,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>183.8592073261414</v>
+        <v>186.8698109912924</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2574,7 +2577,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>183.4098685618668</v>
+        <v>185.2939951103034</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2582,7 +2585,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>183.3867120389398</v>
+        <v>184.9821008465948</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2590,7 +2593,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>183.3397013248745</v>
+        <v>184.6386179807687</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2598,7 +2601,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>183.0671825424205</v>
+        <v>183.5416829861585</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2606,7 +2609,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>182.8219132933098</v>
+        <v>182.6249865484989</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2614,7 +2617,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>181.8470391845812</v>
+        <v>181.971861626282</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2622,7 +2625,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>181.8051086802839</v>
+        <v>181.8024061245602</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2630,7 +2633,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>181.0029853824078</v>
+        <v>180.7485579499775</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2638,7 +2641,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>180.2942159653385</v>
+        <v>180.5006879000337</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2646,7 +2649,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>179.8149000360741</v>
+        <v>180.1085914131051</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2654,7 +2657,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>179.6776311116332</v>
+        <v>179.4782738021327</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2662,7 +2665,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>179.0537438625254</v>
+        <v>179.3146463123026</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2670,7 +2673,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>178.3000332019203</v>
+        <v>178.4772309888049</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2678,7 +2681,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>178.2761751248962</v>
+        <v>178.4135718699315</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2686,7 +2689,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>178.1352526580611</v>
+        <v>177.9699274497758</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2694,7 +2697,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>177.3291868992648</v>
+        <v>176.3766340973736</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2702,7 +2705,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>175.8294413339237</v>
+        <v>176.1214189796679</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2710,7 +2713,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>175.6194993449164</v>
+        <v>175.7789597048523</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2718,7 +2721,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>175.3450533442745</v>
+        <v>175.0509145189149</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2726,7 +2729,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>174.7980890393005</v>
+        <v>175.0497469725911</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2734,7 +2737,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>174.5292743560361</v>
+        <v>174.5957635085009</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2742,7 +2745,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>174.2665816847922</v>
+        <v>174.3587821387607</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2750,7 +2753,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>174.1995475324639</v>
+        <v>174.3047564073049</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2758,7 +2761,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>173.2192721323784</v>
+        <v>173.0034574155072</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2766,7 +2769,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>172.9227369891877</v>
+        <v>172.7876433257744</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2774,7 +2777,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>172.9087698639939</v>
+        <v>172.6082367382666</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2782,7 +2785,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>172.7060855337455</v>
+        <v>171.542442890974</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2790,7 +2793,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>172.1386282587162</v>
+        <v>171.0512362548167</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2798,7 +2801,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>172.1173390655148</v>
+        <v>170.9077934397905</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2806,7 +2809,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>171.3112139345328</v>
+        <v>170.818544576336</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2814,7 +2817,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>170.2580240358326</v>
+        <v>170.7578587498603</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2822,7 +2825,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>170.030228098906</v>
+        <v>170.5491165110062</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2830,7 +2833,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>169.9010348832895</v>
+        <v>170.4260280866168</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2838,7 +2841,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>169.7360061252195</v>
+        <v>170.3317984797958</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2846,7 +2849,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>169.0407875714442</v>
+        <v>169.9839487232292</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2854,7 +2857,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>167.7932685676735</v>
+        <v>169.1641438711346</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2862,7 +2865,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>167.6243860507081</v>
+        <v>169.0982536460868</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2870,7 +2873,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>167.5136713694659</v>
+        <v>168.9077536679874</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2878,7 +2881,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>167.1318797548075</v>
+        <v>168.8110523440444</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2886,7 +2889,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>166.6631694584948</v>
+        <v>168.7146957314439</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2894,7 +2897,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>166.4973290679817</v>
+        <v>168.368657868436</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2902,7 +2905,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>166.4703427474792</v>
+        <v>168.3132791689028</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2910,7 +2913,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>166.3961327747301</v>
+        <v>168.1881327356786</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2918,7 +2921,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>165.9932655528489</v>
+        <v>167.5299581584952</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2926,7 +2929,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>165.9675511334461</v>
+        <v>167.4553209352694</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2934,7 +2937,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>165.6009984308646</v>
+        <v>167.0253793255278</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2942,7 +2945,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>165.5051101307496</v>
+        <v>166.7139681878746</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2950,7 +2953,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>165.1212143168495</v>
+        <v>166.4490031101861</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2958,7 +2961,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>164.847054124522</v>
+        <v>166.4361891583767</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2966,7 +2969,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>164.7126386019181</v>
+        <v>166.2046566999933</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2974,7 +2977,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>164.6360362420815</v>
+        <v>165.9930952992201</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2982,7 +2985,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>164.1222674798733</v>
+        <v>165.9327602452691</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2990,7 +2993,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>164.0456553824763</v>
+        <v>165.3108511970274</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2998,7 +3001,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>163.8423051585371</v>
+        <v>165.3045275027268</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3006,7 +3009,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>163.7571677461654</v>
+        <v>165.1501352358471</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3014,7 +3017,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>163.3961473383027</v>
+        <v>165.082377577493</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3022,7 +3025,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>163.3940173409482</v>
+        <v>164.9390989925772</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3030,7 +3033,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>162.76289294951</v>
+        <v>164.2264355185392</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3038,7 +3041,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>162.6087197992098</v>
+        <v>164.1599289070231</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3046,7 +3049,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>162.4789787535335</v>
+        <v>163.1308254394053</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3054,7 +3057,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>162.4250962681461</v>
+        <v>162.6979150748597</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3062,7 +3065,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>162.0007375049034</v>
+        <v>162.6273973115567</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3070,7 +3073,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>161.8057276185583</v>
+        <v>162.6026381705777</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3078,7 +3081,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>161.3276023918729</v>
+        <v>162.2694406545614</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3086,7 +3089,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>160.9174722483266</v>
+        <v>162.1158829082273</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3094,7 +3097,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>160.9036620049415</v>
+        <v>161.4827460025753</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3102,7 +3105,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>160.7637484060138</v>
+        <v>161.3411031637729</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3110,7 +3113,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>160.6397089379776</v>
+        <v>161.1839425719712</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3118,7 +3121,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>159.8370759511383</v>
+        <v>161.1797193933612</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3126,7 +3129,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>159.7736350478393</v>
+        <v>161.0365481673622</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3134,7 +3137,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>159.6733940919481</v>
+        <v>160.829754420714</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3142,7 +3145,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>159.0531376526341</v>
+        <v>160.7905850045628</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3150,7 +3153,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>158.86482706354</v>
+        <v>160.6749818345714</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3158,7 +3161,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>158.5192756147213</v>
+        <v>160.6162919972001</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3166,7 +3169,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>158.4631051451589</v>
+        <v>160.5975319416088</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3174,7 +3177,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>158.3464586609861</v>
+        <v>160.4050841785208</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3182,7 +3185,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>158.2882074408374</v>
+        <v>160.308493646598</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3190,7 +3193,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>158.2635046526287</v>
+        <v>160.1605228396694</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3198,7 +3201,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>158.130916238728</v>
+        <v>160.0510934875579</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3206,7 +3209,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>157.8416653006802</v>
+        <v>159.8921234804399</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3214,7 +3217,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>157.7112852777196</v>
+        <v>159.746860616816</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3222,7 +3225,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>157.5148235622562</v>
+        <v>159.5975931491502</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3230,7 +3233,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>156.9072048425875</v>
+        <v>159.0966122230364</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3238,7 +3241,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>156.7832386076331</v>
+        <v>158.6060649786014</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3246,7 +3249,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>156.6282812909215</v>
+        <v>158.5537849291667</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3254,7 +3257,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>155.7895396300546</v>
+        <v>158.4927646009274</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3262,7 +3265,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>155.5666639498032</v>
+        <v>157.9250050533362</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3270,7 +3273,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>155.4913257852101</v>
+        <v>157.8968545818402</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3278,7 +3281,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>155.3058013928895</v>
+        <v>157.3160283128504</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3286,7 +3289,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>155.2579830547822</v>
+        <v>157.2186611625988</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3294,7 +3297,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>155.040388683078</v>
+        <v>157.1605400664508</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3302,7 +3305,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>154.5908340443499</v>
+        <v>156.8570656665011</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3310,7 +3313,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>154.4377640074869</v>
+        <v>156.7252519626622</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3318,7 +3321,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>154.4242077025185</v>
+        <v>156.5443771770912</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3326,7 +3329,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>154.2997203330521</v>
+        <v>156.5160121507495</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3334,7 +3337,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>154.095301282314</v>
+        <v>156.4604627353314</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3342,7 +3345,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>154.0355158500684</v>
+        <v>156.2699679346556</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3350,7 +3353,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>153.9769851186637</v>
+        <v>155.7149164387489</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3358,7 +3361,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>153.9016945468901</v>
+        <v>155.4214389709048</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3366,7 +3369,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>153.8678701343113</v>
+        <v>155.3885123355786</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3374,7 +3377,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>153.79373494229</v>
+        <v>155.3210000376918</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3382,7 +3385,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>153.7301979762256</v>
+        <v>155.2869162065143</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3390,7 +3393,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>153.4730926774123</v>
+        <v>155.2697065702189</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3398,7 +3401,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>153.4266012259737</v>
+        <v>155.2665922094037</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3406,7 +3409,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>153.0055261148817</v>
+        <v>155.2508061589254</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3414,7 +3417,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>152.9481155682125</v>
+        <v>155.0400873938374</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -3422,7 +3425,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>152.9051326626987</v>
+        <v>154.9240753847274</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -3430,7 +3433,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>152.8927196107902</v>
+        <v>154.1707468969185</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3438,7 +3441,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>152.7252304472475</v>
+        <v>154.0220918450032</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3446,7 +3449,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>152.30799203296</v>
+        <v>153.9076175904028</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3454,7 +3457,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>152.227924477125</v>
+        <v>153.7730145736938</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3462,7 +3465,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>151.6673765246762</v>
+        <v>153.7210104968901</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3470,7 +3473,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>151.6138198421972</v>
+        <v>153.6674770273514</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3478,7 +3481,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>151.4017703936251</v>
+        <v>153.6569846051624</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3486,7 +3489,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>151.3992675431089</v>
+        <v>153.6189160392408</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3494,7 +3497,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>151.3530072150283</v>
+        <v>153.5710585612534</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3502,7 +3505,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>151.332847032617</v>
+        <v>153.0835606094885</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3510,7 +3513,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>151.0995752802726</v>
+        <v>153.0347718383562</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3518,7 +3521,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>151.0566802759085</v>
+        <v>152.8620911214278</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3526,7 +3529,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>151.0494711920319</v>
+        <v>152.3815891455287</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3534,7 +3537,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>150.9596325127919</v>
+        <v>151.92859466097</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3542,7 +3545,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>150.6872561811326</v>
+        <v>151.8597811729161</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3550,7 +3553,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>150.5043919249341</v>
+        <v>151.7576169190243</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3558,7 +3561,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>150.4859768991003</v>
+        <v>151.597218096595</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3566,7 +3569,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>150.4030492558813</v>
+        <v>151.5296171487744</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3574,7 +3577,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>150.1584299458016</v>
+        <v>151.5281439212168</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3582,7 +3585,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>149.8756807576229</v>
+        <v>151.5055302285114</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3590,7 +3593,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>149.7020620080436</v>
+        <v>151.0437044712974</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3598,7 +3601,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>149.5126865731177</v>
+        <v>150.793765578433</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3606,7 +3609,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>149.4644877044751</v>
+        <v>150.5697292686278</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3614,7 +3617,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>149.3293091402235</v>
+        <v>150.0695316640594</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3622,7 +3625,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>149.2981109241952</v>
+        <v>149.7760179240261</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3630,7 +3633,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>149.080876421635</v>
+        <v>149.7018322561275</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3638,7 +3641,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>149.0311079770999</v>
+        <v>149.6326270157741</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3646,7 +3649,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>148.5863051336133</v>
+        <v>149.4996070950543</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3654,7 +3657,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>148.5605142748601</v>
+        <v>149.2256376509808</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3662,7 +3665,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>148.4081194986588</v>
+        <v>149.222242147628</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3670,7 +3673,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>148.3343361039399</v>
+        <v>149.1457740936939</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3678,7 +3681,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>148.3002315045435</v>
+        <v>149.1330852898585</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3686,7 +3689,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>148.2912780905471</v>
+        <v>149.1143020050641</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3694,7 +3697,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>147.7736355779643</v>
+        <v>149.0221590723868</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3702,7 +3705,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>147.6763285357554</v>
+        <v>148.915273233594</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3710,7 +3713,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>147.1095565593818</v>
+        <v>148.9070186123722</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3718,7 +3721,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>146.8705056413796</v>
+        <v>148.8741085590092</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3726,7 +3729,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>146.866626496892</v>
+        <v>148.8501637205502</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3734,7 +3737,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>146.5901157019858</v>
+        <v>148.6907835701901</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3742,7 +3745,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>146.5204046373005</v>
+        <v>148.6350616250891</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3750,7 +3753,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>146.0381306677117</v>
+        <v>148.5886508193919</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3758,7 +3761,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>145.8202837004987</v>
+        <v>148.3346114536579</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3766,7 +3769,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>145.7083641504138</v>
+        <v>148.1503099521756</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3774,7 +3777,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>145.6422661571636</v>
+        <v>148.1340667614234</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3782,7 +3785,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>145.6389299657713</v>
+        <v>148.1240596045525</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3790,7 +3793,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>145.6195937103561</v>
+        <v>148.0648153026395</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3798,7 +3801,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>145.3429103151014</v>
+        <v>148.0474140905396</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3806,7 +3809,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>145.0364433819561</v>
+        <v>147.9414335819244</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3814,7 +3817,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>144.9833797159702</v>
+        <v>147.5719549783491</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3822,7 +3825,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>144.8505876020079</v>
+        <v>147.4411235168573</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3830,7 +3833,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>144.5495647205423</v>
+        <v>147.2401167534479</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3838,7 +3841,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>144.4280502958692</v>
+        <v>147.0190252767957</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3846,7 +3849,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>144.2951731517515</v>
+        <v>146.9822438102071</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3854,7 +3857,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>144.2172921360329</v>
+        <v>146.5036340637371</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3862,7 +3865,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>144.0055322160865</v>
+        <v>146.3155806161165</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3870,7 +3873,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>143.8860731970635</v>
+        <v>146.278932853952</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3878,7 +3881,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>143.79641013781</v>
+        <v>146.1285053586191</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3886,7 +3889,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>143.7518447743103</v>
+        <v>146.0700636359962</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3894,7 +3897,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>143.6720189399621</v>
+        <v>145.9369908927859</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3902,7 +3905,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>143.350006598375</v>
+        <v>145.8470763201506</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3910,7 +3913,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>143.270153486762</v>
+        <v>145.6123646246551</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3918,7 +3921,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>143.1989858525894</v>
+        <v>145.2475082041239</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3926,7 +3929,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>143.167402405357</v>
+        <v>145.1754315035232</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3934,7 +3937,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>143.153612439664</v>
+        <v>145.1120382609269</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3942,7 +3945,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>143.0929445445091</v>
+        <v>144.8344639739914</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3950,7 +3953,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>142.9853168152086</v>
+        <v>144.7622746743536</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3958,7 +3961,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>142.8257246063277</v>
+        <v>144.7344708911768</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3966,7 +3969,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>142.7734463703551</v>
+        <v>144.7000116467767</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3974,7 +3977,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>142.7475267902678</v>
+        <v>144.4365305669562</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3982,7 +3985,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>142.6578558301345</v>
+        <v>144.4015664084325</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3990,7 +3993,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>142.6314331034537</v>
+        <v>144.2536207840737</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3998,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>142.5325023314945</v>
+        <v>144.201703772354</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4006,7 +4009,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>142.3904987565423</v>
+        <v>144.1766285558855</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4014,7 +4017,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>142.3822072827061</v>
+        <v>144.1522560579459</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4022,7 +4025,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>142.3292676753946</v>
+        <v>144.0410884377031</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4030,7 +4033,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>142.2790251814566</v>
+        <v>143.797195159445</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4038,7 +4041,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>142.2355648174488</v>
+        <v>143.7773927879591</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4046,7 +4049,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>142.2189115550009</v>
+        <v>143.6929410204513</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4054,7 +4057,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>142.1307114684748</v>
+        <v>143.6280835667835</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4062,7 +4065,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>142.1014729476676</v>
+        <v>143.6139976412302</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4070,7 +4073,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>141.9286902497569</v>
+        <v>143.3891081601116</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4078,7 +4081,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>141.8356896648192</v>
+        <v>143.3336353652158</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4086,7 +4089,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>141.6775809258328</v>
+        <v>143.325881782841</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4094,7 +4097,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>141.6573320586146</v>
+        <v>143.2541176709967</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4102,7 +4105,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>141.6009192508177</v>
+        <v>143.2135871214038</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4110,7 +4113,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>141.469055414031</v>
+        <v>143.0514076215094</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4118,7 +4121,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>141.3233236090321</v>
+        <v>142.9550190119734</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4126,7 +4129,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>141.2952558456391</v>
+        <v>142.8035586007938</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4134,7 +4137,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>141.281393701315</v>
+        <v>142.7709826447743</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4142,7 +4145,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>141.0687392909593</v>
+        <v>142.7223578824749</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4150,7 +4153,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>140.837043568145</v>
+        <v>142.4698780578472</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4158,7 +4161,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>140.7831771618348</v>
+        <v>142.3847444937108</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4166,7 +4169,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>140.7236282913396</v>
+        <v>142.2288386436049</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4174,7 +4177,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>140.622167925837</v>
+        <v>142.2239374411784</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4182,7 +4185,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>140.4954127429718</v>
+        <v>141.9814069066562</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4190,7 +4193,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>140.4667836254618</v>
+        <v>141.9615570283183</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4198,7 +4201,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>140.3183747117703</v>
+        <v>141.9280625098522</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4206,7 +4209,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>140.2812781175905</v>
+        <v>141.9113371249674</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4214,7 +4217,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>140.2709857312056</v>
+        <v>141.7209794121305</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4222,7 +4225,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>140.1426510915536</v>
+        <v>141.6474652189282</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4230,7 +4233,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>140.0032423823479</v>
+        <v>141.6048550076262</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4238,7 +4241,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>139.8758848999815</v>
+        <v>141.5584939770991</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4246,7 +4249,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>139.8700118011949</v>
+        <v>141.4303561027013</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4254,7 +4257,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>139.8260445616984</v>
+        <v>141.3306313251829</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4262,7 +4265,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>139.7526485789137</v>
+        <v>141.2668185472203</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4270,7 +4273,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>139.712898807347</v>
+        <v>141.2113699009201</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4278,7 +4281,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>139.5285521240404</v>
+        <v>141.0194996889242</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4286,7 +4289,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>139.4232606319929</v>
+        <v>140.8443228938744</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4294,7 +4297,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>139.4152053670403</v>
+        <v>140.7803615874485</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4302,7 +4305,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>139.07276009247</v>
+        <v>140.7717823186706</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4310,7 +4313,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>139.0717528399503</v>
+        <v>140.6740353375496</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4318,7 +4321,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>139.000141060723</v>
+        <v>140.6019683615472</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4326,7 +4329,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>138.8876838597598</v>
+        <v>140.570564057072</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4334,7 +4337,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>138.757530956834</v>
+        <v>140.5299853668633</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4342,7 +4345,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>138.4585106980577</v>
+        <v>140.5286248511245</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4350,7 +4353,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>138.3757021251016</v>
+        <v>140.4563441254241</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4358,7 +4361,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>138.3134976692729</v>
+        <v>140.4412009957717</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4366,7 +4369,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>138.3004934457557</v>
+        <v>140.4078124968144</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4374,7 +4377,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>138.2247667539818</v>
+        <v>140.1508567730949</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4382,7 +4385,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>138.1946189360682</v>
+        <v>140.0650406596046</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4390,7 +4393,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>138.1649788922283</v>
+        <v>139.9608568098105</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4398,7 +4401,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>138.1421840395282</v>
+        <v>139.7836078939281</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4406,7 +4409,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>138.0678853327856</v>
+        <v>139.7502038792029</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4414,7 +4417,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>137.9319397796686</v>
+        <v>139.6892986162769</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -4422,7 +4425,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>137.9089933130399</v>
+        <v>139.6123587974486</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -4430,7 +4433,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>137.8751069078024</v>
+        <v>139.5539356562642</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4438,7 +4441,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>137.8233476928218</v>
+        <v>139.463528368292</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4446,7 +4449,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>137.7289479185786</v>
+        <v>139.4418416807437</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4454,7 +4457,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>137.5998302442785</v>
+        <v>139.4291973820562</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4462,7 +4465,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>137.5620665023833</v>
+        <v>139.3189540153565</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4470,7 +4473,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>137.5492988083257</v>
+        <v>139.2220132505952</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4478,7 +4481,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>137.5225269094026</v>
+        <v>139.1886707086</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4486,7 +4489,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>137.4917762612925</v>
+        <v>139.1511814174104</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4494,7 +4497,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>137.3091374238749</v>
+        <v>139.091525926522</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4502,7 +4505,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>137.1305287063741</v>
+        <v>139.0254593664064</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4510,7 +4513,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>137.0777665358281</v>
+        <v>139.0221498180411</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4518,7 +4521,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>137.0736211891701</v>
+        <v>139.0118735281979</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4526,7 +4529,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>137.0475751390173</v>
+        <v>138.9967678491392</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4534,7 +4537,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>136.8932059297087</v>
+        <v>138.991556121747</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4542,7 +4545,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>136.8830822531503</v>
+        <v>138.942460177695</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4550,7 +4553,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>136.8762115340304</v>
+        <v>138.9306436577899</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4558,7 +4561,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>136.8272427162115</v>
+        <v>138.9305577100772</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4566,7 +4569,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>136.7870332700534</v>
+        <v>138.7665337174682</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4574,7 +4577,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>136.5896591056988</v>
+        <v>138.7621214133535</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4582,7 +4585,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>136.5888155444449</v>
+        <v>138.4453001028014</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4590,7 +4593,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>136.5820695450764</v>
+        <v>138.3555099368631</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4598,7 +4601,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>136.5664519846778</v>
+        <v>138.351073687169</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4606,7 +4609,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>136.5588552686513</v>
+        <v>138.1344811207482</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4614,7 +4617,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>136.5134546717367</v>
+        <v>138.0202686034483</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4622,7 +4625,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>136.510856857912</v>
+        <v>137.9776357841513</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4630,7 +4633,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>136.4946885430332</v>
+        <v>137.9774717493777</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4638,7 +4641,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>136.3425062120198</v>
+        <v>137.886984935802</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4646,7 +4649,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>136.240501535632</v>
+        <v>137.8771069127125</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4654,7 +4657,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>136.149696433469</v>
+        <v>137.8537210104483</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4662,7 +4665,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>136.1343000627213</v>
+        <v>137.8064395317516</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4670,7 +4673,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>136.1167688559052</v>
+        <v>137.7818737478745</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4678,7 +4681,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>136.0283612725839</v>
+        <v>137.7487822425381</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4686,7 +4689,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>135.9898367487228</v>
+        <v>137.7481085816444</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4694,7 +4697,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>135.9564132216049</v>
+        <v>137.6631623218189</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4702,7 +4705,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>135.8944043923146</v>
+        <v>137.6357608026485</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4710,7 +4713,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>135.8659213812735</v>
+        <v>137.6051047758088</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4718,7 +4721,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>135.8204251442773</v>
+        <v>137.5677074223164</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4726,7 +4729,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>135.8133700575665</v>
+        <v>137.5078261479056</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4734,7 +4737,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>135.8010516678593</v>
+        <v>137.4488712200943</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4742,7 +4745,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>135.7845847834069</v>
+        <v>137.4100044033157</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4750,7 +4753,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>135.7775327278687</v>
+        <v>137.3951754783096</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4758,7 +4761,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>135.777217425524</v>
+        <v>137.3717127019078</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4766,7 +4769,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>135.696341430034</v>
+        <v>137.2439905249437</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4774,7 +4777,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>135.6785385298174</v>
+        <v>137.2414968948785</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4782,7 +4785,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>135.6714865845233</v>
+        <v>136.9199055059783</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4790,7 +4793,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>135.6437489798742</v>
+        <v>136.8966086700268</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4798,7 +4801,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>135.6228382269661</v>
+        <v>136.7648448728588</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4806,7 +4809,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>135.4493073430927</v>
+        <v>136.7562181924881</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4814,7 +4817,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>135.4233809437227</v>
+        <v>136.7475871419273</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4822,7 +4825,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>135.3660302608396</v>
+        <v>136.7084229871608</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4830,7 +4833,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>135.2723893503697</v>
+        <v>136.6728118405206</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4838,7 +4841,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>135.2609209140926</v>
+        <v>136.672146242307</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4846,7 +4849,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>135.2294264056247</v>
+        <v>136.6281824241374</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -4854,7 +4857,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>135.1369064179616</v>
+        <v>136.622411870566</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -4862,7 +4865,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>135.1184404643811</v>
+        <v>136.6218900158275</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -4870,7 +4873,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>135.0663314383268</v>
+        <v>136.6130266527108</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -4878,7 +4881,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>135.05611330084</v>
+        <v>136.4449891450951</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -4886,7 +4889,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>135.0307576311058</v>
+        <v>136.3895379615882</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -4894,7 +4897,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>135.0162056260318</v>
+        <v>136.362520286189</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -4902,7 +4905,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>134.9205196922295</v>
+        <v>136.3204318905187</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -4910,7 +4913,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>134.9120315388282</v>
+        <v>136.3165709655628</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -4918,7 +4921,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>134.7675143339929</v>
+        <v>136.3038400181987</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -4926,7 +4929,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>134.7369521197146</v>
+        <v>136.1470585481695</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -4934,7 +4937,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>134.6134762322478</v>
+        <v>136.1228328501329</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -4942,7 +4945,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>134.6131570464181</v>
+        <v>136.0947339689865</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -4950,7 +4953,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>134.5480889998557</v>
+        <v>136.0922696454659</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -4958,7 +4961,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>134.5077423355252</v>
+        <v>136.0908385377301</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -4966,7 +4969,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>134.4816530498618</v>
+        <v>136.0315986429879</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -4974,7 +4977,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>134.3423768536229</v>
+        <v>135.9082474193783</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -4982,7 +4985,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>134.3185113309643</v>
+        <v>135.8424667809095</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -4990,7 +4993,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>134.2330568107842</v>
+        <v>135.8113116182437</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -4998,7 +5001,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>134.2311972295556</v>
+        <v>135.733674985963</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5006,7 +5009,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>134.1972802944035</v>
+        <v>135.7057383302308</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5014,7 +5017,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>134.1218000012914</v>
+        <v>135.5732844191952</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5022,7 +5025,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>134.0887356560289</v>
+        <v>135.4338359978402</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5030,7 +5033,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>134.0706978202651</v>
+        <v>135.424444894522</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5038,7 +5041,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>134.0648806703029</v>
+        <v>135.38004764303</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5046,7 +5049,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>133.8666702648151</v>
+        <v>135.3452152935372</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5054,7 +5057,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>133.8331580648533</v>
+        <v>135.3305545925031</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5062,7 +5065,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>133.8288463997068</v>
+        <v>135.2602364342985</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5070,7 +5073,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>133.7814363366115</v>
+        <v>135.225789636551</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5078,7 +5081,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>133.6733717616019</v>
+        <v>135.2197469506932</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5086,7 +5089,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>133.578471733086</v>
+        <v>135.2147839591076</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5094,7 +5097,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>133.5517455804628</v>
+        <v>135.143692595718</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5102,7 +5105,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>133.5316917758043</v>
+        <v>135.1032881425067</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5110,7 +5113,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>133.5122898801307</v>
+        <v>134.9235365348869</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5118,7 +5121,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>133.4758687716442</v>
+        <v>134.8864638028099</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5126,7 +5129,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>133.4303669656856</v>
+        <v>134.7865819064378</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5134,7 +5137,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>133.4287969044585</v>
+        <v>134.6445997186187</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5142,7 +5145,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>133.3496372350919</v>
+        <v>134.5729434973776</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5150,7 +5153,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>133.2009906876031</v>
+        <v>134.4908802172189</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5158,7 +5161,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>133.1526995673106</v>
+        <v>134.4746099604771</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5166,7 +5169,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>133.0951091735079</v>
+        <v>134.4200565861081</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5174,7 +5177,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>133.0345319386588</v>
+        <v>134.313028567549</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5182,7 +5185,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>132.8606974725568</v>
+        <v>134.282989463613</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5190,7 +5193,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>132.7867263234683</v>
+        <v>134.2255687757858</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5198,7 +5201,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>132.6685312417383</v>
+        <v>134.1832354553839</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5206,7 +5209,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>132.3597795865131</v>
+        <v>134.1605030180027</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5214,7 +5217,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>132.3017531819189</v>
+        <v>133.9309337731709</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5222,7 +5225,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>132.2645678691204</v>
+        <v>133.9254913374075</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5230,7 +5233,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>132.247949881012</v>
+        <v>133.859619537572</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5238,7 +5241,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>132.2105418897723</v>
+        <v>133.8594620719003</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5246,7 +5249,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>132.1791428249641</v>
+        <v>133.8360470398028</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5254,7 +5257,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>132.1461889816248</v>
+        <v>133.8277429856861</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5262,7 +5265,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>132.1335650303092</v>
+        <v>133.8112882948815</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5270,7 +5273,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>132.107613301763</v>
+        <v>133.8091967054344</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5278,7 +5281,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>132.0922967519471</v>
+        <v>133.7470223899563</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5286,7 +5289,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>132.0055047455213</v>
+        <v>133.7169499990574</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5294,7 +5297,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>131.9862732497961</v>
+        <v>133.6639295128814</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5302,7 +5305,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>131.9716528205148</v>
+        <v>133.6473289424102</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5310,7 +5313,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>131.9506770923455</v>
+        <v>133.6203044651925</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5318,7 +5321,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>131.9334877013236</v>
+        <v>133.5338665489575</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5326,7 +5329,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>131.8892335357851</v>
+        <v>133.5286651582111</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5334,7 +5337,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>131.8828113013893</v>
+        <v>133.4704409487516</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5342,7 +5345,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>131.8141385415728</v>
+        <v>133.4340809307714</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5350,7 +5353,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>131.7293820784066</v>
+        <v>133.3880779971888</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5358,7 +5361,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>131.7218314513688</v>
+        <v>133.3626162204999</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5366,7 +5369,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>131.635055785486</v>
+        <v>133.3535376951698</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5374,7 +5377,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>131.5528423215511</v>
+        <v>133.3481586617093</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5382,7 +5385,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>131.5080563449507</v>
+        <v>133.2767864115389</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5390,7 +5393,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>131.371738915307</v>
+        <v>133.2607924657643</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5398,7 +5401,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>131.3689553832469</v>
+        <v>133.1531708146952</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5406,7 +5409,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>131.3168470501039</v>
+        <v>133.1054347000736</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5414,7 +5417,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>131.2583293614723</v>
+        <v>133.0763897016234</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -5422,7 +5425,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>131.2418158996013</v>
+        <v>133.0719182351639</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -5430,7 +5433,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>131.2281651718217</v>
+        <v>133.0436106801711</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -5438,7 +5441,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>131.1847081728993</v>
+        <v>133.0277902287309</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -5446,7 +5449,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>131.1636131856755</v>
+        <v>132.9949152634937</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -5454,7 +5457,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>131.1550718727375</v>
+        <v>132.9529175576483</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -5462,7 +5465,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>131.0718791149157</v>
+        <v>132.905384793962</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -5470,7 +5473,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>131.0688545601615</v>
+        <v>132.9031381656227</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -5478,7 +5481,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>131.0161634288398</v>
+        <v>132.9001307398944</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -5486,7 +5489,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>130.9908175574508</v>
+        <v>132.854889780675</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -5494,7 +5497,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>130.863944788545</v>
+        <v>132.7697161624091</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -5502,7 +5505,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>130.8588862090086</v>
+        <v>132.7162212371166</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -5510,7 +5513,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>130.8115438109213</v>
+        <v>132.7107462500755</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -5518,7 +5521,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>130.7781202492414</v>
+        <v>132.6891869011912</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -5526,7 +5529,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>130.6295161894465</v>
+        <v>132.6786989338985</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -5534,7 +5537,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>130.6074131791358</v>
+        <v>132.6354506472408</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -5542,7 +5545,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>130.5369201784649</v>
+        <v>132.5954776746657</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -5550,7 +5553,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>130.5273717485854</v>
+        <v>132.5954268874411</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -5558,7 +5561,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>130.5269369481896</v>
+        <v>132.5513268702032</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -5566,7 +5569,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>130.468765165976</v>
+        <v>132.4857113731321</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -5574,7 +5577,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>130.4663188942164</v>
+        <v>132.468012951102</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -5582,7 +5585,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>130.3890215026617</v>
+        <v>132.4222952330721</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -5590,7 +5593,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>130.3409533201896</v>
+        <v>132.4220498358883</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -5598,7 +5601,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>130.328051430999</v>
+        <v>132.3445752790196</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -5606,7 +5609,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>130.2232698255305</v>
+        <v>132.3158910413945</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -5614,7 +5617,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>130.2144633368873</v>
+        <v>132.2800530178514</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -5622,7 +5625,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>130.1573207532953</v>
+        <v>132.2412283120618</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -5630,7 +5633,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>130.0523698271155</v>
+        <v>132.1737036816361</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -5638,7 +5641,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>130.0353570197399</v>
+        <v>132.1315070298003</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -5646,7 +5649,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>129.957473993423</v>
+        <v>132.1201015215967</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -5654,7 +5657,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>129.9449890315277</v>
+        <v>131.9917168057956</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -5662,7 +5665,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>129.8224217422613</v>
+        <v>131.9361601327157</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -5670,7 +5673,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>129.7965216854572</v>
+        <v>131.9348459060617</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -5678,7 +5681,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>129.72166837428</v>
+        <v>131.9111387349154</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -5686,7 +5689,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>129.699570358383</v>
+        <v>131.8516732592326</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -5694,7 +5697,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>129.5938102747621</v>
+        <v>131.8227819512963</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -5702,7 +5705,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>129.5914271114432</v>
+        <v>131.7879607635908</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -5710,7 +5713,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>129.5533230881431</v>
+        <v>131.7297238162334</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -5718,7 +5721,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>129.427110473218</v>
+        <v>131.6757992092322</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -5726,7 +5729,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>129.3942498504892</v>
+        <v>131.6255739161631</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -5734,7 +5737,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>129.3699124862285</v>
+        <v>131.6046365651741</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -5742,7 +5745,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>129.2365240642166</v>
+        <v>131.4739227660783</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -5750,7 +5753,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>129.1715695365264</v>
+        <v>131.4630137051692</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -5758,7 +5761,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>129.0360905156825</v>
+        <v>131.4552123263185</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -5766,7 +5769,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>129.0003355394946</v>
+        <v>131.3760099553248</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -5774,7 +5777,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>128.9772195775112</v>
+        <v>131.3008712225925</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -5782,7 +5785,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>128.9145340736237</v>
+        <v>131.2670344561847</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -5790,7 +5793,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>128.8738592974142</v>
+        <v>131.2573628092051</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -5798,7 +5801,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>128.8335380088422</v>
+        <v>131.2057416519139</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -5806,7 +5809,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>128.7038881705562</v>
+        <v>131.204676959675</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -5814,7 +5817,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>128.6758480505154</v>
+        <v>131.1507951085356</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -5822,7 +5825,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>128.6441440817489</v>
+        <v>131.0998436261258</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -5830,7 +5833,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>128.6135092122462</v>
+        <v>131.0822551268714</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -5838,7 +5841,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>128.4878467360042</v>
+        <v>131.0585535811872</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -5846,7 +5849,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>128.4625038683571</v>
+        <v>131.0553854884349</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -5854,7 +5857,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>128.4580555714589</v>
+        <v>131.0359862502081</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -5862,7 +5865,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>128.4439111866835</v>
+        <v>131.0031465968854</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -5870,7 +5873,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>128.435328157059</v>
+        <v>131.0020095749622</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -5878,7 +5881,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>128.4200921017961</v>
+        <v>130.92143083918</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -5886,7 +5889,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>128.3891767215763</v>
+        <v>130.9149193123315</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -5894,7 +5897,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>128.3281056227393</v>
+        <v>130.8229855712876</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -5902,7 +5905,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>128.3260938096832</v>
+        <v>130.820075838985</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -5910,7 +5913,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>128.323204087398</v>
+        <v>130.7386393297271</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -5918,7 +5921,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>128.1895807288587</v>
+        <v>130.7252738197572</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -5926,7 +5929,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>128.1511122907845</v>
+        <v>130.6091753074226</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -5934,7 +5937,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>128.1016985033609</v>
+        <v>130.6043059559825</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -5942,7 +5945,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>128.0722391793587</v>
+        <v>130.5033950599916</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -5950,7 +5953,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>128.0421016796318</v>
+        <v>130.498788484542</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -5958,7 +5961,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>128.0273627501318</v>
+        <v>130.4669599917902</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -5966,7 +5969,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>128.0050406490876</v>
+        <v>130.4027503027989</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -5974,7 +5977,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>127.9954091664016</v>
+        <v>130.3231732861187</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -5982,7 +5985,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>127.9653612193474</v>
+        <v>130.1838280490228</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -5990,7 +5993,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>127.9502987701212</v>
+        <v>130.154216649341</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -5998,7 +6001,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>127.9303864554428</v>
+        <v>130.151665678821</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6006,7 +6009,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>127.9193447919005</v>
+        <v>130.1250198348725</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6014,7 +6017,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>127.7782149490504</v>
+        <v>130.1243182911902</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6022,7 +6025,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>127.7654179919931</v>
+        <v>130.0850531821347</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6030,7 +6033,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>127.6837691403796</v>
+        <v>130.0486063851139</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6038,7 +6041,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>127.4394049117574</v>
+        <v>130.0373099723514</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6046,7 +6049,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>127.4144714814237</v>
+        <v>129.9386152250608</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6054,7 +6057,15 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>127.4127621386592</v>
+        <v>129.8205570143515</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" t="s">
+        <v>518</v>
+      </c>
+      <c r="B518" s="1">
+        <v>129.7904992160464</v>
       </c>
     </row>
   </sheetData>
